--- a/Database.xlsx
+++ b/Database.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/ashokgopalan/Desktop/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/ashokgopalan/Downloads/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:9_{13295075-9B4C-FC4F-A700-3F600EC05FAC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BC4D9C23-E246-4041-835A-F2CE3C16B735}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="740" windowWidth="34560" windowHeight="21600" xr2:uid="{26FF7FE2-E5E3-384C-ABF6-08C089761ADA}"/>
+    <workbookView xWindow="0" yWindow="760" windowWidth="34560" windowHeight="20440" xr2:uid="{26FF7FE2-E5E3-384C-ABF6-08C089761ADA}"/>
   </bookViews>
   <sheets>
     <sheet name="sample2" sheetId="1" r:id="rId1"/>
@@ -18,7 +18,7 @@
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">sample2!$A$1:$D$956</definedName>
   </definedNames>
-  <calcPr calcId="181029"/>
+  <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -42,7 +42,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3816" uniqueCount="3013">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4052" uniqueCount="3236">
   <si>
     <t>VideoID</t>
   </si>
@@ -9081,6 +9081,675 @@
   </si>
   <si>
     <t>SRF|||| Guided Meditation|</t>
+  </si>
+  <si>
+    <t>Rc5Twttk5Mw</t>
+  </si>
+  <si>
+    <t>Hymn to Brahma</t>
+  </si>
+  <si>
+    <t>https://www.youtube.com/watch?v=Rc5Twttk5Mw</t>
+  </si>
+  <si>
+    <t>YnBLADvOleE</t>
+  </si>
+  <si>
+    <t>Dawn Chant</t>
+  </si>
+  <si>
+    <t>https://www.youtube.com/watch?v=YnBLADvOleE</t>
+  </si>
+  <si>
+    <t>kd4H7nnnB8Y</t>
+  </si>
+  <si>
+    <t>Brindavan Vihari</t>
+  </si>
+  <si>
+    <t>https://www.youtube.com/watch?v=kd4H7nnnB8Y</t>
+  </si>
+  <si>
+    <t>OfGe2pmnA48</t>
+  </si>
+  <si>
+    <t>Om Kali</t>
+  </si>
+  <si>
+    <t>https://www.youtube.com/watch?v=OfGe2pmnA48</t>
+  </si>
+  <si>
+    <t>zcJda9_MuGY</t>
+  </si>
+  <si>
+    <t>Do Not Dry the Ocean of My Love</t>
+  </si>
+  <si>
+    <t>https://www.youtube.com/watch?v=zcJda9_MuGY</t>
+  </si>
+  <si>
+    <t>MNZVJDr4l90</t>
+  </si>
+  <si>
+    <t>Jai Guru, Jai Ma</t>
+  </si>
+  <si>
+    <t>https://www.youtube.com/watch?v=MNZVJDr4l90</t>
+  </si>
+  <si>
+    <t>LZ4heAblFzQ</t>
+  </si>
+  <si>
+    <t>My Krishna Is Blue</t>
+  </si>
+  <si>
+    <t>https://www.youtube.com/watch?v=LZ4heAblFzQ</t>
+  </si>
+  <si>
+    <t>nIDLu09FRyA</t>
+  </si>
+  <si>
+    <t>Thou Art My Life</t>
+  </si>
+  <si>
+    <t>https://www.youtube.com/watch?v=nIDLu09FRyA</t>
+  </si>
+  <si>
+    <t>Gkrti3-1LjA</t>
+  </si>
+  <si>
+    <t>I Am the Bubble, Make Me the Sea</t>
+  </si>
+  <si>
+    <t>https://www.youtube.com/watch?v=Gkrti3-1LjA</t>
+  </si>
+  <si>
+    <t>RrZT6ATYNjc</t>
+  </si>
+  <si>
+    <t>Om Namo Bhagavate Vasudevaya</t>
+  </si>
+  <si>
+    <t>https://www.youtube.com/watch?v=RrZT6ATYNjc</t>
+  </si>
+  <si>
+    <t>dO2cbEY61lw</t>
+  </si>
+  <si>
+    <t>Ever New Joy</t>
+  </si>
+  <si>
+    <t>https://www.youtube.com/watch?v=dO2cbEY61lw</t>
+  </si>
+  <si>
+    <t>WUX6g83IR34</t>
+  </si>
+  <si>
+    <t>When Thy Song Flows Through Me</t>
+  </si>
+  <si>
+    <t>https://www.youtube.com/watch?v=WUX6g83IR34</t>
+  </si>
+  <si>
+    <t>c4N3fCg8AR0</t>
+  </si>
+  <si>
+    <t>https://www.youtube.com/watch?v=c4N3fCg8AR0</t>
+  </si>
+  <si>
+    <t>RtxaSGVLiHI</t>
+  </si>
+  <si>
+    <t>At Thy Feet</t>
+  </si>
+  <si>
+    <t>https://www.youtube.com/watch?v=RtxaSGVLiHI</t>
+  </si>
+  <si>
+    <t>MQZvITlGMkI</t>
+  </si>
+  <si>
+    <t>Sri Guru Sharanam</t>
+  </si>
+  <si>
+    <t>https://www.youtube.com/watch?v=MQZvITlGMkI</t>
+  </si>
+  <si>
+    <t>gHVdC3yiSu8</t>
+  </si>
+  <si>
+    <t>Will That Day Come to Me, Mother?</t>
+  </si>
+  <si>
+    <t>https://www.youtube.com/watch?v=gHVdC3yiSu8</t>
+  </si>
+  <si>
+    <t>0ikmHYSpT3A</t>
+  </si>
+  <si>
+    <t>Blue Lotus Feet</t>
+  </si>
+  <si>
+    <t>https://www.youtube.com/watch?v=0ikmHYSpT3A</t>
+  </si>
+  <si>
+    <t>UgmKA0pxP0s</t>
+  </si>
+  <si>
+    <t>https://www.youtube.com/watch?v=UgmKA0pxP0s</t>
+  </si>
+  <si>
+    <t>mxKZdxvWCrY</t>
+  </si>
+  <si>
+    <t>Govinda Jai Jai</t>
+  </si>
+  <si>
+    <t>https://www.youtube.com/watch?v=mxKZdxvWCrY</t>
+  </si>
+  <si>
+    <t>NuxP3UX_SUY</t>
+  </si>
+  <si>
+    <t>https://www.youtube.com/watch?v=NuxP3UX_SUY</t>
+  </si>
+  <si>
+    <t>Zf6a2fXS9VU</t>
+  </si>
+  <si>
+    <t>Jai Guru Jai</t>
+  </si>
+  <si>
+    <t>https://www.youtube.com/watch?v=Zf6a2fXS9VU</t>
+  </si>
+  <si>
+    <t>Shof_WmmlG0</t>
+  </si>
+  <si>
+    <t>Om Shanti</t>
+  </si>
+  <si>
+    <t>https://www.youtube.com/watch?v=Shof_WmmlG0</t>
+  </si>
+  <si>
+    <t>TR4SBHRZUE8</t>
+  </si>
+  <si>
+    <t>Aum Intro / Hymn to Brahman</t>
+  </si>
+  <si>
+    <t>https://www.youtube.com/watch?v=TR4SBHRZUE8</t>
+  </si>
+  <si>
+    <t>R4I-zcV7tNE</t>
+  </si>
+  <si>
+    <t>I Give You My Soul Call</t>
+  </si>
+  <si>
+    <t>https://www.youtube.com/watch?v=R4I-zcV7tNE</t>
+  </si>
+  <si>
+    <t>FPse1MZLiuM</t>
+  </si>
+  <si>
+    <t>Who Is In My Temple?</t>
+  </si>
+  <si>
+    <t>https://www.youtube.com/watch?v=FPse1MZLiuM</t>
+  </si>
+  <si>
+    <t>iadprkEqREE</t>
+  </si>
+  <si>
+    <t>What Lightning Flash</t>
+  </si>
+  <si>
+    <t>https://www.youtube.com/watch?v=iadprkEqREE</t>
+  </si>
+  <si>
+    <t>HvKaDD1IEw0</t>
+  </si>
+  <si>
+    <t>Wink Has Not Touched My Eyes</t>
+  </si>
+  <si>
+    <t>https://www.youtube.com/watch?v=HvKaDD1IEw0</t>
+  </si>
+  <si>
+    <t>THH3-_uJq2g</t>
+  </si>
+  <si>
+    <t>Narayan Kirtan</t>
+  </si>
+  <si>
+    <t>https://www.youtube.com/watch?v=THH3-_uJq2g</t>
+  </si>
+  <si>
+    <t>LzQmWfPc5jU</t>
+  </si>
+  <si>
+    <t>Madhura, Madhura Naam / Namo Namaste</t>
+  </si>
+  <si>
+    <t>https://www.youtube.com/watch?v=LzQmWfPc5jU</t>
+  </si>
+  <si>
+    <t>zPUzuy6hcoE</t>
+  </si>
+  <si>
+    <t>https://www.youtube.com/watch?v=zPUzuy6hcoE</t>
+  </si>
+  <si>
+    <t>kE-i8p-wGdA</t>
+  </si>
+  <si>
+    <t>https://www.youtube.com/watch?v=kE-i8p-wGdA</t>
+  </si>
+  <si>
+    <t>Au30AuaIEog</t>
+  </si>
+  <si>
+    <t>https://www.youtube.com/watch?v=Au30AuaIEog</t>
+  </si>
+  <si>
+    <t>9jJW93JMFxs</t>
+  </si>
+  <si>
+    <t>https://www.youtube.com/watch?v=9jJW93JMFxs</t>
+  </si>
+  <si>
+    <t>vQKGqftLSXs</t>
+  </si>
+  <si>
+    <t>Swami Ram Tirtha’s Song</t>
+  </si>
+  <si>
+    <t>https://www.youtube.com/watch?v=vQKGqftLSXs</t>
+  </si>
+  <si>
+    <t>4WzwdIJJ8DA</t>
+  </si>
+  <si>
+    <t>https://www.youtube.com/watch?v=4WzwdIJJ8DA</t>
+  </si>
+  <si>
+    <t>FnL2A5_2sbQ</t>
+  </si>
+  <si>
+    <t>Gurudeva</t>
+  </si>
+  <si>
+    <t>https://www.youtube.com/watch?v=FnL2A5_2sbQ</t>
+  </si>
+  <si>
+    <t>K2ed6uMPSZc</t>
+  </si>
+  <si>
+    <t>Namo Namaste</t>
+  </si>
+  <si>
+    <t>https://www.youtube.com/watch?v=K2ed6uMPSZc</t>
+  </si>
+  <si>
+    <t>5AvzM_Ljdaw</t>
+  </si>
+  <si>
+    <t>Come, Listen to My Soul Song</t>
+  </si>
+  <si>
+    <t>https://www.youtube.com/watch?v=5AvzM_Ljdaw</t>
+  </si>
+  <si>
+    <t>DAvau8w3d4A</t>
+  </si>
+  <si>
+    <t>Amaraguru, Yogananda</t>
+  </si>
+  <si>
+    <t>https://www.youtube.com/watch?v=DAvau8w3d4A</t>
+  </si>
+  <si>
+    <t>Amaraguru Yogananda</t>
+  </si>
+  <si>
+    <t>u-j-fNkNxac</t>
+  </si>
+  <si>
+    <t>O Thou Blue Sky</t>
+  </si>
+  <si>
+    <t>https://www.youtube.com/watch?v=u-j-fNkNxac</t>
+  </si>
+  <si>
+    <t>OMAS58Z6P-I</t>
+  </si>
+  <si>
+    <t>https://www.youtube.com/watch?v=OMAS58Z6P-I</t>
+  </si>
+  <si>
+    <t>O3SBN67-hDc</t>
+  </si>
+  <si>
+    <t>In the Land Beyond My Dreams</t>
+  </si>
+  <si>
+    <t>https://www.youtube.com/watch?v=O3SBN67-hDc</t>
+  </si>
+  <si>
+    <t>K5LzMw2NR-k</t>
+  </si>
+  <si>
+    <t>Thousands of Suns</t>
+  </si>
+  <si>
+    <t>https://www.youtube.com/watch?v=K5LzMw2NR-k</t>
+  </si>
+  <si>
+    <t>6OHyDyVm9wU</t>
+  </si>
+  <si>
+    <t>Cloud-Colored Christ</t>
+  </si>
+  <si>
+    <t>https://www.youtube.com/watch?v=6OHyDyVm9wU</t>
+  </si>
+  <si>
+    <t>hkZ1wB0PEOk</t>
+  </si>
+  <si>
+    <t>Receive Me on Thy Lap</t>
+  </si>
+  <si>
+    <t>https://www.youtube.com/watch?v=hkZ1wB0PEOk</t>
+  </si>
+  <si>
+    <t>-ytgLWdJUik</t>
+  </si>
+  <si>
+    <t>From This Sleep, Lord</t>
+  </si>
+  <si>
+    <t>https://www.youtube.com/watch?v=-ytgLWdJUik</t>
+  </si>
+  <si>
+    <t>ZJkaKJdzUhU</t>
+  </si>
+  <si>
+    <t>Hare Krishna</t>
+  </si>
+  <si>
+    <t>https://www.youtube.com/watch?v=ZJkaKJdzUhU</t>
+  </si>
+  <si>
+    <t>jqj5hwxDfBA</t>
+  </si>
+  <si>
+    <t>Where Is There Love?</t>
+  </si>
+  <si>
+    <t>https://www.youtube.com/watch?v=jqj5hwxDfBA</t>
+  </si>
+  <si>
+    <t>Gd9gYcaXjco</t>
+  </si>
+  <si>
+    <t>Yogananda Sharanam</t>
+  </si>
+  <si>
+    <t>https://www.youtube.com/watch?v=Gd9gYcaXjco</t>
+  </si>
+  <si>
+    <t>pr5NNezfNgE</t>
+  </si>
+  <si>
+    <t>https://www.youtube.com/watch?v=pr5NNezfNgE</t>
+  </si>
+  <si>
+    <t>3JtTQzZYQgc</t>
+  </si>
+  <si>
+    <t>https://www.youtube.com/watch?v=3JtTQzZYQgc</t>
+  </si>
+  <si>
+    <t>-mI5NZt35X0</t>
+  </si>
+  <si>
+    <t>Search Him Out in Secret</t>
+  </si>
+  <si>
+    <t>https://www.youtube.com/watch?v=-mI5NZt35X0</t>
+  </si>
+  <si>
+    <t>IPjp5WgxdqQ</t>
+  </si>
+  <si>
+    <t>Hey Bhagavan</t>
+  </si>
+  <si>
+    <t>https://www.youtube.com/watch?v=IPjp5WgxdqQ</t>
+  </si>
+  <si>
+    <t>ENx8UKqJATs</t>
+  </si>
+  <si>
+    <t>https://www.youtube.com/watch?v=ENx8UKqJATs</t>
+  </si>
+  <si>
+    <t>XO5Ea_KZ6wc</t>
+  </si>
+  <si>
+    <t>https://www.youtube.com/watch?v=XO5Ea_KZ6wc</t>
+  </si>
+  <si>
+    <t>yBml0dMPA10</t>
+  </si>
+  <si>
+    <t>https://www.youtube.com/watch?v=yBml0dMPA10</t>
+  </si>
+  <si>
+    <t>dqJOYQ9v7YE</t>
+  </si>
+  <si>
+    <t>I Will Sing Thy Name</t>
+  </si>
+  <si>
+    <t>https://www.youtube.com/watch?v=dqJOYQ9v7YE</t>
+  </si>
+  <si>
+    <t>hrihi0H-txw</t>
+  </si>
+  <si>
+    <t>Spirit and Nature</t>
+  </si>
+  <si>
+    <t>https://www.youtube.com/watch?v=hrihi0H-txw</t>
+  </si>
+  <si>
+    <t>FwTeRCBokZQ</t>
+  </si>
+  <si>
+    <t>Deliver Us From Delusion</t>
+  </si>
+  <si>
+    <t>https://www.youtube.com/watch?v=FwTeRCBokZQ</t>
+  </si>
+  <si>
+    <t>Kirtan | English|Hymn Brahma|The Ocean of Love|Kamlanada|SRF Monks</t>
+  </si>
+  <si>
+    <t>Kirtan | English|Dawn Chant|The Ocean of Love|Kamlanada|SRF Monks</t>
+  </si>
+  <si>
+    <t>Kirtan | English|Brindavan Vihari|The Ocean of Love|Kamlanada|SRF Monks</t>
+  </si>
+  <si>
+    <t>Kirtan | English|Kali|The Ocean of Love|Kamlanada|SRF Monks</t>
+  </si>
+  <si>
+    <t>Kirtan | English|Not Dry Ocean Love|The Ocean of Love|Kamlanada|SRF Monks</t>
+  </si>
+  <si>
+    <t>Kirtan | English|Jai Guru|The Ocean of Love|Kamlanada|SRF Monks</t>
+  </si>
+  <si>
+    <t>Kirtan | English|Krishna Blue|The Ocean of Love|Kamlanada|SRF Monks</t>
+  </si>
+  <si>
+    <t>Kirtan | English|Thou Art Life|The Ocean of Love|Kamlanada|SRF Monks</t>
+  </si>
+  <si>
+    <t>Kirtan | English|Bubble Make Sea|The Ocean of Love|Kamlanada|SRF Monks</t>
+  </si>
+  <si>
+    <t>Kirtan | English|Namo Bhagavate Vasudevaya|The Ocean of Love|Kamlanada|SRF Monks</t>
+  </si>
+  <si>
+    <t>Kirtan | English|Ever New Joy|The Ocean of Love|Kamlanada|SRF Monks</t>
+  </si>
+  <si>
+    <t>Kirtan | English|When Thy Song Flows Through|The Ocean of Love|Kamlanada|SRF Monks</t>
+  </si>
+  <si>
+    <t>Kirtan | English|Hymn Brahma|Listen to My Soul Song|Premamai|SRF Nuns</t>
+  </si>
+  <si>
+    <t>Kirtan | English|Thy Feet|Listen to My Soul Song|Premamai|SRF Nuns</t>
+  </si>
+  <si>
+    <t>Kirtan | English|Sri Guru Sharanam|Listen to My Soul Song|Premamai|SRF Nuns</t>
+  </si>
+  <si>
+    <t>Kirtan | English|Will That Day Come Mother|Listen to My Soul Song|Premamai|SRF Nuns</t>
+  </si>
+  <si>
+    <t>Kirtan | English|Blue Lotus Feet|Listen to My Soul Song|Premamai|SRF Nuns</t>
+  </si>
+  <si>
+    <t>Kirtan | English|Krishna Blue|Listen to My Soul Song|Premamai|SRF Nuns</t>
+  </si>
+  <si>
+    <t>Kirtan | English|Govinda Jai|Listen to My Soul Song|Premamai|SRF Nuns</t>
+  </si>
+  <si>
+    <t>Kirtan | English|When Thy Song Flows Through|Listen to My Soul Song|Premamai|SRF Nuns</t>
+  </si>
+  <si>
+    <t>Kirtan | English|Jai Guru|Listen to My Soul Song|Premamai|SRF Nuns</t>
+  </si>
+  <si>
+    <t>Kirtan | English|Shanti|Listen to My Soul Song|Premamai|SRF Nuns</t>
+  </si>
+  <si>
+    <t>Kirtan | English|Aum Intro Hymn Brahman|Come Out of the Silent Sky|Baskaranada|SRF Monks</t>
+  </si>
+  <si>
+    <t>Kirtan | English|Give You Soul Call|Come Out of the Silent Sky|Baskaranada|SRF Monks</t>
+  </si>
+  <si>
+    <t>Kirtan | English|Who Temple|Come Out of the Silent Sky|Baskaranada|SRF Monks</t>
+  </si>
+  <si>
+    <t>Kirtan | English|What Lightning Flash|Come Out of the Silent Sky|Baskaranada|SRF Monks</t>
+  </si>
+  <si>
+    <t>Kirtan | English|Wink Has Not Touched Eyes|Come Out of the Silent Sky|Baskaranada|SRF Monks</t>
+  </si>
+  <si>
+    <t>Kirtan | English|Narayan Kirtan|Come Out of the Silent Sky|Baskaranada|SRF Monks</t>
+  </si>
+  <si>
+    <t>Kirtan | English|Madhura Naam Namo Namaste|Come Out of the Silent Sky|Baskaranada|SRF Monks</t>
+  </si>
+  <si>
+    <t>Kirtan | English|Hymn Brahma|O Blazing Light|Baskaranada|SRF Monks</t>
+  </si>
+  <si>
+    <t>Kirtan | English|Dawn Chant|O Blazing Light|Baskaranada|SRF Monks</t>
+  </si>
+  <si>
+    <t>Kirtan | English|Govinda Jai|O Blazing Light|Baskaranada|SRF Monks</t>
+  </si>
+  <si>
+    <t>Kirtan | English|Blue Lotus Feet|O Blazing Light|Baskaranada|SRF Monks</t>
+  </si>
+  <si>
+    <t>Kirtan | English|Swami Ram Tirthas Song|O Blazing Light|Baskaranada|SRF Monks</t>
+  </si>
+  <si>
+    <t>Kirtan | English|Kali|O Blazing Light|Baskaranada|SRF Monks</t>
+  </si>
+  <si>
+    <t>Kirtan | English|Gurudeva|O Blazing Light|Baskaranada|SRF Monks</t>
+  </si>
+  <si>
+    <t>Kirtan | English|Namo Namaste|O Blazing Light|Baskaranada|SRF Monks</t>
+  </si>
+  <si>
+    <t>Kirtan | English|Come Listen Soul Song|Thy Heart of Hearts|Kamlanada|SRF Monks</t>
+  </si>
+  <si>
+    <t>Kirtan | English|Amaraguru Yogananda|Thy Heart of Hearts|Kamlanada|SRF Monks</t>
+  </si>
+  <si>
+    <t>Kirtan | English|Thou Blue Sky|Thy Heart of Hearts|Kamlanada|SRF Monks</t>
+  </si>
+  <si>
+    <t>Kirtan | English|Thy Feet|Thy Heart of Hearts|Kamlanada|SRF Monks</t>
+  </si>
+  <si>
+    <t>Kirtan | English|Land Beyond Dreams|Thy Heart of Hearts|Kamlanada|SRF Monks</t>
+  </si>
+  <si>
+    <t>Kirtan | English|Thousands Suns|Thy Heart of Hearts|Kamlanada|SRF Monks</t>
+  </si>
+  <si>
+    <t>Kirtan | English|CloudColored Christ|Thy Heart of Hearts|Kamlanada|SRF Monks</t>
+  </si>
+  <si>
+    <t>Kirtan | English|Receive Thy Lap|Thy Heart of Hearts|Kamlanada|SRF Monks</t>
+  </si>
+  <si>
+    <t>Kirtan | English|From This Sleep Lord|Thy Heart of Hearts|Kamlanada|SRF Monks</t>
+  </si>
+  <si>
+    <t>Kirtan | English|Hare Krishna|Thy Heart of Hearts|Kamlanada|SRF Monks</t>
+  </si>
+  <si>
+    <t>Kirtan | English|Where There Love|Thy Heart of Hearts|Kamlanada|SRF Monks</t>
+  </si>
+  <si>
+    <t>Kirtan | English|Yogananda Sharanam|Thy Heart of Hearts|Kamlanada|SRF Monks</t>
+  </si>
+  <si>
+    <t>Kirtan | English|Hymn Brahma|Ever New Joy|Premamai|SRF Nuns</t>
+  </si>
+  <si>
+    <t>Kirtan | English|Amaraguru Yogananda|Ever New Joy|Premamai|SRF Nuns</t>
+  </si>
+  <si>
+    <t>Kirtan | English|Search Him Out Secret|Ever New Joy|Premamai|SRF Nuns</t>
+  </si>
+  <si>
+    <t>Kirtan | English|Hey Bhagavan|Ever New Joy|Premamai|SRF Nuns</t>
+  </si>
+  <si>
+    <t>Kirtan | English|Hare Krishna|Ever New Joy|Premamai|SRF Nuns</t>
+  </si>
+  <si>
+    <t>Kirtan | English|Give You Soul Call|Ever New Joy|Premamai|SRF Nuns</t>
+  </si>
+  <si>
+    <t>Kirtan | English|Ever New Joy|Ever New Joy|Premamai|SRF Nuns</t>
+  </si>
+  <si>
+    <t>Kirtan | English|Will Sing Thy Name|Ever New Joy|Premamai|SRF Nuns</t>
+  </si>
+  <si>
+    <t>Kirtan | English|Spirit Nature|Ever New Joy|Premamai|SRF Nuns</t>
+  </si>
+  <si>
+    <t>Kirtan | English|Deliver From Delusion|Ever New Joy|Premamai|SRF Nuns</t>
   </si>
 </sst>
 </file>
@@ -9452,7 +10121,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{EE52D9B7-0D33-6C4B-ABD2-124A93043E14}">
-  <dimension ref="A1:D956"/>
+  <dimension ref="A1:D1015"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="44" bestFit="1" customWidth="1"/>
@@ -22842,6 +23511,832 @@
         <v>2999</v>
       </c>
     </row>
+    <row r="957" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A957" t="s">
+        <v>3013</v>
+      </c>
+      <c r="B957" t="s">
+        <v>3014</v>
+      </c>
+      <c r="C957" t="s">
+        <v>3015</v>
+      </c>
+      <c r="D957" t="s">
+        <v>3177</v>
+      </c>
+    </row>
+    <row r="958" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A958" t="s">
+        <v>3016</v>
+      </c>
+      <c r="B958" t="s">
+        <v>3017</v>
+      </c>
+      <c r="C958" t="s">
+        <v>3018</v>
+      </c>
+      <c r="D958" t="s">
+        <v>3178</v>
+      </c>
+    </row>
+    <row r="959" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A959" t="s">
+        <v>3019</v>
+      </c>
+      <c r="B959" t="s">
+        <v>3020</v>
+      </c>
+      <c r="C959" t="s">
+        <v>3021</v>
+      </c>
+      <c r="D959" t="s">
+        <v>3179</v>
+      </c>
+    </row>
+    <row r="960" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A960" t="s">
+        <v>3022</v>
+      </c>
+      <c r="B960" t="s">
+        <v>3023</v>
+      </c>
+      <c r="C960" t="s">
+        <v>3024</v>
+      </c>
+      <c r="D960" t="s">
+        <v>3180</v>
+      </c>
+    </row>
+    <row r="961" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A961" t="s">
+        <v>3025</v>
+      </c>
+      <c r="B961" t="s">
+        <v>3026</v>
+      </c>
+      <c r="C961" t="s">
+        <v>3027</v>
+      </c>
+      <c r="D961" t="s">
+        <v>3181</v>
+      </c>
+    </row>
+    <row r="962" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A962" t="s">
+        <v>3028</v>
+      </c>
+      <c r="B962" t="s">
+        <v>3029</v>
+      </c>
+      <c r="C962" t="s">
+        <v>3030</v>
+      </c>
+      <c r="D962" t="s">
+        <v>3182</v>
+      </c>
+    </row>
+    <row r="963" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A963" t="s">
+        <v>3031</v>
+      </c>
+      <c r="B963" t="s">
+        <v>3032</v>
+      </c>
+      <c r="C963" t="s">
+        <v>3033</v>
+      </c>
+      <c r="D963" t="s">
+        <v>3183</v>
+      </c>
+    </row>
+    <row r="964" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A964" t="s">
+        <v>3034</v>
+      </c>
+      <c r="B964" t="s">
+        <v>3035</v>
+      </c>
+      <c r="C964" t="s">
+        <v>3036</v>
+      </c>
+      <c r="D964" t="s">
+        <v>3184</v>
+      </c>
+    </row>
+    <row r="965" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A965" t="s">
+        <v>3037</v>
+      </c>
+      <c r="B965" t="s">
+        <v>3038</v>
+      </c>
+      <c r="C965" t="s">
+        <v>3039</v>
+      </c>
+      <c r="D965" t="s">
+        <v>3185</v>
+      </c>
+    </row>
+    <row r="966" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A966" t="s">
+        <v>3040</v>
+      </c>
+      <c r="B966" t="s">
+        <v>3041</v>
+      </c>
+      <c r="C966" t="s">
+        <v>3042</v>
+      </c>
+      <c r="D966" t="s">
+        <v>3186</v>
+      </c>
+    </row>
+    <row r="967" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A967" t="s">
+        <v>3043</v>
+      </c>
+      <c r="B967" t="s">
+        <v>3044</v>
+      </c>
+      <c r="C967" t="s">
+        <v>3045</v>
+      </c>
+      <c r="D967" t="s">
+        <v>3187</v>
+      </c>
+    </row>
+    <row r="968" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A968" t="s">
+        <v>3046</v>
+      </c>
+      <c r="B968" t="s">
+        <v>3047</v>
+      </c>
+      <c r="C968" t="s">
+        <v>3048</v>
+      </c>
+      <c r="D968" t="s">
+        <v>3188</v>
+      </c>
+    </row>
+    <row r="969" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A969" t="s">
+        <v>3049</v>
+      </c>
+      <c r="B969" t="s">
+        <v>3014</v>
+      </c>
+      <c r="C969" t="s">
+        <v>3050</v>
+      </c>
+      <c r="D969" t="s">
+        <v>3189</v>
+      </c>
+    </row>
+    <row r="970" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A970" t="s">
+        <v>3051</v>
+      </c>
+      <c r="B970" t="s">
+        <v>3052</v>
+      </c>
+      <c r="C970" t="s">
+        <v>3053</v>
+      </c>
+      <c r="D970" t="s">
+        <v>3190</v>
+      </c>
+    </row>
+    <row r="971" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A971" t="s">
+        <v>3054</v>
+      </c>
+      <c r="B971" t="s">
+        <v>3055</v>
+      </c>
+      <c r="C971" t="s">
+        <v>3056</v>
+      </c>
+      <c r="D971" t="s">
+        <v>3191</v>
+      </c>
+    </row>
+    <row r="972" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A972" t="s">
+        <v>3057</v>
+      </c>
+      <c r="B972" t="s">
+        <v>3058</v>
+      </c>
+      <c r="C972" t="s">
+        <v>3059</v>
+      </c>
+      <c r="D972" t="s">
+        <v>3192</v>
+      </c>
+    </row>
+    <row r="973" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A973" t="s">
+        <v>3060</v>
+      </c>
+      <c r="B973" t="s">
+        <v>3061</v>
+      </c>
+      <c r="C973" t="s">
+        <v>3062</v>
+      </c>
+      <c r="D973" t="s">
+        <v>3193</v>
+      </c>
+    </row>
+    <row r="974" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A974" t="s">
+        <v>3063</v>
+      </c>
+      <c r="B974" t="s">
+        <v>3032</v>
+      </c>
+      <c r="C974" t="s">
+        <v>3064</v>
+      </c>
+      <c r="D974" t="s">
+        <v>3194</v>
+      </c>
+    </row>
+    <row r="975" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A975" t="s">
+        <v>3065</v>
+      </c>
+      <c r="B975" t="s">
+        <v>3066</v>
+      </c>
+      <c r="C975" t="s">
+        <v>3067</v>
+      </c>
+      <c r="D975" t="s">
+        <v>3195</v>
+      </c>
+    </row>
+    <row r="976" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A976" t="s">
+        <v>3068</v>
+      </c>
+      <c r="B976" t="s">
+        <v>3047</v>
+      </c>
+      <c r="C976" t="s">
+        <v>3069</v>
+      </c>
+      <c r="D976" t="s">
+        <v>3196</v>
+      </c>
+    </row>
+    <row r="977" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A977" t="s">
+        <v>3070</v>
+      </c>
+      <c r="B977" t="s">
+        <v>3071</v>
+      </c>
+      <c r="C977" t="s">
+        <v>3072</v>
+      </c>
+      <c r="D977" t="s">
+        <v>3197</v>
+      </c>
+    </row>
+    <row r="978" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A978" t="s">
+        <v>3073</v>
+      </c>
+      <c r="B978" t="s">
+        <v>3074</v>
+      </c>
+      <c r="C978" t="s">
+        <v>3075</v>
+      </c>
+      <c r="D978" t="s">
+        <v>3198</v>
+      </c>
+    </row>
+    <row r="979" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A979" t="s">
+        <v>3076</v>
+      </c>
+      <c r="B979" t="s">
+        <v>3077</v>
+      </c>
+      <c r="C979" t="s">
+        <v>3078</v>
+      </c>
+      <c r="D979" t="s">
+        <v>3199</v>
+      </c>
+    </row>
+    <row r="980" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A980" t="s">
+        <v>3079</v>
+      </c>
+      <c r="B980" t="s">
+        <v>3080</v>
+      </c>
+      <c r="C980" t="s">
+        <v>3081</v>
+      </c>
+      <c r="D980" t="s">
+        <v>3200</v>
+      </c>
+    </row>
+    <row r="981" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A981" t="s">
+        <v>3082</v>
+      </c>
+      <c r="B981" t="s">
+        <v>3083</v>
+      </c>
+      <c r="C981" t="s">
+        <v>3084</v>
+      </c>
+      <c r="D981" t="s">
+        <v>3201</v>
+      </c>
+    </row>
+    <row r="982" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A982" t="s">
+        <v>3085</v>
+      </c>
+      <c r="B982" t="s">
+        <v>3086</v>
+      </c>
+      <c r="C982" t="s">
+        <v>3087</v>
+      </c>
+      <c r="D982" t="s">
+        <v>3202</v>
+      </c>
+    </row>
+    <row r="983" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A983" t="s">
+        <v>3088</v>
+      </c>
+      <c r="B983" t="s">
+        <v>3089</v>
+      </c>
+      <c r="C983" t="s">
+        <v>3090</v>
+      </c>
+      <c r="D983" t="s">
+        <v>3203</v>
+      </c>
+    </row>
+    <row r="984" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A984" t="s">
+        <v>3091</v>
+      </c>
+      <c r="B984" t="s">
+        <v>3092</v>
+      </c>
+      <c r="C984" t="s">
+        <v>3093</v>
+      </c>
+      <c r="D984" t="s">
+        <v>3204</v>
+      </c>
+    </row>
+    <row r="985" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A985" t="s">
+        <v>3094</v>
+      </c>
+      <c r="B985" t="s">
+        <v>3095</v>
+      </c>
+      <c r="C985" t="s">
+        <v>3096</v>
+      </c>
+      <c r="D985" t="s">
+        <v>3205</v>
+      </c>
+    </row>
+    <row r="986" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A986" t="s">
+        <v>3097</v>
+      </c>
+      <c r="B986" t="s">
+        <v>3014</v>
+      </c>
+      <c r="C986" t="s">
+        <v>3098</v>
+      </c>
+      <c r="D986" t="s">
+        <v>3206</v>
+      </c>
+    </row>
+    <row r="987" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A987" t="s">
+        <v>3099</v>
+      </c>
+      <c r="B987" t="s">
+        <v>3017</v>
+      </c>
+      <c r="C987" t="s">
+        <v>3100</v>
+      </c>
+      <c r="D987" t="s">
+        <v>3207</v>
+      </c>
+    </row>
+    <row r="988" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A988" t="s">
+        <v>3101</v>
+      </c>
+      <c r="B988" t="s">
+        <v>3066</v>
+      </c>
+      <c r="C988" t="s">
+        <v>3102</v>
+      </c>
+      <c r="D988" t="s">
+        <v>3208</v>
+      </c>
+    </row>
+    <row r="989" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A989" t="s">
+        <v>3103</v>
+      </c>
+      <c r="B989" t="s">
+        <v>3061</v>
+      </c>
+      <c r="C989" t="s">
+        <v>3104</v>
+      </c>
+      <c r="D989" t="s">
+        <v>3209</v>
+      </c>
+    </row>
+    <row r="990" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A990" t="s">
+        <v>3105</v>
+      </c>
+      <c r="B990" t="s">
+        <v>3106</v>
+      </c>
+      <c r="C990" t="s">
+        <v>3107</v>
+      </c>
+      <c r="D990" t="s">
+        <v>3210</v>
+      </c>
+    </row>
+    <row r="991" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A991" t="s">
+        <v>3108</v>
+      </c>
+      <c r="B991" t="s">
+        <v>3023</v>
+      </c>
+      <c r="C991" t="s">
+        <v>3109</v>
+      </c>
+      <c r="D991" t="s">
+        <v>3211</v>
+      </c>
+    </row>
+    <row r="992" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A992" t="s">
+        <v>3110</v>
+      </c>
+      <c r="B992" t="s">
+        <v>3111</v>
+      </c>
+      <c r="C992" t="s">
+        <v>3112</v>
+      </c>
+      <c r="D992" t="s">
+        <v>3212</v>
+      </c>
+    </row>
+    <row r="993" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A993" t="s">
+        <v>3113</v>
+      </c>
+      <c r="B993" t="s">
+        <v>3114</v>
+      </c>
+      <c r="C993" t="s">
+        <v>3115</v>
+      </c>
+      <c r="D993" t="s">
+        <v>3213</v>
+      </c>
+    </row>
+    <row r="994" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A994" t="s">
+        <v>3116</v>
+      </c>
+      <c r="B994" t="s">
+        <v>3117</v>
+      </c>
+      <c r="C994" t="s">
+        <v>3118</v>
+      </c>
+      <c r="D994" t="s">
+        <v>3214</v>
+      </c>
+    </row>
+    <row r="995" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A995" t="s">
+        <v>3119</v>
+      </c>
+      <c r="B995" t="s">
+        <v>3120</v>
+      </c>
+      <c r="C995" t="s">
+        <v>3121</v>
+      </c>
+      <c r="D995" t="s">
+        <v>3215</v>
+      </c>
+    </row>
+    <row r="996" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A996" t="s">
+        <v>3123</v>
+      </c>
+      <c r="B996" t="s">
+        <v>3124</v>
+      </c>
+      <c r="C996" t="s">
+        <v>3125</v>
+      </c>
+      <c r="D996" t="s">
+        <v>3216</v>
+      </c>
+    </row>
+    <row r="997" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A997" t="s">
+        <v>3126</v>
+      </c>
+      <c r="B997" t="s">
+        <v>3052</v>
+      </c>
+      <c r="C997" t="s">
+        <v>3127</v>
+      </c>
+      <c r="D997" t="s">
+        <v>3217</v>
+      </c>
+    </row>
+    <row r="998" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A998" t="s">
+        <v>3128</v>
+      </c>
+      <c r="B998" t="s">
+        <v>3129</v>
+      </c>
+      <c r="C998" t="s">
+        <v>3130</v>
+      </c>
+      <c r="D998" t="s">
+        <v>3218</v>
+      </c>
+    </row>
+    <row r="999" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A999" t="s">
+        <v>3131</v>
+      </c>
+      <c r="B999" t="s">
+        <v>3132</v>
+      </c>
+      <c r="C999" t="s">
+        <v>3133</v>
+      </c>
+      <c r="D999" t="s">
+        <v>3219</v>
+      </c>
+    </row>
+    <row r="1000" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A1000" t="s">
+        <v>3134</v>
+      </c>
+      <c r="B1000" t="s">
+        <v>3135</v>
+      </c>
+      <c r="C1000" t="s">
+        <v>3136</v>
+      </c>
+      <c r="D1000" t="s">
+        <v>3220</v>
+      </c>
+    </row>
+    <row r="1001" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A1001" t="s">
+        <v>3137</v>
+      </c>
+      <c r="B1001" t="s">
+        <v>3138</v>
+      </c>
+      <c r="C1001" t="s">
+        <v>3139</v>
+      </c>
+      <c r="D1001" t="s">
+        <v>3221</v>
+      </c>
+    </row>
+    <row r="1002" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A1002" t="s">
+        <v>3140</v>
+      </c>
+      <c r="B1002" t="s">
+        <v>3141</v>
+      </c>
+      <c r="C1002" t="s">
+        <v>3142</v>
+      </c>
+      <c r="D1002" t="s">
+        <v>3222</v>
+      </c>
+    </row>
+    <row r="1003" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A1003" t="s">
+        <v>3143</v>
+      </c>
+      <c r="B1003" t="s">
+        <v>3144</v>
+      </c>
+      <c r="C1003" t="s">
+        <v>3145</v>
+      </c>
+      <c r="D1003" t="s">
+        <v>3223</v>
+      </c>
+    </row>
+    <row r="1004" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A1004" t="s">
+        <v>3146</v>
+      </c>
+      <c r="B1004" t="s">
+        <v>3147</v>
+      </c>
+      <c r="C1004" t="s">
+        <v>3148</v>
+      </c>
+      <c r="D1004" t="s">
+        <v>3224</v>
+      </c>
+    </row>
+    <row r="1005" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A1005" t="s">
+        <v>3149</v>
+      </c>
+      <c r="B1005" t="s">
+        <v>3150</v>
+      </c>
+      <c r="C1005" t="s">
+        <v>3151</v>
+      </c>
+      <c r="D1005" t="s">
+        <v>3225</v>
+      </c>
+    </row>
+    <row r="1006" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A1006" t="s">
+        <v>3152</v>
+      </c>
+      <c r="B1006" t="s">
+        <v>3014</v>
+      </c>
+      <c r="C1006" t="s">
+        <v>3153</v>
+      </c>
+      <c r="D1006" t="s">
+        <v>3226</v>
+      </c>
+    </row>
+    <row r="1007" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A1007" t="s">
+        <v>3154</v>
+      </c>
+      <c r="B1007" t="s">
+        <v>3122</v>
+      </c>
+      <c r="C1007" t="s">
+        <v>3155</v>
+      </c>
+      <c r="D1007" t="s">
+        <v>3227</v>
+      </c>
+    </row>
+    <row r="1008" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A1008" t="s">
+        <v>3156</v>
+      </c>
+      <c r="B1008" t="s">
+        <v>3157</v>
+      </c>
+      <c r="C1008" t="s">
+        <v>3158</v>
+      </c>
+      <c r="D1008" t="s">
+        <v>3228</v>
+      </c>
+    </row>
+    <row r="1009" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A1009" t="s">
+        <v>3159</v>
+      </c>
+      <c r="B1009" t="s">
+        <v>3160</v>
+      </c>
+      <c r="C1009" t="s">
+        <v>3161</v>
+      </c>
+      <c r="D1009" t="s">
+        <v>3229</v>
+      </c>
+    </row>
+    <row r="1010" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A1010" t="s">
+        <v>3162</v>
+      </c>
+      <c r="B1010" t="s">
+        <v>3144</v>
+      </c>
+      <c r="C1010" t="s">
+        <v>3163</v>
+      </c>
+      <c r="D1010" t="s">
+        <v>3230</v>
+      </c>
+    </row>
+    <row r="1011" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A1011" t="s">
+        <v>3164</v>
+      </c>
+      <c r="B1011" t="s">
+        <v>3080</v>
+      </c>
+      <c r="C1011" t="s">
+        <v>3165</v>
+      </c>
+      <c r="D1011" t="s">
+        <v>3231</v>
+      </c>
+    </row>
+    <row r="1012" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A1012" t="s">
+        <v>3166</v>
+      </c>
+      <c r="B1012" t="s">
+        <v>3044</v>
+      </c>
+      <c r="C1012" t="s">
+        <v>3167</v>
+      </c>
+      <c r="D1012" t="s">
+        <v>3232</v>
+      </c>
+    </row>
+    <row r="1013" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A1013" t="s">
+        <v>3168</v>
+      </c>
+      <c r="B1013" t="s">
+        <v>3169</v>
+      </c>
+      <c r="C1013" t="s">
+        <v>3170</v>
+      </c>
+      <c r="D1013" t="s">
+        <v>3233</v>
+      </c>
+    </row>
+    <row r="1014" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A1014" t="s">
+        <v>3171</v>
+      </c>
+      <c r="B1014" t="s">
+        <v>3172</v>
+      </c>
+      <c r="C1014" t="s">
+        <v>3173</v>
+      </c>
+      <c r="D1014" t="s">
+        <v>3234</v>
+      </c>
+    </row>
+    <row r="1015" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A1015" t="s">
+        <v>3174</v>
+      </c>
+      <c r="B1015" t="s">
+        <v>3175</v>
+      </c>
+      <c r="C1015" t="s">
+        <v>3176</v>
+      </c>
+      <c r="D1015" t="s">
+        <v>3235</v>
+      </c>
+    </row>
   </sheetData>
   <autoFilter ref="A1:D956" xr:uid="{EE52D9B7-0D33-6C4B-ABD2-124A93043E14}"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/Database.xlsx
+++ b/Database.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/ashokgopalan/Downloads/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BC4D9C23-E246-4041-835A-F2CE3C16B735}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D7297A8B-7A0C-BF44-AEB1-A124FF2D5DCC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="760" windowWidth="34560" windowHeight="20440" xr2:uid="{26FF7FE2-E5E3-384C-ABF6-08C089761ADA}"/>
   </bookViews>
@@ -42,7 +42,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4052" uniqueCount="3236">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4628" uniqueCount="3658">
   <si>
     <t>VideoID</t>
   </si>
@@ -9750,6 +9750,1272 @@
   </si>
   <si>
     <t>Kirtan | English|Deliver From Delusion|Ever New Joy|Premamai|SRF Nuns</t>
+  </si>
+  <si>
+    <t>1aBSfh5r-2o</t>
+  </si>
+  <si>
+    <t>A God You Can Relate To</t>
+  </si>
+  <si>
+    <t>https://www.youtube.com/watch?v=1aBSfh5r-2o</t>
+  </si>
+  <si>
+    <t>NRuiugdzrEA</t>
+  </si>
+  <si>
+    <t>Your Real Nature Is Joy</t>
+  </si>
+  <si>
+    <t>https://www.youtube.com/watch?v=NRuiugdzrEA</t>
+  </si>
+  <si>
+    <t>ozg-3QB1EIk</t>
+  </si>
+  <si>
+    <t>Prayer Is an Intimate Conversation With God</t>
+  </si>
+  <si>
+    <t>https://www.youtube.com/watch?v=ozg-3QB1EIk</t>
+  </si>
+  <si>
+    <t>JcwdYg1Dwmg</t>
+  </si>
+  <si>
+    <t>God Loves Us as We Are</t>
+  </si>
+  <si>
+    <t>https://www.youtube.com/watch?v=JcwdYg1Dwmg</t>
+  </si>
+  <si>
+    <t>kJHRZgBX4RU</t>
+  </si>
+  <si>
+    <t>“Trying On” Personal Change</t>
+  </si>
+  <si>
+    <t>https://www.youtube.com/watch?v=kJHRZgBX4RU</t>
+  </si>
+  <si>
+    <t>5_WPl1HVCGo</t>
+  </si>
+  <si>
+    <t>Discover the Joy of the Soul | 2026 SRF World Convocation</t>
+  </si>
+  <si>
+    <t>https://www.youtube.com/watch?v=5_WPl1HVCGo</t>
+  </si>
+  <si>
+    <t>1hEhGN4PVo4</t>
+  </si>
+  <si>
+    <t>“I Give You My Soul Call” | A Guided Meditation</t>
+  </si>
+  <si>
+    <t>https://www.youtube.com/watch?v=1hEhGN4PVo4</t>
+  </si>
+  <si>
+    <t>-Mxf7alEQjw</t>
+  </si>
+  <si>
+    <t>E-Sjl_LKkF4</t>
+  </si>
+  <si>
+    <t>Use Your Initiative to Find Lasting Joy</t>
+  </si>
+  <si>
+    <t>https://www.youtube.com/watch?v=E-Sjl_LKkF4</t>
+  </si>
+  <si>
+    <t>1H8Ee88Y8Ug</t>
+  </si>
+  <si>
+    <t>Gratitude Brings Happiness</t>
+  </si>
+  <si>
+    <t>https://www.youtube.com/watch?v=1H8Ee88Y8Ug</t>
+  </si>
+  <si>
+    <t>WSJl9D9RHlI</t>
+  </si>
+  <si>
+    <t>Learn to Love God Through Yoga Meditation</t>
+  </si>
+  <si>
+    <t>https://www.youtube.com/watch?v=WSJl9D9RHlI</t>
+  </si>
+  <si>
+    <t>NCV3FVBadWQ</t>
+  </si>
+  <si>
+    <t>Guided Visualization on Ever-Expanding Love by Paramahansa Yogananda</t>
+  </si>
+  <si>
+    <t>https://www.youtube.com/watch?v=NCV3FVBadWQ</t>
+  </si>
+  <si>
+    <t>dKtggFgR79k</t>
+  </si>
+  <si>
+    <t>You Will Realize God</t>
+  </si>
+  <si>
+    <t>https://www.youtube.com/watch?v=dKtggFgR79k</t>
+  </si>
+  <si>
+    <t>QqqnTYFC3hU</t>
+  </si>
+  <si>
+    <t>God Will Answer You | Yogananda’s “How-to-Live” Wisdom</t>
+  </si>
+  <si>
+    <t>https://www.youtube.com/watch?v=QqqnTYFC3hU</t>
+  </si>
+  <si>
+    <t>D_tdWu5MGlg</t>
+  </si>
+  <si>
+    <t>Keep More of Your Consciousness Within</t>
+  </si>
+  <si>
+    <t>https://www.youtube.com/watch?v=D_tdWu5MGlg</t>
+  </si>
+  <si>
+    <t>xMBNMnS3YDY</t>
+  </si>
+  <si>
+    <t>We Need a Guide on the Spiritual Path</t>
+  </si>
+  <si>
+    <t>https://www.youtube.com/watch?v=xMBNMnS3YDY</t>
+  </si>
+  <si>
+    <t>7KpZ3zQKIAQ</t>
+  </si>
+  <si>
+    <t>The Eternal Life of God | An Affirmation by Paramahansa Yogananda</t>
+  </si>
+  <si>
+    <t>https://www.youtube.com/watch?v=7KpZ3zQKIAQ</t>
+  </si>
+  <si>
+    <t>ECB1F9wE2wQ</t>
+  </si>
+  <si>
+    <t>Radiate Your Love to Others</t>
+  </si>
+  <si>
+    <t>https://www.youtube.com/watch?v=ECB1F9wE2wQ</t>
+  </si>
+  <si>
+    <t>Nw-izzO9-qM</t>
+  </si>
+  <si>
+    <t>Stay Close to God</t>
+  </si>
+  <si>
+    <t>https://www.youtube.com/watch?v=Nw-izzO9-qM</t>
+  </si>
+  <si>
+    <t>LbyoZx-bs6c</t>
+  </si>
+  <si>
+    <t>Yogananda’s Kriya Yoga Harmonizes Our Inner Life</t>
+  </si>
+  <si>
+    <t>https://www.youtube.com/watch?v=LbyoZx-bs6c</t>
+  </si>
+  <si>
+    <t>W8a2O5-gpC8</t>
+  </si>
+  <si>
+    <t>The Highest Joy in Life</t>
+  </si>
+  <si>
+    <t>https://www.youtube.com/watch?v=W8a2O5-gpC8</t>
+  </si>
+  <si>
+    <t>El7frk-iMec</t>
+  </si>
+  <si>
+    <t>The Supreme Gift | Yogananda’s “How-to-Live” Wisdom</t>
+  </si>
+  <si>
+    <t>https://www.youtube.com/watch?v=El7frk-iMec</t>
+  </si>
+  <si>
+    <t>PCIn1miQtQ4</t>
+  </si>
+  <si>
+    <t>You Can Find Peace in the New Year</t>
+  </si>
+  <si>
+    <t>https://www.youtube.com/watch?v=PCIn1miQtQ4</t>
+  </si>
+  <si>
+    <t>wxzPhOUqfI8</t>
+  </si>
+  <si>
+    <t>How to Improve the World We Live In</t>
+  </si>
+  <si>
+    <t>https://www.youtube.com/watch?v=wxzPhOUqfI8</t>
+  </si>
+  <si>
+    <t>-UOAQlzbfVo</t>
+  </si>
+  <si>
+    <t>Tough Experiences Bring Out Our Strength</t>
+  </si>
+  <si>
+    <t>https://www.youtube.com/watch?v=-UOAQlzbfVo</t>
+  </si>
+  <si>
+    <t>F1j0pl-iH8Q</t>
+  </si>
+  <si>
+    <t>What Is Self-realization?</t>
+  </si>
+  <si>
+    <t>https://www.youtube.com/watch?v=F1j0pl-iH8Q</t>
+  </si>
+  <si>
+    <t>CHdjOkUbBNs</t>
+  </si>
+  <si>
+    <t>“The Cosmic Sphere of Love” | An Affirmation by Paramahansa Yogananda</t>
+  </si>
+  <si>
+    <t>https://www.youtube.com/watch?v=CHdjOkUbBNs</t>
+  </si>
+  <si>
+    <t>KonJOVGtRzk</t>
+  </si>
+  <si>
+    <t>Meditation Awakens Divine Realization</t>
+  </si>
+  <si>
+    <t>https://www.youtube.com/watch?v=KonJOVGtRzk</t>
+  </si>
+  <si>
+    <t>i6hVyuVDWEw</t>
+  </si>
+  <si>
+    <t>We Can All Have Divine Joy</t>
+  </si>
+  <si>
+    <t>https://www.youtube.com/watch?v=i6hVyuVDWEw</t>
+  </si>
+  <si>
+    <t>gfJmynBOM40</t>
+  </si>
+  <si>
+    <t>Our Relationship With God | Yogananda’s “How-to-Live” Wisdom</t>
+  </si>
+  <si>
+    <t>https://www.youtube.com/watch?v=gfJmynBOM40</t>
+  </si>
+  <si>
+    <t>-Xk73ENV-40</t>
+  </si>
+  <si>
+    <t>The Power to Accomplish | Yogananda’s “How-to-Live” Wisdom</t>
+  </si>
+  <si>
+    <t>https://www.youtube.com/watch?v=-Xk73ENV-40</t>
+  </si>
+  <si>
+    <t>Jk2il25SKqs</t>
+  </si>
+  <si>
+    <t>You Are Unique | Yogananda’s “How-to-Live” Wisdom</t>
+  </si>
+  <si>
+    <t>https://www.youtube.com/watch?v=Jk2il25SKqs</t>
+  </si>
+  <si>
+    <t>XENzQdN-DLc</t>
+  </si>
+  <si>
+    <t>Be on Fire With Purpose | Yogananda’s “How-to-Live” Wisdom</t>
+  </si>
+  <si>
+    <t>https://www.youtube.com/watch?v=XENzQdN-DLc</t>
+  </si>
+  <si>
+    <t>SWJfwG556ZE</t>
+  </si>
+  <si>
+    <t>Creating Dynamic Will Power | Yogananda’s “How-to-Live” Wisdom</t>
+  </si>
+  <si>
+    <t>https://www.youtube.com/watch?v=SWJfwG556ZE</t>
+  </si>
+  <si>
+    <t>RLrePhZXQTM</t>
+  </si>
+  <si>
+    <t>Experiencing the Soul’s Love for God</t>
+  </si>
+  <si>
+    <t>https://www.youtube.com/watch?v=RLrePhZXQTM</t>
+  </si>
+  <si>
+    <t>2vvKo3Z5xbc</t>
+  </si>
+  <si>
+    <t>Discovering Your Unique Purpose</t>
+  </si>
+  <si>
+    <t>https://www.youtube.com/watch?v=2vvKo3Z5xbc</t>
+  </si>
+  <si>
+    <t>1PWwg-YR_fk</t>
+  </si>
+  <si>
+    <t>World Meditation Day 2025 Guided Meditation</t>
+  </si>
+  <si>
+    <t>https://www.youtube.com/watch?v=1PWwg-YR_fk</t>
+  </si>
+  <si>
+    <t>fLhjgozFAE0</t>
+  </si>
+  <si>
+    <t>The Power of Meditation and Inner Joy</t>
+  </si>
+  <si>
+    <t>https://www.youtube.com/watch?v=fLhjgozFAE0</t>
+  </si>
+  <si>
+    <t>W5nly71GVJA</t>
+  </si>
+  <si>
+    <t>Yogananda Says: “Love Gives Joy”</t>
+  </si>
+  <si>
+    <t>https://www.youtube.com/watch?v=W5nly71GVJA</t>
+  </si>
+  <si>
+    <t>F69o_9IMbmA</t>
+  </si>
+  <si>
+    <t>Cultivating Gratitude in Daily Life</t>
+  </si>
+  <si>
+    <t>https://www.youtube.com/watch?v=F69o_9IMbmA</t>
+  </si>
+  <si>
+    <t>EFjO6X53QDE</t>
+  </si>
+  <si>
+    <t>Turning Inspiration Into Spiritual Activity</t>
+  </si>
+  <si>
+    <t>https://www.youtube.com/watch?v=EFjO6X53QDE</t>
+  </si>
+  <si>
+    <t>_cCFQsBafes</t>
+  </si>
+  <si>
+    <t>Each Person’s Relationship With God Is Unique</t>
+  </si>
+  <si>
+    <t>https://www.youtube.com/watch?v=_cCFQsBafes</t>
+  </si>
+  <si>
+    <t>sk7hG34Xtk8</t>
+  </si>
+  <si>
+    <t>Why Yogananda Taught Scientific Techniques of Meditation</t>
+  </si>
+  <si>
+    <t>https://www.youtube.com/watch?v=sk7hG34Xtk8</t>
+  </si>
+  <si>
+    <t>znasct0LLCY</t>
+  </si>
+  <si>
+    <t>What Happens When We Recognize Our Divinity?</t>
+  </si>
+  <si>
+    <t>https://www.youtube.com/watch?v=znasct0LLCY</t>
+  </si>
+  <si>
+    <t>JUB2iBF8Fyo</t>
+  </si>
+  <si>
+    <t>Where Does the Soul Reside?</t>
+  </si>
+  <si>
+    <t>https://www.youtube.com/watch?v=JUB2iBF8Fyo</t>
+  </si>
+  <si>
+    <t>G12nyjdFBVU</t>
+  </si>
+  <si>
+    <t>Spirituality for the Modern World</t>
+  </si>
+  <si>
+    <t>https://www.youtube.com/watch?v=G12nyjdFBVU</t>
+  </si>
+  <si>
+    <t>rEfCpGy5L4g</t>
+  </si>
+  <si>
+    <t>Meditation Strengthens the Link Between You and God</t>
+  </si>
+  <si>
+    <t>https://www.youtube.com/watch?v=rEfCpGy5L4g</t>
+  </si>
+  <si>
+    <t>_nCo0tzX5ZU</t>
+  </si>
+  <si>
+    <t>Karma: The Golden Rule in Action</t>
+  </si>
+  <si>
+    <t>https://www.youtube.com/watch?v=_nCo0tzX5ZU</t>
+  </si>
+  <si>
+    <t>SDF2Um_P3sI</t>
+  </si>
+  <si>
+    <t>Most Inspiring Passage in “Autobiography of a Yogi”</t>
+  </si>
+  <si>
+    <t>https://www.youtube.com/watch?v=SDF2Um_P3sI</t>
+  </si>
+  <si>
+    <t>TQhrrTwMd8s</t>
+  </si>
+  <si>
+    <t>Never Get Discouraged — Motivation From the Bhagavad Gita</t>
+  </si>
+  <si>
+    <t>https://www.youtube.com/watch?v=TQhrrTwMd8s</t>
+  </si>
+  <si>
+    <t>x_bFHpKHWW0</t>
+  </si>
+  <si>
+    <t>The United Power of Prayer</t>
+  </si>
+  <si>
+    <t>https://www.youtube.com/watch?v=x_bFHpKHWW0</t>
+  </si>
+  <si>
+    <t>DrHtW269Y6c</t>
+  </si>
+  <si>
+    <t>The Value of Group Meditation</t>
+  </si>
+  <si>
+    <t>https://www.youtube.com/watch?v=DrHtW269Y6c</t>
+  </si>
+  <si>
+    <t>H8c2lj1ATko</t>
+  </si>
+  <si>
+    <t>The Surest Way to Coax God to Respond</t>
+  </si>
+  <si>
+    <t>https://www.youtube.com/watch?v=H8c2lj1ATko</t>
+  </si>
+  <si>
+    <t>RWSUCqf23-8</t>
+  </si>
+  <si>
+    <t>Finding Peace in Meditation</t>
+  </si>
+  <si>
+    <t>https://www.youtube.com/watch?v=RWSUCqf23-8</t>
+  </si>
+  <si>
+    <t>3xy2LbDj4E8</t>
+  </si>
+  <si>
+    <t>Putting God First</t>
+  </si>
+  <si>
+    <t>https://www.youtube.com/watch?v=3xy2LbDj4E8</t>
+  </si>
+  <si>
+    <t>RXXPq74kpWQ</t>
+  </si>
+  <si>
+    <t>Include God in Your Daily Life</t>
+  </si>
+  <si>
+    <t>https://www.youtube.com/watch?v=RXXPq74kpWQ</t>
+  </si>
+  <si>
+    <t>uh7nznN0S6Q</t>
+  </si>
+  <si>
+    <t>Thank You for Supporting Paramahansa Yogananda’s Work</t>
+  </si>
+  <si>
+    <t>https://www.youtube.com/watch?v=uh7nznN0S6Q</t>
+  </si>
+  <si>
+    <t>68YUK_oZBHY</t>
+  </si>
+  <si>
+    <t>Living a Joyful and Successful Life</t>
+  </si>
+  <si>
+    <t>https://www.youtube.com/watch?v=68YUK_oZBHY</t>
+  </si>
+  <si>
+    <t>Ow--o-3qLig</t>
+  </si>
+  <si>
+    <t>A Perfect Example of Balanced Living</t>
+  </si>
+  <si>
+    <t>https://www.youtube.com/watch?v=Ow--o-3qLig</t>
+  </si>
+  <si>
+    <t>B9LKEvpoR_U</t>
+  </si>
+  <si>
+    <t>Using Affirmations to Overcome Fear</t>
+  </si>
+  <si>
+    <t>https://www.youtube.com/watch?v=B9LKEvpoR_U</t>
+  </si>
+  <si>
+    <t>GZ2zgmN52WI</t>
+  </si>
+  <si>
+    <t>A Simple Technique to Overcome Fear</t>
+  </si>
+  <si>
+    <t>https://www.youtube.com/watch?v=GZ2zgmN52WI</t>
+  </si>
+  <si>
+    <t>515kr-xnHg4</t>
+  </si>
+  <si>
+    <t>Live Well Now</t>
+  </si>
+  <si>
+    <t>https://www.youtube.com/watch?v=515kr-xnHg4</t>
+  </si>
+  <si>
+    <t>df-KGIcn13s</t>
+  </si>
+  <si>
+    <t>Experience God Within Through Daily Meditation</t>
+  </si>
+  <si>
+    <t>https://www.youtube.com/watch?v=df-KGIcn13s</t>
+  </si>
+  <si>
+    <t>hflHtvzvaAQ</t>
+  </si>
+  <si>
+    <t>Attuning Ourselves to the Divine</t>
+  </si>
+  <si>
+    <t>https://www.youtube.com/watch?v=hflHtvzvaAQ</t>
+  </si>
+  <si>
+    <t>KggYIFs58Wk</t>
+  </si>
+  <si>
+    <t>How Do We Realize Our Divinity?</t>
+  </si>
+  <si>
+    <t>https://www.youtube.com/watch?v=KggYIFs58Wk</t>
+  </si>
+  <si>
+    <t>be3bGqNfmnw</t>
+  </si>
+  <si>
+    <t>Keep On Keeping On</t>
+  </si>
+  <si>
+    <t>https://www.youtube.com/watch?v=be3bGqNfmnw</t>
+  </si>
+  <si>
+    <t>ktuY0ry9vd4</t>
+  </si>
+  <si>
+    <t>Everyone Can Meditate</t>
+  </si>
+  <si>
+    <t>https://www.youtube.com/watch?v=ktuY0ry9vd4</t>
+  </si>
+  <si>
+    <t>4KihjUJmg00</t>
+  </si>
+  <si>
+    <t>Rise Above Fear of Failure</t>
+  </si>
+  <si>
+    <t>https://www.youtube.com/watch?v=4KihjUJmg00</t>
+  </si>
+  <si>
+    <t>9d_WmFF7O8M</t>
+  </si>
+  <si>
+    <t>God Is Already With Us</t>
+  </si>
+  <si>
+    <t>https://www.youtube.com/watch?v=9d_WmFF7O8M</t>
+  </si>
+  <si>
+    <t>tTjRVNRpQVA</t>
+  </si>
+  <si>
+    <t>Receiving Help Through Divine Communion</t>
+  </si>
+  <si>
+    <t>https://www.youtube.com/watch?v=tTjRVNRpQVA</t>
+  </si>
+  <si>
+    <t>CdUu9oPEI5o</t>
+  </si>
+  <si>
+    <t>Faith Is the Proof of Things Unseen</t>
+  </si>
+  <si>
+    <t>https://www.youtube.com/watch?v=CdUu9oPEI5o</t>
+  </si>
+  <si>
+    <t>LCAplcE1-J8</t>
+  </si>
+  <si>
+    <t>What Is Love?</t>
+  </si>
+  <si>
+    <t>https://www.youtube.com/watch?v=LCAplcE1-J8</t>
+  </si>
+  <si>
+    <t>8QVyZTtH-qU</t>
+  </si>
+  <si>
+    <t>God’s Aspect of Unconditional Love</t>
+  </si>
+  <si>
+    <t>https://www.youtube.com/watch?v=8QVyZTtH-qU</t>
+  </si>
+  <si>
+    <t>2qcrUA5b0k4</t>
+  </si>
+  <si>
+    <t>Yoga Brings Lasting Happiness</t>
+  </si>
+  <si>
+    <t>https://www.youtube.com/watch?v=2qcrUA5b0k4</t>
+  </si>
+  <si>
+    <t>oK-CzCWG9bs</t>
+  </si>
+  <si>
+    <t>Buddha’s Famous Answer to “What Are You?”</t>
+  </si>
+  <si>
+    <t>https://www.youtube.com/watch?v=oK-CzCWG9bs</t>
+  </si>
+  <si>
+    <t>AR2ErMaUXwQ</t>
+  </si>
+  <si>
+    <t>Stillness: Basic Principle of Meditation</t>
+  </si>
+  <si>
+    <t>https://www.youtube.com/watch?v=AR2ErMaUXwQ</t>
+  </si>
+  <si>
+    <t>0iMFjj0_xjQ</t>
+  </si>
+  <si>
+    <t>Achieving Constant Communion With God</t>
+  </si>
+  <si>
+    <t>https://www.youtube.com/watch?v=0iMFjj0_xjQ</t>
+  </si>
+  <si>
+    <t>zviwboz_WkQ</t>
+  </si>
+  <si>
+    <t>Change Your Life by Whispering to God</t>
+  </si>
+  <si>
+    <t>https://www.youtube.com/watch?v=zviwboz_WkQ</t>
+  </si>
+  <si>
+    <t>WcqLsn1HcKE</t>
+  </si>
+  <si>
+    <t>Change Creation With Will</t>
+  </si>
+  <si>
+    <t>https://www.youtube.com/watch?v=WcqLsn1HcKE</t>
+  </si>
+  <si>
+    <t>0rmJgGAeh0Q</t>
+  </si>
+  <si>
+    <t>The Joy of Loving Service</t>
+  </si>
+  <si>
+    <t>https://www.youtube.com/watch?v=0rmJgGAeh0Q</t>
+  </si>
+  <si>
+    <t>cbQP0H4zTE0</t>
+  </si>
+  <si>
+    <t>What Is God’s Love Like?</t>
+  </si>
+  <si>
+    <t>https://www.youtube.com/watch?v=cbQP0H4zTE0</t>
+  </si>
+  <si>
+    <t>C8LES0t0BOE</t>
+  </si>
+  <si>
+    <t>3 Ways To Feel God in Daily Life</t>
+  </si>
+  <si>
+    <t>https://www.youtube.com/watch?v=C8LES0t0BOE</t>
+  </si>
+  <si>
+    <t>6fGRQiTzMHY</t>
+  </si>
+  <si>
+    <t>Guided Affirmation on Living Fearlessly</t>
+  </si>
+  <si>
+    <t>https://www.youtube.com/watch?v=6fGRQiTzMHY</t>
+  </si>
+  <si>
+    <t>gNwW7EX3kIQ</t>
+  </si>
+  <si>
+    <t>Scientific Way to Cosmic Consciousness</t>
+  </si>
+  <si>
+    <t>https://www.youtube.com/watch?v=gNwW7EX3kIQ</t>
+  </si>
+  <si>
+    <t>2fH3XcIg3y8</t>
+  </si>
+  <si>
+    <t>Do Everything With Peace | Inspirational Quotes by Paramahansa Yogananda</t>
+  </si>
+  <si>
+    <t>https://www.youtube.com/watch?v=2fH3XcIg3y8</t>
+  </si>
+  <si>
+    <t>YZNczxMFT3g</t>
+  </si>
+  <si>
+    <t>Overcome Moods by Self-Analysis</t>
+  </si>
+  <si>
+    <t>https://www.youtube.com/watch?v=YZNczxMFT3g</t>
+  </si>
+  <si>
+    <t>-Y97cBOD_OA</t>
+  </si>
+  <si>
+    <t>Discover Higher Realities Within You</t>
+  </si>
+  <si>
+    <t>https://www.youtube.com/watch?v=-Y97cBOD_OA</t>
+  </si>
+  <si>
+    <t>WAU0CSx4OUA</t>
+  </si>
+  <si>
+    <t>Harnessing Divine Power</t>
+  </si>
+  <si>
+    <t>https://www.youtube.com/watch?v=WAU0CSx4OUA</t>
+  </si>
+  <si>
+    <t>VQrA0fC-saI</t>
+  </si>
+  <si>
+    <t>Quiet the Mind Through Forgiveness</t>
+  </si>
+  <si>
+    <t>https://www.youtube.com/watch?v=VQrA0fC-saI</t>
+  </si>
+  <si>
+    <t>-kwNgpLEwr0</t>
+  </si>
+  <si>
+    <t>Yogananda Said: God Is Already Yours</t>
+  </si>
+  <si>
+    <t>https://www.youtube.com/watch?v=-kwNgpLEwr0</t>
+  </si>
+  <si>
+    <t>mo09HXeLesI</t>
+  </si>
+  <si>
+    <t>A Story: The Power of Sincere Prayer</t>
+  </si>
+  <si>
+    <t>https://www.youtube.com/watch?v=mo09HXeLesI</t>
+  </si>
+  <si>
+    <t>aSbehuyZc2g</t>
+  </si>
+  <si>
+    <t>Divine Power of Materializing Our Thoughts</t>
+  </si>
+  <si>
+    <t>https://www.youtube.com/watch?v=aSbehuyZc2g</t>
+  </si>
+  <si>
+    <t>wDkD-YMTvwg</t>
+  </si>
+  <si>
+    <t>Meditation: From the Finite to the Infinite</t>
+  </si>
+  <si>
+    <t>https://www.youtube.com/watch?v=wDkD-YMTvwg</t>
+  </si>
+  <si>
+    <t>8GjMYstN1pc</t>
+  </si>
+  <si>
+    <t>"Behold, the Kingdom of God Is Within You" | Sri Mrinalini Mata</t>
+  </si>
+  <si>
+    <t>https://www.youtube.com/watch?v=8GjMYstN1pc</t>
+  </si>
+  <si>
+    <t>The Guru Is Not Limited by the Material World | Brother Bhaktananda</t>
+  </si>
+  <si>
+    <t>English|God You Can Relate|Inspirational Inspirational Clips||</t>
+  </si>
+  <si>
+    <t>English|Your Real Nature Joy|Inspirational Inspirational Clips||</t>
+  </si>
+  <si>
+    <t>English|Prayer Intimate Conversation God|Inspirational Inspirational Clips||</t>
+  </si>
+  <si>
+    <t>English|God Loves Are|Inspirational Inspirational Clips||</t>
+  </si>
+  <si>
+    <t>English|Trying Personal Change|Inspirational Inspirational Clips||</t>
+  </si>
+  <si>
+    <t>English|Discover Joy Soul 2026 SRF|Inspirational Inspirational Clips||</t>
+  </si>
+  <si>
+    <t>English|Give You Soul Call Guided|Inspirational Inspirational Clips||</t>
+  </si>
+  <si>
+    <t>English|Overcoming Fear Divine Vibrations Brother|Inspirational Inspirational Clips||</t>
+  </si>
+  <si>
+    <t>English|Use Your Initiative Find Lasting|Inspirational Inspirational Clips||</t>
+  </si>
+  <si>
+    <t>English|Gratitude Brings Happiness|Inspirational Inspirational Clips||</t>
+  </si>
+  <si>
+    <t>English|Learn Love God Through Yoga|Inspirational Inspirational Clips||</t>
+  </si>
+  <si>
+    <t>English|Guided Visualization EverExpanding Love Paramahansa|Inspirational Inspirational Clips||</t>
+  </si>
+  <si>
+    <t>English|You Will Realize God|Inspirational Inspirational Clips||</t>
+  </si>
+  <si>
+    <t>English|God Will Answer You Yoganandas|Inspirational Inspirational Clips||</t>
+  </si>
+  <si>
+    <t>English|Keep More Your Consciousness Within|Inspirational Inspirational Clips||</t>
+  </si>
+  <si>
+    <t>English|Need Guide Spiritual Path|Inspirational Inspirational Clips||</t>
+  </si>
+  <si>
+    <t>English|Eternal Life God Affirmation Paramahansa|Inspirational Inspirational Clips||</t>
+  </si>
+  <si>
+    <t>English|Radiate Your Love Others|Inspirational Inspirational Clips||</t>
+  </si>
+  <si>
+    <t>English|Stay Close God|Inspirational Inspirational Clips||</t>
+  </si>
+  <si>
+    <t>English|Yoganandas Kriya Yoga Harmonizes Our|Inspirational Inspirational Clips||</t>
+  </si>
+  <si>
+    <t>English|Highest Joy Life|Inspirational Inspirational Clips||</t>
+  </si>
+  <si>
+    <t>English|Supreme Gift Yoganandas HowtoLive Wisdom|Inspirational Inspirational Clips||</t>
+  </si>
+  <si>
+    <t>English|You Can Find Peace New|Inspirational Inspirational Clips||</t>
+  </si>
+  <si>
+    <t>English|How Improve World Live|Inspirational Inspirational Clips||</t>
+  </si>
+  <si>
+    <t>English|Tough Experiences Bring Out Our|Inspirational Inspirational Clips||</t>
+  </si>
+  <si>
+    <t>English|What Selfrealization|Inspirational Inspirational Clips||</t>
+  </si>
+  <si>
+    <t>English|Cosmic Sphere Love Affirmation Paramahansa|Inspirational Inspirational Clips||</t>
+  </si>
+  <si>
+    <t>English|Meditation Awakens Divine Realization|Inspirational Inspirational Clips||</t>
+  </si>
+  <si>
+    <t>English|Can All Have Divine Joy|Inspirational Inspirational Clips||</t>
+  </si>
+  <si>
+    <t>English|Our Relationship God Yoganandas HowtoLive|Inspirational Inspirational Clips||</t>
+  </si>
+  <si>
+    <t>English|Power Accomplish Yoganandas HowtoLive Wisdom|Inspirational Inspirational Clips||</t>
+  </si>
+  <si>
+    <t>English|You Are Unique Yoganandas HowtoLive|Inspirational Inspirational Clips||</t>
+  </si>
+  <si>
+    <t>English|Fire Purpose Yoganandas HowtoLive Wisdom|Inspirational Inspirational Clips||</t>
+  </si>
+  <si>
+    <t>English|Creating Dynamic Will Power Yoganandas|Inspirational Inspirational Clips||</t>
+  </si>
+  <si>
+    <t>English|Experiencing Souls Love God|Inspirational Inspirational Clips||</t>
+  </si>
+  <si>
+    <t>English|Discovering Your Unique Purpose|Inspirational Inspirational Clips||</t>
+  </si>
+  <si>
+    <t>English|World Meditation Day 2025 Guided|Inspirational Inspirational Clips||</t>
+  </si>
+  <si>
+    <t>English|Power Meditation Inner Joy|Inspirational Inspirational Clips||</t>
+  </si>
+  <si>
+    <t>English|Yogananda Says Love Gives Joy|Inspirational Inspirational Clips||</t>
+  </si>
+  <si>
+    <t>English|Cultivating Gratitude Daily Life|Inspirational Inspirational Clips||</t>
+  </si>
+  <si>
+    <t>English|Turning Inspiration Into Spiritual Activity|Inspirational Inspirational Clips||</t>
+  </si>
+  <si>
+    <t>English|Each Persons Relationship God Unique|Inspirational Inspirational Clips||</t>
+  </si>
+  <si>
+    <t>English|Why Yogananda Taught Scientific Techniques|Inspirational Inspirational Clips||</t>
+  </si>
+  <si>
+    <t>English|What Happens When Recognize Our|Inspirational Inspirational Clips||</t>
+  </si>
+  <si>
+    <t>English|Where Does Soul Reside|Inspirational Inspirational Clips||</t>
+  </si>
+  <si>
+    <t>English|Spirituality Modern World|Inspirational Inspirational Clips||</t>
+  </si>
+  <si>
+    <t>English|Meditation Strengthens Link Between You|Inspirational Inspirational Clips||</t>
+  </si>
+  <si>
+    <t>English|Karma Golden Rule Action|Inspirational Inspirational Clips||</t>
+  </si>
+  <si>
+    <t>English|Most Inspiring Passage Autobiography Yogi|Inspirational Inspirational Clips||</t>
+  </si>
+  <si>
+    <t>English|Never Get Discouraged Motivation From|Inspirational Inspirational Clips||</t>
+  </si>
+  <si>
+    <t>English|United Power Prayer|Inspirational Inspirational Clips||</t>
+  </si>
+  <si>
+    <t>English|Value Group Meditation|Inspirational Inspirational Clips||</t>
+  </si>
+  <si>
+    <t>English|Surest Way Coax God Respond|Inspirational Inspirational Clips||</t>
+  </si>
+  <si>
+    <t>English|Finding Peace Meditation|Inspirational Inspirational Clips||</t>
+  </si>
+  <si>
+    <t>English|Putting God First|Inspirational Inspirational Clips||</t>
+  </si>
+  <si>
+    <t>English|Include God Your Daily Life|Inspirational Inspirational Clips||</t>
+  </si>
+  <si>
+    <t>English|Thank You Supporting Paramahansa Yoganandas|Inspirational Inspirational Clips||</t>
+  </si>
+  <si>
+    <t>English|Living Joyful Successful Life|Inspirational Inspirational Clips||</t>
+  </si>
+  <si>
+    <t>English|Perfect Example Balanced Living|Inspirational Inspirational Clips||</t>
+  </si>
+  <si>
+    <t>English|Using Affirmations Overcome Fear|Inspirational Inspirational Clips||</t>
+  </si>
+  <si>
+    <t>English|Simple Technique Overcome Fear|Inspirational Inspirational Clips||</t>
+  </si>
+  <si>
+    <t>English|Live Well Now|Inspirational Inspirational Clips||</t>
+  </si>
+  <si>
+    <t>English|Experience God Within Through Daily|Inspirational Inspirational Clips||</t>
+  </si>
+  <si>
+    <t>English|Attuning Ourselves Divine|Inspirational Inspirational Clips||</t>
+  </si>
+  <si>
+    <t>English|How Realize Our Divinity|Inspirational Inspirational Clips||</t>
+  </si>
+  <si>
+    <t>English|Keep Keeping|Inspirational Inspirational Clips||</t>
+  </si>
+  <si>
+    <t>English|Everyone Can Meditate|Inspirational Inspirational Clips||</t>
+  </si>
+  <si>
+    <t>English|Rise Above Fear Failure|Inspirational Inspirational Clips||</t>
+  </si>
+  <si>
+    <t>English|God Already|Inspirational Inspirational Clips||</t>
+  </si>
+  <si>
+    <t>English|Receiving Help Through Divine Communion|Inspirational Inspirational Clips||</t>
+  </si>
+  <si>
+    <t>English|Faith Proof Things Unseen|Inspirational Inspirational Clips||</t>
+  </si>
+  <si>
+    <t>English|What Love|Inspirational Inspirational Clips||</t>
+  </si>
+  <si>
+    <t>English|Gods Aspect Unconditional Love|Inspirational Inspirational Clips||</t>
+  </si>
+  <si>
+    <t>English|Yoga Brings Lasting Happiness|Inspirational Inspirational Clips||</t>
+  </si>
+  <si>
+    <t>English|Buddhas Famous Answer What Are|Inspirational Inspirational Clips||</t>
+  </si>
+  <si>
+    <t>English|Stillness Basic Principle Meditation|Inspirational Inspirational Clips||</t>
+  </si>
+  <si>
+    <t>English|Achieving Constant Communion God|Inspirational Inspirational Clips||</t>
+  </si>
+  <si>
+    <t>English|Change Your Life Whispering God|Inspirational Inspirational Clips||</t>
+  </si>
+  <si>
+    <t>English|Spiritual Photosynthesis Converting Gods Grace|Inspirational Inspirational Clips||</t>
+  </si>
+  <si>
+    <t>English|Change Creation Will|Inspirational Inspirational Clips||</t>
+  </si>
+  <si>
+    <t>English|Joy Loving Service|Inspirational Inspirational Clips||</t>
+  </si>
+  <si>
+    <t>English|What Gods Love Like|Inspirational Inspirational Clips||</t>
+  </si>
+  <si>
+    <t>English|Ways Feel God Daily Life|Inspirational Inspirational Clips||</t>
+  </si>
+  <si>
+    <t>English|What Kriya Yoga Brother Chidananda|Inspirational Inspirational Clips||</t>
+  </si>
+  <si>
+    <t>English|Guided Affirmation Living Fearlessly|Inspirational Inspirational Clips||</t>
+  </si>
+  <si>
+    <t>English|Scientific Way Cosmic Consciousness|Inspirational Inspirational Clips||</t>
+  </si>
+  <si>
+    <t>English|Everything Peace Inspirational Quotes Paramahansa|Inspirational Inspirational Clips||</t>
+  </si>
+  <si>
+    <t>English|Overcome Moods SelfAnalysis|Inspirational Inspirational Clips||</t>
+  </si>
+  <si>
+    <t>English|Discover Higher Realities Within You|Inspirational Inspirational Clips||</t>
+  </si>
+  <si>
+    <t>English|Harnessing Divine Power|Inspirational Inspirational Clips||</t>
+  </si>
+  <si>
+    <t>English|Quiet Mind Through Forgiveness|Inspirational Inspirational Clips||</t>
+  </si>
+  <si>
+    <t>English|Yogananda Said God Already Yours|Inspirational Inspirational Clips||</t>
+  </si>
+  <si>
+    <t>English|Story Power Sincere Prayer|Inspirational Inspirational Clips||</t>
+  </si>
+  <si>
+    <t>English|Divine Power Materializing Our Thoughts|Inspirational Inspirational Clips||</t>
+  </si>
+  <si>
+    <t>English|Meditation From Finite Infinite|Inspirational Inspirational Clips||</t>
+  </si>
+  <si>
+    <t>English|Awakening Divine Qualities Through Kriya|Inspirational Inspirational Clips||</t>
+  </si>
+  <si>
+    <t>English|Flooding Our Consciousness Divine Enthusiasm|Inspirational Inspirational Clips||</t>
+  </si>
+  <si>
+    <t>English|Drawing Divine Energy From Our|Inspirational Inspirational Clips||</t>
+  </si>
+  <si>
+    <t>English|Finding Complete Fulfillment God Sri|Inspirational Inspirational Clips||</t>
+  </si>
+  <si>
+    <t>English|Karma Samskaras Sri Mrinalini Mata|Inspirational Inspirational Clips||</t>
+  </si>
+  <si>
+    <t>English|Practicing Presence God Change Your|Inspirational Inspirational Clips||</t>
+  </si>
+  <si>
+    <t>English|How Know You Are Making|Inspirational Inspirational Clips||</t>
+  </si>
+  <si>
+    <t>English|Kriya Yoga Science Godrealization Sri|Inspirational Inspirational Clips||</t>
+  </si>
+  <si>
+    <t>English|Holy Ghost Aum Vibration Sri|Inspirational Inspirational Clips||</t>
+  </si>
+  <si>
+    <t>English|Beginning Paramahansa Yoganandas Mission Sri|Inspirational Inspirational Clips||</t>
+  </si>
+  <si>
+    <t>English|Behold Kingdom God Within You|Inspirational Inspirational Clips||</t>
+  </si>
+  <si>
+    <t>English|When Only Dream Poem Paramahansa|Inspirational Inspirational Clips||</t>
+  </si>
+  <si>
+    <t>English|Opening Gods Love Meditation Part|Inspirational Inspirational Clips||</t>
+  </si>
+  <si>
+    <t>English|Developing Unconquerable Will Part|Inspirational Inspirational Clips||</t>
+  </si>
+  <si>
+    <t>English|Inspiration Spiritualizing Family Life Sri|Inspirational Inspirational Clips||</t>
+  </si>
+  <si>
+    <t>English|Paramahansa Yoganandas Great Samadhi 1948|Inspirational Inspirational Clips||</t>
+  </si>
+  <si>
+    <t>English|Paramahansa Yogananda Teachings Will Guru|Inspirational Inspirational Clips||</t>
+  </si>
+  <si>
+    <t>English|Spiritual Benefits Simplicity Brother Bhaktananda|Inspirational Inspirational Clips||</t>
+  </si>
+  <si>
+    <t>English|Paramahansa Yoganandas 125th Birthday Special|Inspirational Inspirational Clips||</t>
+  </si>
+  <si>
+    <t>English|Understanding Karma Brother Anandamoy|Inspirational Inspirational Clips||</t>
+  </si>
+  <si>
+    <t>English|God Talks Arjuna Hindi Translation|Inspirational Inspirational Clips||</t>
+  </si>
+  <si>
+    <t>English|Overcoming Negativity Todays World|Inspirational Inspirational Clips||</t>
+  </si>
+  <si>
+    <t>English|How Spiritualize Your Actions Brother|Inspirational Inspirational Clips||</t>
+  </si>
+  <si>
+    <t>English|Spirit Pilgrimage Centennial Celebratory Procession|Inspirational Inspirational Clips||</t>
+  </si>
+  <si>
+    <t>English|Promising Vision Future Yoganandas Aims|Inspirational Inspirational Clips||</t>
+  </si>
+  <si>
+    <t>English|Practice Yoganandas Healing Technique SRF|Inspirational Inspirational Clips||</t>
+  </si>
+  <si>
+    <t>English|Paramahansa Yoganandas Concept Freedom Brother|Inspirational Inspirational Clips||</t>
+  </si>
+  <si>
+    <t>English|Guru Stirs Divine Longing Sri|Inspirational Inspirational Clips||</t>
+  </si>
+  <si>
+    <t>English|Guru Not Just Teacher Brother|Inspirational Inspirational Clips||</t>
+  </si>
+  <si>
+    <t>English|Experiencing Unconditional Love God Sri|Inspirational Inspirational Clips||</t>
+  </si>
+  <si>
+    <t>English|Practice Kriya Yoga Every Day|Inspirational Inspirational Clips||</t>
+  </si>
+  <si>
+    <t>English|Paramahansa Yoganandas Advice About World|Inspirational Inspirational Clips||</t>
+  </si>
+  <si>
+    <t>English|Message Sacred Holiday Observances Brother|Inspirational Inspirational Clips||</t>
+  </si>
+  <si>
+    <t>English|Yoganandas SuperArt Living Benefits Scheduling|Inspirational Inspirational Clips||</t>
+  </si>
+  <si>
+    <t>English|Choosing Conqueror That Remedy Brother|Inspirational Inspirational Clips||</t>
+  </si>
+  <si>
+    <t>English|Embrace Divine Mother Brother Chidananda|Inspirational Inspirational Clips||</t>
+  </si>
+  <si>
+    <t>English|Scripture Love|Inspirational Inspirational Clips||</t>
+  </si>
+  <si>
+    <t>English|How Can Prayers Help Others|Inspirational Inspirational Clips||</t>
+  </si>
+  <si>
+    <t>English|Castled Gods Presence Brother Chidananda|Inspirational Inspirational Clips||</t>
+  </si>
+  <si>
+    <t>English|Pranayama Technique Given Paramahansa Yogananda|Inspirational Inspirational Clips||</t>
+  </si>
+  <si>
+    <t>English|Neuroplasticity Yoga Science Meditation Brother|Inspirational Inspirational Clips||</t>
+  </si>
+  <si>
+    <t>English|Christ Consciousness Goal Each One|Inspirational Inspirational Clips||</t>
+  </si>
+  <si>
+    <t>English|Overcoming Soul Fog Through Kriya|Inspirational Inspirational Clips||</t>
+  </si>
+  <si>
+    <t>English|Awakening Spine Through Kriya Yoga|Inspirational Inspirational Clips||</t>
+  </si>
+  <si>
+    <t>English|Guru Not Limited Material World|Inspirational Inspirational Clips||</t>
+  </si>
+  <si>
+    <t>English|True Guru Guides From Experience|Inspirational Inspirational Clips||</t>
   </si>
 </sst>
 </file>
@@ -10121,7 +11387,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{EE52D9B7-0D33-6C4B-ABD2-124A93043E14}">
-  <dimension ref="A1:D1015"/>
+  <dimension ref="A1:D1159"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="44" bestFit="1" customWidth="1"/>
@@ -24337,6 +25603,2022 @@
         <v>3235</v>
       </c>
     </row>
+    <row r="1016" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A1016" t="s">
+        <v>3236</v>
+      </c>
+      <c r="B1016" t="s">
+        <v>3237</v>
+      </c>
+      <c r="C1016" t="s">
+        <v>3238</v>
+      </c>
+      <c r="D1016" t="s">
+        <v>3517</v>
+      </c>
+    </row>
+    <row r="1017" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A1017" t="s">
+        <v>3239</v>
+      </c>
+      <c r="B1017" t="s">
+        <v>3240</v>
+      </c>
+      <c r="C1017" t="s">
+        <v>3241</v>
+      </c>
+      <c r="D1017" t="s">
+        <v>3518</v>
+      </c>
+    </row>
+    <row r="1018" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A1018" t="s">
+        <v>3242</v>
+      </c>
+      <c r="B1018" t="s">
+        <v>3243</v>
+      </c>
+      <c r="C1018" t="s">
+        <v>3244</v>
+      </c>
+      <c r="D1018" t="s">
+        <v>3519</v>
+      </c>
+    </row>
+    <row r="1019" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A1019" t="s">
+        <v>3245</v>
+      </c>
+      <c r="B1019" t="s">
+        <v>3246</v>
+      </c>
+      <c r="C1019" t="s">
+        <v>3247</v>
+      </c>
+      <c r="D1019" t="s">
+        <v>3520</v>
+      </c>
+    </row>
+    <row r="1020" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A1020" t="s">
+        <v>3248</v>
+      </c>
+      <c r="B1020" t="s">
+        <v>3249</v>
+      </c>
+      <c r="C1020" t="s">
+        <v>3250</v>
+      </c>
+      <c r="D1020" t="s">
+        <v>3521</v>
+      </c>
+    </row>
+    <row r="1021" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A1021" t="s">
+        <v>3251</v>
+      </c>
+      <c r="B1021" t="s">
+        <v>3252</v>
+      </c>
+      <c r="C1021" t="s">
+        <v>3253</v>
+      </c>
+      <c r="D1021" t="s">
+        <v>3522</v>
+      </c>
+    </row>
+    <row r="1022" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A1022" t="s">
+        <v>3254</v>
+      </c>
+      <c r="B1022" t="s">
+        <v>3255</v>
+      </c>
+      <c r="C1022" t="s">
+        <v>3256</v>
+      </c>
+      <c r="D1022" t="s">
+        <v>3523</v>
+      </c>
+    </row>
+    <row r="1023" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A1023" t="s">
+        <v>3257</v>
+      </c>
+      <c r="B1023" t="s">
+        <v>2187</v>
+      </c>
+      <c r="C1023" t="s">
+        <v>2188</v>
+      </c>
+      <c r="D1023" t="s">
+        <v>3524</v>
+      </c>
+    </row>
+    <row r="1024" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A1024" t="s">
+        <v>3258</v>
+      </c>
+      <c r="B1024" t="s">
+        <v>3259</v>
+      </c>
+      <c r="C1024" t="s">
+        <v>3260</v>
+      </c>
+      <c r="D1024" t="s">
+        <v>3525</v>
+      </c>
+    </row>
+    <row r="1025" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A1025" t="s">
+        <v>3261</v>
+      </c>
+      <c r="B1025" t="s">
+        <v>3262</v>
+      </c>
+      <c r="C1025" t="s">
+        <v>3263</v>
+      </c>
+      <c r="D1025" t="s">
+        <v>3526</v>
+      </c>
+    </row>
+    <row r="1026" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A1026" t="s">
+        <v>3264</v>
+      </c>
+      <c r="B1026" t="s">
+        <v>3265</v>
+      </c>
+      <c r="C1026" t="s">
+        <v>3266</v>
+      </c>
+      <c r="D1026" t="s">
+        <v>3527</v>
+      </c>
+    </row>
+    <row r="1027" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A1027" t="s">
+        <v>3267</v>
+      </c>
+      <c r="B1027" t="s">
+        <v>3268</v>
+      </c>
+      <c r="C1027" t="s">
+        <v>3269</v>
+      </c>
+      <c r="D1027" t="s">
+        <v>3528</v>
+      </c>
+    </row>
+    <row r="1028" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A1028" t="s">
+        <v>3270</v>
+      </c>
+      <c r="B1028" t="s">
+        <v>3271</v>
+      </c>
+      <c r="C1028" t="s">
+        <v>3272</v>
+      </c>
+      <c r="D1028" t="s">
+        <v>3529</v>
+      </c>
+    </row>
+    <row r="1029" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A1029" t="s">
+        <v>3273</v>
+      </c>
+      <c r="B1029" t="s">
+        <v>3274</v>
+      </c>
+      <c r="C1029" t="s">
+        <v>3275</v>
+      </c>
+      <c r="D1029" t="s">
+        <v>3530</v>
+      </c>
+    </row>
+    <row r="1030" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A1030" t="s">
+        <v>3276</v>
+      </c>
+      <c r="B1030" t="s">
+        <v>3277</v>
+      </c>
+      <c r="C1030" t="s">
+        <v>3278</v>
+      </c>
+      <c r="D1030" t="s">
+        <v>3531</v>
+      </c>
+    </row>
+    <row r="1031" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A1031" t="s">
+        <v>3279</v>
+      </c>
+      <c r="B1031" t="s">
+        <v>3280</v>
+      </c>
+      <c r="C1031" t="s">
+        <v>3281</v>
+      </c>
+      <c r="D1031" t="s">
+        <v>3532</v>
+      </c>
+    </row>
+    <row r="1032" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A1032" t="s">
+        <v>3282</v>
+      </c>
+      <c r="B1032" t="s">
+        <v>3283</v>
+      </c>
+      <c r="C1032" t="s">
+        <v>3284</v>
+      </c>
+      <c r="D1032" t="s">
+        <v>3533</v>
+      </c>
+    </row>
+    <row r="1033" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A1033" t="s">
+        <v>3285</v>
+      </c>
+      <c r="B1033" t="s">
+        <v>3286</v>
+      </c>
+      <c r="C1033" t="s">
+        <v>3287</v>
+      </c>
+      <c r="D1033" t="s">
+        <v>3534</v>
+      </c>
+    </row>
+    <row r="1034" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A1034" t="s">
+        <v>3288</v>
+      </c>
+      <c r="B1034" t="s">
+        <v>3289</v>
+      </c>
+      <c r="C1034" t="s">
+        <v>3290</v>
+      </c>
+      <c r="D1034" t="s">
+        <v>3535</v>
+      </c>
+    </row>
+    <row r="1035" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A1035" t="s">
+        <v>3291</v>
+      </c>
+      <c r="B1035" t="s">
+        <v>3292</v>
+      </c>
+      <c r="C1035" t="s">
+        <v>3293</v>
+      </c>
+      <c r="D1035" t="s">
+        <v>3536</v>
+      </c>
+    </row>
+    <row r="1036" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A1036" t="s">
+        <v>3294</v>
+      </c>
+      <c r="B1036" t="s">
+        <v>3295</v>
+      </c>
+      <c r="C1036" t="s">
+        <v>3296</v>
+      </c>
+      <c r="D1036" t="s">
+        <v>3537</v>
+      </c>
+    </row>
+    <row r="1037" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A1037" t="s">
+        <v>3297</v>
+      </c>
+      <c r="B1037" t="s">
+        <v>3298</v>
+      </c>
+      <c r="C1037" t="s">
+        <v>3299</v>
+      </c>
+      <c r="D1037" t="s">
+        <v>3538</v>
+      </c>
+    </row>
+    <row r="1038" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A1038" t="s">
+        <v>3300</v>
+      </c>
+      <c r="B1038" t="s">
+        <v>3301</v>
+      </c>
+      <c r="C1038" t="s">
+        <v>3302</v>
+      </c>
+      <c r="D1038" t="s">
+        <v>3539</v>
+      </c>
+    </row>
+    <row r="1039" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A1039" t="s">
+        <v>3303</v>
+      </c>
+      <c r="B1039" t="s">
+        <v>3304</v>
+      </c>
+      <c r="C1039" t="s">
+        <v>3305</v>
+      </c>
+      <c r="D1039" t="s">
+        <v>3540</v>
+      </c>
+    </row>
+    <row r="1040" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A1040" t="s">
+        <v>3306</v>
+      </c>
+      <c r="B1040" t="s">
+        <v>3307</v>
+      </c>
+      <c r="C1040" t="s">
+        <v>3308</v>
+      </c>
+      <c r="D1040" t="s">
+        <v>3541</v>
+      </c>
+    </row>
+    <row r="1041" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A1041" t="s">
+        <v>3309</v>
+      </c>
+      <c r="B1041" t="s">
+        <v>3310</v>
+      </c>
+      <c r="C1041" t="s">
+        <v>3311</v>
+      </c>
+      <c r="D1041" t="s">
+        <v>3542</v>
+      </c>
+    </row>
+    <row r="1042" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A1042" t="s">
+        <v>3312</v>
+      </c>
+      <c r="B1042" t="s">
+        <v>3313</v>
+      </c>
+      <c r="C1042" t="s">
+        <v>3314</v>
+      </c>
+      <c r="D1042" t="s">
+        <v>3543</v>
+      </c>
+    </row>
+    <row r="1043" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A1043" t="s">
+        <v>3315</v>
+      </c>
+      <c r="B1043" t="s">
+        <v>3316</v>
+      </c>
+      <c r="C1043" t="s">
+        <v>3317</v>
+      </c>
+      <c r="D1043" t="s">
+        <v>3544</v>
+      </c>
+    </row>
+    <row r="1044" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A1044" t="s">
+        <v>3318</v>
+      </c>
+      <c r="B1044" t="s">
+        <v>3319</v>
+      </c>
+      <c r="C1044" t="s">
+        <v>3320</v>
+      </c>
+      <c r="D1044" t="s">
+        <v>3545</v>
+      </c>
+    </row>
+    <row r="1045" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A1045" t="s">
+        <v>3321</v>
+      </c>
+      <c r="B1045" t="s">
+        <v>3322</v>
+      </c>
+      <c r="C1045" t="s">
+        <v>3323</v>
+      </c>
+      <c r="D1045" t="s">
+        <v>3546</v>
+      </c>
+    </row>
+    <row r="1046" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A1046" t="s">
+        <v>3324</v>
+      </c>
+      <c r="B1046" t="s">
+        <v>3325</v>
+      </c>
+      <c r="C1046" t="s">
+        <v>3326</v>
+      </c>
+      <c r="D1046" t="s">
+        <v>3547</v>
+      </c>
+    </row>
+    <row r="1047" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A1047" t="s">
+        <v>3327</v>
+      </c>
+      <c r="B1047" t="s">
+        <v>3328</v>
+      </c>
+      <c r="C1047" t="s">
+        <v>3329</v>
+      </c>
+      <c r="D1047" t="s">
+        <v>3548</v>
+      </c>
+    </row>
+    <row r="1048" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A1048" t="s">
+        <v>3330</v>
+      </c>
+      <c r="B1048" t="s">
+        <v>3331</v>
+      </c>
+      <c r="C1048" t="s">
+        <v>3332</v>
+      </c>
+      <c r="D1048" t="s">
+        <v>3549</v>
+      </c>
+    </row>
+    <row r="1049" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A1049" t="s">
+        <v>3333</v>
+      </c>
+      <c r="B1049" t="s">
+        <v>3334</v>
+      </c>
+      <c r="C1049" t="s">
+        <v>3335</v>
+      </c>
+      <c r="D1049" t="s">
+        <v>3550</v>
+      </c>
+    </row>
+    <row r="1050" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A1050" t="s">
+        <v>3336</v>
+      </c>
+      <c r="B1050" t="s">
+        <v>3337</v>
+      </c>
+      <c r="C1050" t="s">
+        <v>3338</v>
+      </c>
+      <c r="D1050" t="s">
+        <v>3551</v>
+      </c>
+    </row>
+    <row r="1051" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A1051" t="s">
+        <v>3339</v>
+      </c>
+      <c r="B1051" t="s">
+        <v>3340</v>
+      </c>
+      <c r="C1051" t="s">
+        <v>3341</v>
+      </c>
+      <c r="D1051" t="s">
+        <v>3552</v>
+      </c>
+    </row>
+    <row r="1052" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A1052" t="s">
+        <v>3342</v>
+      </c>
+      <c r="B1052" t="s">
+        <v>3343</v>
+      </c>
+      <c r="C1052" t="s">
+        <v>3344</v>
+      </c>
+      <c r="D1052" t="s">
+        <v>3553</v>
+      </c>
+    </row>
+    <row r="1053" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A1053" t="s">
+        <v>3345</v>
+      </c>
+      <c r="B1053" t="s">
+        <v>3346</v>
+      </c>
+      <c r="C1053" t="s">
+        <v>3347</v>
+      </c>
+      <c r="D1053" t="s">
+        <v>3554</v>
+      </c>
+    </row>
+    <row r="1054" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A1054" t="s">
+        <v>3348</v>
+      </c>
+      <c r="B1054" t="s">
+        <v>3349</v>
+      </c>
+      <c r="C1054" t="s">
+        <v>3350</v>
+      </c>
+      <c r="D1054" t="s">
+        <v>3555</v>
+      </c>
+    </row>
+    <row r="1055" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A1055" t="s">
+        <v>3351</v>
+      </c>
+      <c r="B1055" t="s">
+        <v>3352</v>
+      </c>
+      <c r="C1055" t="s">
+        <v>3353</v>
+      </c>
+      <c r="D1055" t="s">
+        <v>3556</v>
+      </c>
+    </row>
+    <row r="1056" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A1056" t="s">
+        <v>3354</v>
+      </c>
+      <c r="B1056" t="s">
+        <v>3355</v>
+      </c>
+      <c r="C1056" t="s">
+        <v>3356</v>
+      </c>
+      <c r="D1056" t="s">
+        <v>3557</v>
+      </c>
+    </row>
+    <row r="1057" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A1057" t="s">
+        <v>3357</v>
+      </c>
+      <c r="B1057" t="s">
+        <v>3358</v>
+      </c>
+      <c r="C1057" t="s">
+        <v>3359</v>
+      </c>
+      <c r="D1057" t="s">
+        <v>3558</v>
+      </c>
+    </row>
+    <row r="1058" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A1058" t="s">
+        <v>3360</v>
+      </c>
+      <c r="B1058" t="s">
+        <v>3361</v>
+      </c>
+      <c r="C1058" t="s">
+        <v>3362</v>
+      </c>
+      <c r="D1058" t="s">
+        <v>3559</v>
+      </c>
+    </row>
+    <row r="1059" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A1059" t="s">
+        <v>3363</v>
+      </c>
+      <c r="B1059" t="s">
+        <v>3364</v>
+      </c>
+      <c r="C1059" t="s">
+        <v>3365</v>
+      </c>
+      <c r="D1059" t="s">
+        <v>3560</v>
+      </c>
+    </row>
+    <row r="1060" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A1060" t="s">
+        <v>3366</v>
+      </c>
+      <c r="B1060" t="s">
+        <v>3367</v>
+      </c>
+      <c r="C1060" t="s">
+        <v>3368</v>
+      </c>
+      <c r="D1060" t="s">
+        <v>3561</v>
+      </c>
+    </row>
+    <row r="1061" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A1061" t="s">
+        <v>3369</v>
+      </c>
+      <c r="B1061" t="s">
+        <v>3370</v>
+      </c>
+      <c r="C1061" t="s">
+        <v>3371</v>
+      </c>
+      <c r="D1061" t="s">
+        <v>3562</v>
+      </c>
+    </row>
+    <row r="1062" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A1062" t="s">
+        <v>3372</v>
+      </c>
+      <c r="B1062" t="s">
+        <v>3373</v>
+      </c>
+      <c r="C1062" t="s">
+        <v>3374</v>
+      </c>
+      <c r="D1062" t="s">
+        <v>3563</v>
+      </c>
+    </row>
+    <row r="1063" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A1063" t="s">
+        <v>3375</v>
+      </c>
+      <c r="B1063" t="s">
+        <v>3376</v>
+      </c>
+      <c r="C1063" t="s">
+        <v>3377</v>
+      </c>
+      <c r="D1063" t="s">
+        <v>3564</v>
+      </c>
+    </row>
+    <row r="1064" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A1064" t="s">
+        <v>3378</v>
+      </c>
+      <c r="B1064" t="s">
+        <v>3379</v>
+      </c>
+      <c r="C1064" t="s">
+        <v>3380</v>
+      </c>
+      <c r="D1064" t="s">
+        <v>3565</v>
+      </c>
+    </row>
+    <row r="1065" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A1065" t="s">
+        <v>3381</v>
+      </c>
+      <c r="B1065" t="s">
+        <v>3382</v>
+      </c>
+      <c r="C1065" t="s">
+        <v>3383</v>
+      </c>
+      <c r="D1065" t="s">
+        <v>3566</v>
+      </c>
+    </row>
+    <row r="1066" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A1066" t="s">
+        <v>3384</v>
+      </c>
+      <c r="B1066" t="s">
+        <v>3385</v>
+      </c>
+      <c r="C1066" t="s">
+        <v>3386</v>
+      </c>
+      <c r="D1066" t="s">
+        <v>3567</v>
+      </c>
+    </row>
+    <row r="1067" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A1067" t="s">
+        <v>3387</v>
+      </c>
+      <c r="B1067" t="s">
+        <v>3388</v>
+      </c>
+      <c r="C1067" t="s">
+        <v>3389</v>
+      </c>
+      <c r="D1067" t="s">
+        <v>3568</v>
+      </c>
+    </row>
+    <row r="1068" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A1068" t="s">
+        <v>3390</v>
+      </c>
+      <c r="B1068" t="s">
+        <v>3391</v>
+      </c>
+      <c r="C1068" t="s">
+        <v>3392</v>
+      </c>
+      <c r="D1068" t="s">
+        <v>3569</v>
+      </c>
+    </row>
+    <row r="1069" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A1069" t="s">
+        <v>3393</v>
+      </c>
+      <c r="B1069" t="s">
+        <v>3394</v>
+      </c>
+      <c r="C1069" t="s">
+        <v>3395</v>
+      </c>
+      <c r="D1069" t="s">
+        <v>3570</v>
+      </c>
+    </row>
+    <row r="1070" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A1070" t="s">
+        <v>3396</v>
+      </c>
+      <c r="B1070" t="s">
+        <v>3397</v>
+      </c>
+      <c r="C1070" t="s">
+        <v>3398</v>
+      </c>
+      <c r="D1070" t="s">
+        <v>3571</v>
+      </c>
+    </row>
+    <row r="1071" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A1071" t="s">
+        <v>3399</v>
+      </c>
+      <c r="B1071" t="s">
+        <v>3400</v>
+      </c>
+      <c r="C1071" t="s">
+        <v>3401</v>
+      </c>
+      <c r="D1071" t="s">
+        <v>3572</v>
+      </c>
+    </row>
+    <row r="1072" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A1072" t="s">
+        <v>3402</v>
+      </c>
+      <c r="B1072" t="s">
+        <v>3403</v>
+      </c>
+      <c r="C1072" t="s">
+        <v>3404</v>
+      </c>
+      <c r="D1072" t="s">
+        <v>3573</v>
+      </c>
+    </row>
+    <row r="1073" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A1073" t="s">
+        <v>3405</v>
+      </c>
+      <c r="B1073" t="s">
+        <v>3406</v>
+      </c>
+      <c r="C1073" t="s">
+        <v>3407</v>
+      </c>
+      <c r="D1073" t="s">
+        <v>3574</v>
+      </c>
+    </row>
+    <row r="1074" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A1074" t="s">
+        <v>3408</v>
+      </c>
+      <c r="B1074" t="s">
+        <v>3409</v>
+      </c>
+      <c r="C1074" t="s">
+        <v>3410</v>
+      </c>
+      <c r="D1074" t="s">
+        <v>3575</v>
+      </c>
+    </row>
+    <row r="1075" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A1075" t="s">
+        <v>3411</v>
+      </c>
+      <c r="B1075" t="s">
+        <v>3412</v>
+      </c>
+      <c r="C1075" t="s">
+        <v>3413</v>
+      </c>
+      <c r="D1075" t="s">
+        <v>3576</v>
+      </c>
+    </row>
+    <row r="1076" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A1076" t="s">
+        <v>3414</v>
+      </c>
+      <c r="B1076" t="s">
+        <v>3415</v>
+      </c>
+      <c r="C1076" t="s">
+        <v>3416</v>
+      </c>
+      <c r="D1076" t="s">
+        <v>3577</v>
+      </c>
+    </row>
+    <row r="1077" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A1077" t="s">
+        <v>3417</v>
+      </c>
+      <c r="B1077" t="s">
+        <v>3418</v>
+      </c>
+      <c r="C1077" t="s">
+        <v>3419</v>
+      </c>
+      <c r="D1077" t="s">
+        <v>3578</v>
+      </c>
+    </row>
+    <row r="1078" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A1078" t="s">
+        <v>3420</v>
+      </c>
+      <c r="B1078" t="s">
+        <v>3421</v>
+      </c>
+      <c r="C1078" t="s">
+        <v>3422</v>
+      </c>
+      <c r="D1078" t="s">
+        <v>3579</v>
+      </c>
+    </row>
+    <row r="1079" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A1079" t="s">
+        <v>3423</v>
+      </c>
+      <c r="B1079" t="s">
+        <v>3424</v>
+      </c>
+      <c r="C1079" t="s">
+        <v>3425</v>
+      </c>
+      <c r="D1079" t="s">
+        <v>3580</v>
+      </c>
+    </row>
+    <row r="1080" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A1080" t="s">
+        <v>3426</v>
+      </c>
+      <c r="B1080" t="s">
+        <v>3427</v>
+      </c>
+      <c r="C1080" t="s">
+        <v>3428</v>
+      </c>
+      <c r="D1080" t="s">
+        <v>3581</v>
+      </c>
+    </row>
+    <row r="1081" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A1081" t="s">
+        <v>3429</v>
+      </c>
+      <c r="B1081" t="s">
+        <v>3430</v>
+      </c>
+      <c r="C1081" t="s">
+        <v>3431</v>
+      </c>
+      <c r="D1081" t="s">
+        <v>3582</v>
+      </c>
+    </row>
+    <row r="1082" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A1082" t="s">
+        <v>3432</v>
+      </c>
+      <c r="B1082" t="s">
+        <v>3433</v>
+      </c>
+      <c r="C1082" t="s">
+        <v>3434</v>
+      </c>
+      <c r="D1082" t="s">
+        <v>3583</v>
+      </c>
+    </row>
+    <row r="1083" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A1083" t="s">
+        <v>3435</v>
+      </c>
+      <c r="B1083" t="s">
+        <v>3436</v>
+      </c>
+      <c r="C1083" t="s">
+        <v>3437</v>
+      </c>
+      <c r="D1083" t="s">
+        <v>3584</v>
+      </c>
+    </row>
+    <row r="1084" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A1084" t="s">
+        <v>3438</v>
+      </c>
+      <c r="B1084" t="s">
+        <v>3439</v>
+      </c>
+      <c r="C1084" t="s">
+        <v>3440</v>
+      </c>
+      <c r="D1084" t="s">
+        <v>3585</v>
+      </c>
+    </row>
+    <row r="1085" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A1085" t="s">
+        <v>3441</v>
+      </c>
+      <c r="B1085" t="s">
+        <v>3442</v>
+      </c>
+      <c r="C1085" t="s">
+        <v>3443</v>
+      </c>
+      <c r="D1085" t="s">
+        <v>3586</v>
+      </c>
+    </row>
+    <row r="1086" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A1086" t="s">
+        <v>3444</v>
+      </c>
+      <c r="B1086" t="s">
+        <v>3445</v>
+      </c>
+      <c r="C1086" t="s">
+        <v>3446</v>
+      </c>
+      <c r="D1086" t="s">
+        <v>3587</v>
+      </c>
+    </row>
+    <row r="1087" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A1087" t="s">
+        <v>3447</v>
+      </c>
+      <c r="B1087" t="s">
+        <v>3448</v>
+      </c>
+      <c r="C1087" t="s">
+        <v>3449</v>
+      </c>
+      <c r="D1087" t="s">
+        <v>3588</v>
+      </c>
+    </row>
+    <row r="1088" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A1088" t="s">
+        <v>3450</v>
+      </c>
+      <c r="B1088" t="s">
+        <v>3451</v>
+      </c>
+      <c r="C1088" t="s">
+        <v>3452</v>
+      </c>
+      <c r="D1088" t="s">
+        <v>3589</v>
+      </c>
+    </row>
+    <row r="1089" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A1089" t="s">
+        <v>3453</v>
+      </c>
+      <c r="B1089" t="s">
+        <v>3454</v>
+      </c>
+      <c r="C1089" t="s">
+        <v>3455</v>
+      </c>
+      <c r="D1089" t="s">
+        <v>3590</v>
+      </c>
+    </row>
+    <row r="1090" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A1090" t="s">
+        <v>3456</v>
+      </c>
+      <c r="B1090" t="s">
+        <v>3457</v>
+      </c>
+      <c r="C1090" t="s">
+        <v>3458</v>
+      </c>
+      <c r="D1090" t="s">
+        <v>3591</v>
+      </c>
+    </row>
+    <row r="1091" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A1091" t="s">
+        <v>3459</v>
+      </c>
+      <c r="B1091" t="s">
+        <v>3460</v>
+      </c>
+      <c r="C1091" t="s">
+        <v>3461</v>
+      </c>
+      <c r="D1091" t="s">
+        <v>3592</v>
+      </c>
+    </row>
+    <row r="1092" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A1092" t="s">
+        <v>3462</v>
+      </c>
+      <c r="B1092" t="s">
+        <v>3463</v>
+      </c>
+      <c r="C1092" t="s">
+        <v>3464</v>
+      </c>
+      <c r="D1092" t="s">
+        <v>3593</v>
+      </c>
+    </row>
+    <row r="1093" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A1093" t="s">
+        <v>3465</v>
+      </c>
+      <c r="B1093" t="s">
+        <v>3466</v>
+      </c>
+      <c r="C1093" t="s">
+        <v>3467</v>
+      </c>
+      <c r="D1093" t="s">
+        <v>3594</v>
+      </c>
+    </row>
+    <row r="1094" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A1094" t="s">
+        <v>2416</v>
+      </c>
+      <c r="B1094" t="s">
+        <v>2417</v>
+      </c>
+      <c r="C1094" t="s">
+        <v>2418</v>
+      </c>
+      <c r="D1094" t="s">
+        <v>3595</v>
+      </c>
+    </row>
+    <row r="1095" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A1095" t="s">
+        <v>3468</v>
+      </c>
+      <c r="B1095" t="s">
+        <v>3469</v>
+      </c>
+      <c r="C1095" t="s">
+        <v>3470</v>
+      </c>
+      <c r="D1095" t="s">
+        <v>3596</v>
+      </c>
+    </row>
+    <row r="1096" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A1096" t="s">
+        <v>3471</v>
+      </c>
+      <c r="B1096" t="s">
+        <v>3472</v>
+      </c>
+      <c r="C1096" t="s">
+        <v>3473</v>
+      </c>
+      <c r="D1096" t="s">
+        <v>3597</v>
+      </c>
+    </row>
+    <row r="1097" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A1097" t="s">
+        <v>3474</v>
+      </c>
+      <c r="B1097" t="s">
+        <v>3475</v>
+      </c>
+      <c r="C1097" t="s">
+        <v>3476</v>
+      </c>
+      <c r="D1097" t="s">
+        <v>3598</v>
+      </c>
+    </row>
+    <row r="1098" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A1098" t="s">
+        <v>3477</v>
+      </c>
+      <c r="B1098" t="s">
+        <v>3478</v>
+      </c>
+      <c r="C1098" t="s">
+        <v>3479</v>
+      </c>
+      <c r="D1098" t="s">
+        <v>3599</v>
+      </c>
+    </row>
+    <row r="1099" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A1099" t="s">
+        <v>2659</v>
+      </c>
+      <c r="B1099" t="s">
+        <v>2660</v>
+      </c>
+      <c r="C1099" t="s">
+        <v>2661</v>
+      </c>
+      <c r="D1099" t="s">
+        <v>3600</v>
+      </c>
+    </row>
+    <row r="1100" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A1100" t="s">
+        <v>3480</v>
+      </c>
+      <c r="B1100" t="s">
+        <v>3481</v>
+      </c>
+      <c r="C1100" t="s">
+        <v>3482</v>
+      </c>
+      <c r="D1100" t="s">
+        <v>3601</v>
+      </c>
+    </row>
+    <row r="1101" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A1101" t="s">
+        <v>3483</v>
+      </c>
+      <c r="B1101" t="s">
+        <v>3484</v>
+      </c>
+      <c r="C1101" t="s">
+        <v>3485</v>
+      </c>
+      <c r="D1101" t="s">
+        <v>3602</v>
+      </c>
+    </row>
+    <row r="1102" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A1102" t="s">
+        <v>3486</v>
+      </c>
+      <c r="B1102" t="s">
+        <v>3487</v>
+      </c>
+      <c r="C1102" t="s">
+        <v>3488</v>
+      </c>
+      <c r="D1102" t="s">
+        <v>3603</v>
+      </c>
+    </row>
+    <row r="1103" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A1103" t="s">
+        <v>3489</v>
+      </c>
+      <c r="B1103" t="s">
+        <v>3490</v>
+      </c>
+      <c r="C1103" t="s">
+        <v>3491</v>
+      </c>
+      <c r="D1103" t="s">
+        <v>3604</v>
+      </c>
+    </row>
+    <row r="1104" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A1104" t="s">
+        <v>3492</v>
+      </c>
+      <c r="B1104" t="s">
+        <v>3493</v>
+      </c>
+      <c r="C1104" t="s">
+        <v>3494</v>
+      </c>
+      <c r="D1104" t="s">
+        <v>3605</v>
+      </c>
+    </row>
+    <row r="1105" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A1105" t="s">
+        <v>3495</v>
+      </c>
+      <c r="B1105" t="s">
+        <v>3496</v>
+      </c>
+      <c r="C1105" t="s">
+        <v>3497</v>
+      </c>
+      <c r="D1105" t="s">
+        <v>3606</v>
+      </c>
+    </row>
+    <row r="1106" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A1106" t="s">
+        <v>3498</v>
+      </c>
+      <c r="B1106" t="s">
+        <v>3499</v>
+      </c>
+      <c r="C1106" t="s">
+        <v>3500</v>
+      </c>
+      <c r="D1106" t="s">
+        <v>3607</v>
+      </c>
+    </row>
+    <row r="1107" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A1107" t="s">
+        <v>3501</v>
+      </c>
+      <c r="B1107" t="s">
+        <v>3502</v>
+      </c>
+      <c r="C1107" t="s">
+        <v>3503</v>
+      </c>
+      <c r="D1107" t="s">
+        <v>3608</v>
+      </c>
+    </row>
+    <row r="1108" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A1108" t="s">
+        <v>3504</v>
+      </c>
+      <c r="B1108" t="s">
+        <v>3505</v>
+      </c>
+      <c r="C1108" t="s">
+        <v>3506</v>
+      </c>
+      <c r="D1108" t="s">
+        <v>3609</v>
+      </c>
+    </row>
+    <row r="1109" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A1109" t="s">
+        <v>3507</v>
+      </c>
+      <c r="B1109" t="s">
+        <v>3508</v>
+      </c>
+      <c r="C1109" t="s">
+        <v>3509</v>
+      </c>
+      <c r="D1109" t="s">
+        <v>3610</v>
+      </c>
+    </row>
+    <row r="1110" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A1110" t="s">
+        <v>3510</v>
+      </c>
+      <c r="B1110" t="s">
+        <v>3511</v>
+      </c>
+      <c r="C1110" t="s">
+        <v>3512</v>
+      </c>
+      <c r="D1110" t="s">
+        <v>3611</v>
+      </c>
+    </row>
+    <row r="1111" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A1111" t="s">
+        <v>233</v>
+      </c>
+      <c r="B1111" t="s">
+        <v>234</v>
+      </c>
+      <c r="C1111" t="s">
+        <v>235</v>
+      </c>
+      <c r="D1111" t="s">
+        <v>3612</v>
+      </c>
+    </row>
+    <row r="1112" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A1112" t="s">
+        <v>1674</v>
+      </c>
+      <c r="B1112" t="s">
+        <v>1675</v>
+      </c>
+      <c r="C1112" t="s">
+        <v>1676</v>
+      </c>
+      <c r="D1112" t="s">
+        <v>3613</v>
+      </c>
+    </row>
+    <row r="1113" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A1113" t="s">
+        <v>1596</v>
+      </c>
+      <c r="B1113" t="s">
+        <v>1597</v>
+      </c>
+      <c r="C1113" t="s">
+        <v>1598</v>
+      </c>
+      <c r="D1113" t="s">
+        <v>3614</v>
+      </c>
+    </row>
+    <row r="1114" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A1114" t="s">
+        <v>1650</v>
+      </c>
+      <c r="B1114" t="s">
+        <v>1651</v>
+      </c>
+      <c r="C1114" t="s">
+        <v>1652</v>
+      </c>
+      <c r="D1114" t="s">
+        <v>3615</v>
+      </c>
+    </row>
+    <row r="1115" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A1115" t="s">
+        <v>1968</v>
+      </c>
+      <c r="B1115" t="s">
+        <v>1969</v>
+      </c>
+      <c r="C1115" t="s">
+        <v>1970</v>
+      </c>
+      <c r="D1115" t="s">
+        <v>3616</v>
+      </c>
+    </row>
+    <row r="1116" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A1116" t="s">
+        <v>2294</v>
+      </c>
+      <c r="B1116" t="s">
+        <v>2295</v>
+      </c>
+      <c r="C1116" t="s">
+        <v>2296</v>
+      </c>
+      <c r="D1116" t="s">
+        <v>3617</v>
+      </c>
+    </row>
+    <row r="1117" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A1117" t="s">
+        <v>1845</v>
+      </c>
+      <c r="B1117" t="s">
+        <v>1846</v>
+      </c>
+      <c r="C1117" t="s">
+        <v>1847</v>
+      </c>
+      <c r="D1117" t="s">
+        <v>3618</v>
+      </c>
+    </row>
+    <row r="1118" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A1118" t="s">
+        <v>1984</v>
+      </c>
+      <c r="B1118" t="s">
+        <v>1985</v>
+      </c>
+      <c r="C1118" t="s">
+        <v>1986</v>
+      </c>
+      <c r="D1118" t="s">
+        <v>3619</v>
+      </c>
+    </row>
+    <row r="1119" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A1119" t="s">
+        <v>2511</v>
+      </c>
+      <c r="B1119" t="s">
+        <v>2512</v>
+      </c>
+      <c r="C1119" t="s">
+        <v>2513</v>
+      </c>
+      <c r="D1119" t="s">
+        <v>3620</v>
+      </c>
+    </row>
+    <row r="1120" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A1120" t="s">
+        <v>2468</v>
+      </c>
+      <c r="B1120" t="s">
+        <v>2469</v>
+      </c>
+      <c r="C1120" t="s">
+        <v>2470</v>
+      </c>
+      <c r="D1120" t="s">
+        <v>3621</v>
+      </c>
+    </row>
+    <row r="1121" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A1121" t="s">
+        <v>3513</v>
+      </c>
+      <c r="B1121" t="s">
+        <v>3514</v>
+      </c>
+      <c r="C1121" t="s">
+        <v>3515</v>
+      </c>
+      <c r="D1121" t="s">
+        <v>3622</v>
+      </c>
+    </row>
+    <row r="1122" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A1122" t="s">
+        <v>2676</v>
+      </c>
+      <c r="B1122" t="s">
+        <v>2677</v>
+      </c>
+      <c r="C1122" t="s">
+        <v>2678</v>
+      </c>
+      <c r="D1122" t="s">
+        <v>3623</v>
+      </c>
+    </row>
+    <row r="1123" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A1123" t="s">
+        <v>2175</v>
+      </c>
+      <c r="B1123" t="s">
+        <v>2176</v>
+      </c>
+      <c r="C1123" t="s">
+        <v>2177</v>
+      </c>
+      <c r="D1123" t="s">
+        <v>3624</v>
+      </c>
+    </row>
+    <row r="1124" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A1124" t="s">
+        <v>2172</v>
+      </c>
+      <c r="B1124" t="s">
+        <v>2173</v>
+      </c>
+      <c r="C1124" t="s">
+        <v>2174</v>
+      </c>
+      <c r="D1124" t="s">
+        <v>3624</v>
+      </c>
+    </row>
+    <row r="1125" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A1125" t="s">
+        <v>1569</v>
+      </c>
+      <c r="B1125" t="s">
+        <v>1570</v>
+      </c>
+      <c r="C1125" t="s">
+        <v>1571</v>
+      </c>
+      <c r="D1125" t="s">
+        <v>3625</v>
+      </c>
+    </row>
+    <row r="1126" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A1126" t="s">
+        <v>1566</v>
+      </c>
+      <c r="B1126" t="s">
+        <v>1567</v>
+      </c>
+      <c r="C1126" t="s">
+        <v>1568</v>
+      </c>
+      <c r="D1126" t="s">
+        <v>3625</v>
+      </c>
+    </row>
+    <row r="1127" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A1127" t="s">
+        <v>1563</v>
+      </c>
+      <c r="B1127" t="s">
+        <v>1564</v>
+      </c>
+      <c r="C1127" t="s">
+        <v>1565</v>
+      </c>
+      <c r="D1127" t="s">
+        <v>3625</v>
+      </c>
+    </row>
+    <row r="1128" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A1128" t="s">
+        <v>1934</v>
+      </c>
+      <c r="B1128" t="s">
+        <v>1935</v>
+      </c>
+      <c r="C1128" t="s">
+        <v>1936</v>
+      </c>
+      <c r="D1128" t="s">
+        <v>3626</v>
+      </c>
+    </row>
+    <row r="1129" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A1129" t="s">
+        <v>2243</v>
+      </c>
+      <c r="B1129" t="s">
+        <v>2244</v>
+      </c>
+      <c r="C1129" t="s">
+        <v>2245</v>
+      </c>
+      <c r="D1129" t="s">
+        <v>3627</v>
+      </c>
+    </row>
+    <row r="1130" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A1130" t="s">
+        <v>2228</v>
+      </c>
+      <c r="B1130" t="s">
+        <v>2229</v>
+      </c>
+      <c r="C1130" t="s">
+        <v>2230</v>
+      </c>
+      <c r="D1130" t="s">
+        <v>3628</v>
+      </c>
+    </row>
+    <row r="1131" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A1131" t="s">
+        <v>2588</v>
+      </c>
+      <c r="B1131" t="s">
+        <v>2589</v>
+      </c>
+      <c r="C1131" t="s">
+        <v>2590</v>
+      </c>
+      <c r="D1131" t="s">
+        <v>3629</v>
+      </c>
+    </row>
+    <row r="1132" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A1132" t="s">
+        <v>2234</v>
+      </c>
+      <c r="B1132" t="s">
+        <v>2235</v>
+      </c>
+      <c r="C1132" t="s">
+        <v>2236</v>
+      </c>
+      <c r="D1132" t="s">
+        <v>3630</v>
+      </c>
+    </row>
+    <row r="1133" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A1133" t="s">
+        <v>2637</v>
+      </c>
+      <c r="B1133" t="s">
+        <v>2638</v>
+      </c>
+      <c r="C1133" t="s">
+        <v>2639</v>
+      </c>
+      <c r="D1133" t="s">
+        <v>3631</v>
+      </c>
+    </row>
+    <row r="1134" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A1134" t="s">
+        <v>1726</v>
+      </c>
+      <c r="B1134" t="s">
+        <v>1727</v>
+      </c>
+      <c r="C1134" t="s">
+        <v>1728</v>
+      </c>
+      <c r="D1134" t="s">
+        <v>3632</v>
+      </c>
+    </row>
+    <row r="1135" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A1135" t="s">
+        <v>2195</v>
+      </c>
+      <c r="B1135" t="s">
+        <v>2196</v>
+      </c>
+      <c r="C1135" t="s">
+        <v>2197</v>
+      </c>
+      <c r="D1135" t="s">
+        <v>3633</v>
+      </c>
+    </row>
+    <row r="1136" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A1136" t="s">
+        <v>1875</v>
+      </c>
+      <c r="B1136" t="s">
+        <v>1876</v>
+      </c>
+      <c r="C1136" t="s">
+        <v>1877</v>
+      </c>
+      <c r="D1136" t="s">
+        <v>3634</v>
+      </c>
+    </row>
+    <row r="1137" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A1137" t="s">
+        <v>1896</v>
+      </c>
+      <c r="B1137" t="s">
+        <v>1897</v>
+      </c>
+      <c r="C1137" t="s">
+        <v>1898</v>
+      </c>
+      <c r="D1137" t="s">
+        <v>3635</v>
+      </c>
+    </row>
+    <row r="1138" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A1138" t="s">
+        <v>137</v>
+      </c>
+      <c r="B1138" t="s">
+        <v>138</v>
+      </c>
+      <c r="C1138" t="s">
+        <v>139</v>
+      </c>
+      <c r="D1138" t="s">
+        <v>3636</v>
+      </c>
+    </row>
+    <row r="1139" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A1139" t="s">
+        <v>2291</v>
+      </c>
+      <c r="B1139" t="s">
+        <v>2292</v>
+      </c>
+      <c r="C1139" t="s">
+        <v>2293</v>
+      </c>
+      <c r="D1139" t="s">
+        <v>3637</v>
+      </c>
+    </row>
+    <row r="1140" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A1140" t="s">
+        <v>2240</v>
+      </c>
+      <c r="B1140" t="s">
+        <v>2241</v>
+      </c>
+      <c r="C1140" t="s">
+        <v>2242</v>
+      </c>
+      <c r="D1140" t="s">
+        <v>3638</v>
+      </c>
+    </row>
+    <row r="1141" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A1141" t="s">
+        <v>2502</v>
+      </c>
+      <c r="B1141" t="s">
+        <v>2503</v>
+      </c>
+      <c r="C1141" t="s">
+        <v>2504</v>
+      </c>
+      <c r="D1141" t="s">
+        <v>3639</v>
+      </c>
+    </row>
+    <row r="1142" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A1142" t="s">
+        <v>2497</v>
+      </c>
+      <c r="B1142" t="s">
+        <v>2498</v>
+      </c>
+      <c r="C1142" t="s">
+        <v>2499</v>
+      </c>
+      <c r="D1142" t="s">
+        <v>3640</v>
+      </c>
+    </row>
+    <row r="1143" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A1143" t="s">
+        <v>1632</v>
+      </c>
+      <c r="B1143" t="s">
+        <v>1633</v>
+      </c>
+      <c r="C1143" t="s">
+        <v>1634</v>
+      </c>
+      <c r="D1143" t="s">
+        <v>3641</v>
+      </c>
+    </row>
+    <row r="1144" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A1144" t="s">
+        <v>2288</v>
+      </c>
+      <c r="B1144" t="s">
+        <v>2289</v>
+      </c>
+      <c r="C1144" t="s">
+        <v>2290</v>
+      </c>
+      <c r="D1144" t="s">
+        <v>3642</v>
+      </c>
+    </row>
+    <row r="1145" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A1145" t="s">
+        <v>2237</v>
+      </c>
+      <c r="B1145" t="s">
+        <v>2238</v>
+      </c>
+      <c r="C1145" t="s">
+        <v>2239</v>
+      </c>
+      <c r="D1145" t="s">
+        <v>3643</v>
+      </c>
+    </row>
+    <row r="1146" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A1146" t="s">
+        <v>2542</v>
+      </c>
+      <c r="B1146" t="s">
+        <v>2543</v>
+      </c>
+      <c r="C1146" t="s">
+        <v>2544</v>
+      </c>
+      <c r="D1146" t="s">
+        <v>3644</v>
+      </c>
+    </row>
+    <row r="1147" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A1147" t="s">
+        <v>2718</v>
+      </c>
+      <c r="B1147" t="s">
+        <v>2719</v>
+      </c>
+      <c r="C1147" t="s">
+        <v>2720</v>
+      </c>
+      <c r="D1147" t="s">
+        <v>3645</v>
+      </c>
+    </row>
+    <row r="1148" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A1148" t="s">
+        <v>1461</v>
+      </c>
+      <c r="B1148" t="s">
+        <v>1462</v>
+      </c>
+      <c r="C1148" t="s">
+        <v>1463</v>
+      </c>
+      <c r="D1148" t="s">
+        <v>3646</v>
+      </c>
+    </row>
+    <row r="1149" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A1149" t="s">
+        <v>1890</v>
+      </c>
+      <c r="B1149" t="s">
+        <v>1891</v>
+      </c>
+      <c r="C1149" t="s">
+        <v>1892</v>
+      </c>
+      <c r="D1149" t="s">
+        <v>3647</v>
+      </c>
+    </row>
+    <row r="1150" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A1150" t="s">
+        <v>2356</v>
+      </c>
+      <c r="B1150" t="s">
+        <v>2357</v>
+      </c>
+      <c r="C1150" t="s">
+        <v>2358</v>
+      </c>
+      <c r="D1150" t="s">
+        <v>3648</v>
+      </c>
+    </row>
+    <row r="1151" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A1151" t="s">
+        <v>1809</v>
+      </c>
+      <c r="B1151" t="s">
+        <v>1810</v>
+      </c>
+      <c r="C1151" t="s">
+        <v>1811</v>
+      </c>
+      <c r="D1151" t="s">
+        <v>3649</v>
+      </c>
+    </row>
+    <row r="1152" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A1152" t="s">
+        <v>25</v>
+      </c>
+      <c r="B1152" t="s">
+        <v>26</v>
+      </c>
+      <c r="C1152" t="s">
+        <v>27</v>
+      </c>
+      <c r="D1152" t="s">
+        <v>3650</v>
+      </c>
+    </row>
+    <row r="1153" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A1153" t="s">
+        <v>131</v>
+      </c>
+      <c r="B1153" t="s">
+        <v>132</v>
+      </c>
+      <c r="C1153" t="s">
+        <v>133</v>
+      </c>
+      <c r="D1153" t="s">
+        <v>3651</v>
+      </c>
+    </row>
+    <row r="1154" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A1154" t="s">
+        <v>2163</v>
+      </c>
+      <c r="B1154" t="s">
+        <v>2164</v>
+      </c>
+      <c r="C1154" t="s">
+        <v>2165</v>
+      </c>
+      <c r="D1154" t="s">
+        <v>3652</v>
+      </c>
+    </row>
+    <row r="1155" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A1155" t="s">
+        <v>1467</v>
+      </c>
+      <c r="B1155" t="s">
+        <v>1468</v>
+      </c>
+      <c r="C1155" t="s">
+        <v>1469</v>
+      </c>
+      <c r="D1155" t="s">
+        <v>3653</v>
+      </c>
+    </row>
+    <row r="1156" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A1156" t="s">
+        <v>2184</v>
+      </c>
+      <c r="B1156" t="s">
+        <v>2185</v>
+      </c>
+      <c r="C1156" t="s">
+        <v>2186</v>
+      </c>
+      <c r="D1156" t="s">
+        <v>3654</v>
+      </c>
+    </row>
+    <row r="1157" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A1157" t="s">
+        <v>239</v>
+      </c>
+      <c r="B1157" t="s">
+        <v>240</v>
+      </c>
+      <c r="C1157" t="s">
+        <v>241</v>
+      </c>
+      <c r="D1157" t="s">
+        <v>3655</v>
+      </c>
+    </row>
+    <row r="1158" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A1158" t="s">
+        <v>2500</v>
+      </c>
+      <c r="B1158" t="s">
+        <v>3516</v>
+      </c>
+      <c r="C1158" t="s">
+        <v>2501</v>
+      </c>
+      <c r="D1158" t="s">
+        <v>3656</v>
+      </c>
+    </row>
+    <row r="1159" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A1159" t="s">
+        <v>149</v>
+      </c>
+      <c r="B1159" t="s">
+        <v>150</v>
+      </c>
+      <c r="C1159" t="s">
+        <v>151</v>
+      </c>
+      <c r="D1159" t="s">
+        <v>3657</v>
+      </c>
+    </row>
   </sheetData>
   <autoFilter ref="A1:D956" xr:uid="{EE52D9B7-0D33-6C4B-ABD2-124A93043E14}"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/Database.xlsx
+++ b/Database.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/ashokgopalan/Downloads/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D7297A8B-7A0C-BF44-AEB1-A124FF2D5DCC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BDD052B9-4E87-D947-BAAE-380C4DE2A69A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="760" windowWidth="34560" windowHeight="20440" xr2:uid="{26FF7FE2-E5E3-384C-ABF6-08C089761ADA}"/>
   </bookViews>
@@ -16,7 +16,7 @@
     <sheet name="sample2" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">sample2!$A$1:$D$956</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">sample2!$A$1:$D$1325</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -42,7 +42,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4628" uniqueCount="3658">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5292" uniqueCount="4234">
   <si>
     <t>VideoID</t>
   </si>
@@ -11016,6 +11016,1734 @@
   </si>
   <si>
     <t>English|True Guru Guides From Experience|Inspirational Inspirational Clips||</t>
+  </si>
+  <si>
+    <t>EyBtOifZAys</t>
+  </si>
+  <si>
+    <t>Prayer at Dawn</t>
+  </si>
+  <si>
+    <t>https://www.youtube.com/watch?v=EyBtOifZAys</t>
+  </si>
+  <si>
+    <t>hc2x64QAmvo</t>
+  </si>
+  <si>
+    <t>O God beautiful - Paramhansa Yogananda</t>
+  </si>
+  <si>
+    <t>https://www.youtube.com/watch?v=hc2x64QAmvo</t>
+  </si>
+  <si>
+    <t>IXY0CM83Jss</t>
+  </si>
+  <si>
+    <t>He Hari Sundara</t>
+  </si>
+  <si>
+    <t>https://www.youtube.com/watch?v=IXY0CM83Jss</t>
+  </si>
+  <si>
+    <t>Bju7gWiuZCU</t>
+  </si>
+  <si>
+    <t>https://www.youtube.com/watch?v=Bju7gWiuZCU</t>
+  </si>
+  <si>
+    <t>hnTJwKDtHDA</t>
+  </si>
+  <si>
+    <t>God, Christ, Gurus</t>
+  </si>
+  <si>
+    <t>https://www.youtube.com/watch?v=hnTJwKDtHDA</t>
+  </si>
+  <si>
+    <t>wIKiFgsIWHs</t>
+  </si>
+  <si>
+    <t>Prayer at Noon</t>
+  </si>
+  <si>
+    <t>https://www.youtube.com/watch?v=wIKiFgsIWHs</t>
+  </si>
+  <si>
+    <t>_rjI-ej-nGY</t>
+  </si>
+  <si>
+    <t>The Hound of Heaven</t>
+  </si>
+  <si>
+    <t>https://www.youtube.com/watch?v=_rjI-ej-nGY</t>
+  </si>
+  <si>
+    <t>FszBLKSeM28</t>
+  </si>
+  <si>
+    <t>https://www.youtube.com/watch?v=FszBLKSeM28</t>
+  </si>
+  <si>
+    <t>DFH5PzhpFz8</t>
+  </si>
+  <si>
+    <t>Divine Mothers Song to the Devotee</t>
+  </si>
+  <si>
+    <t>https://www.youtube.com/watch?v=DFH5PzhpFz8</t>
+  </si>
+  <si>
+    <t>mhgwDjRjdFM</t>
+  </si>
+  <si>
+    <t>In the Temple of Silence</t>
+  </si>
+  <si>
+    <t>https://www.youtube.com/watch?v=mhgwDjRjdFM</t>
+  </si>
+  <si>
+    <t>L6h7v4TqZ4g</t>
+  </si>
+  <si>
+    <t>Song of India</t>
+  </si>
+  <si>
+    <t>https://www.youtube.com/watch?v=L6h7v4TqZ4g</t>
+  </si>
+  <si>
+    <t>KFNdg7Q9YYs</t>
+  </si>
+  <si>
+    <t>Shanti Mundiray</t>
+  </si>
+  <si>
+    <t>https://www.youtube.com/watch?v=KFNdg7Q9YYs</t>
+  </si>
+  <si>
+    <t>3Z79qGEeQL8</t>
+  </si>
+  <si>
+    <t>Prayer at Eventide</t>
+  </si>
+  <si>
+    <t>https://www.youtube.com/watch?v=3Z79qGEeQL8</t>
+  </si>
+  <si>
+    <t>j_8qDvlFmlU</t>
+  </si>
+  <si>
+    <t>I Will Be Thine Always</t>
+  </si>
+  <si>
+    <t>https://www.youtube.com/watch?v=j_8qDvlFmlU</t>
+  </si>
+  <si>
+    <t>A0e9CPSym7k</t>
+  </si>
+  <si>
+    <t>Main Tera Hamesha</t>
+  </si>
+  <si>
+    <t>https://www.youtube.com/watch?v=A0e9CPSym7k</t>
+  </si>
+  <si>
+    <t>iXP8mcipTgs</t>
+  </si>
+  <si>
+    <t>Do not dry the ocean of my Love - Paramhansa Yogananda</t>
+  </si>
+  <si>
+    <t>https://www.youtube.com/watch?v=iXP8mcipTgs</t>
+  </si>
+  <si>
+    <t>upQUvPfT6W8</t>
+  </si>
+  <si>
+    <t>Prayer at Night</t>
+  </si>
+  <si>
+    <t>https://www.youtube.com/watch?v=upQUvPfT6W8</t>
+  </si>
+  <si>
+    <t>MGa88qG0rt8</t>
+  </si>
+  <si>
+    <t>https://www.youtube.com/watch?v=MGa88qG0rt8</t>
+  </si>
+  <si>
+    <t>zV8x8uCoXc8</t>
+  </si>
+  <si>
+    <t>Who is in My Temple</t>
+  </si>
+  <si>
+    <t>https://www.youtube.com/watch?v=zV8x8uCoXc8</t>
+  </si>
+  <si>
+    <t>BgDz6DoeBg4</t>
+  </si>
+  <si>
+    <t>https://www.youtube.com/watch?v=BgDz6DoeBg4</t>
+  </si>
+  <si>
+    <t>MHw4bfEjD2c</t>
+  </si>
+  <si>
+    <t>https://www.youtube.com/watch?v=MHw4bfEjD2c</t>
+  </si>
+  <si>
+    <t>WMa7bIShNKI</t>
+  </si>
+  <si>
+    <t>In the Valley of Sorrow</t>
+  </si>
+  <si>
+    <t>https://www.youtube.com/watch?v=WMa7bIShNKI</t>
+  </si>
+  <si>
+    <t>VlnAaiqtg8k</t>
+  </si>
+  <si>
+    <t>My Krishna is Blue</t>
+  </si>
+  <si>
+    <t>https://www.youtube.com/watch?v=VlnAaiqtg8k</t>
+  </si>
+  <si>
+    <t>OB6x3u7iipU</t>
+  </si>
+  <si>
+    <t>I Am the Sky</t>
+  </si>
+  <si>
+    <t>https://www.youtube.com/watch?v=OB6x3u7iipU</t>
+  </si>
+  <si>
+    <t>lyuP_PgXCTM</t>
+  </si>
+  <si>
+    <t>Where is There Love</t>
+  </si>
+  <si>
+    <t>https://www.youtube.com/watch?v=lyuP_PgXCTM</t>
+  </si>
+  <si>
+    <t>p1TSk004POw</t>
+  </si>
+  <si>
+    <t>https://www.youtube.com/watch?v=p1TSk004POw</t>
+  </si>
+  <si>
+    <t>4Q2sx4pCm0s</t>
+  </si>
+  <si>
+    <t>https://www.youtube.com/watch?v=4Q2sx4pCm0s</t>
+  </si>
+  <si>
+    <t>IBWDk8g5C1g</t>
+  </si>
+  <si>
+    <t>Listen, Listen, Listen</t>
+  </si>
+  <si>
+    <t>https://www.youtube.com/watch?v=IBWDk8g5C1g</t>
+  </si>
+  <si>
+    <t>yBFJlXmngNA</t>
+  </si>
+  <si>
+    <t>https://www.youtube.com/watch?v=yBFJlXmngNA</t>
+  </si>
+  <si>
+    <t>Ryc6TseZDkY</t>
+  </si>
+  <si>
+    <t>Today My Mind Has Dived</t>
+  </si>
+  <si>
+    <t>https://www.youtube.com/watch?v=Ryc6TseZDkY</t>
+  </si>
+  <si>
+    <t>BeXbDCqY3HY</t>
+  </si>
+  <si>
+    <t>Om Song</t>
+  </si>
+  <si>
+    <t>https://www.youtube.com/watch?v=BeXbDCqY3HY</t>
+  </si>
+  <si>
+    <t>IfwGaIW_Bmo</t>
+  </si>
+  <si>
+    <t>O Thou King of the Infinite</t>
+  </si>
+  <si>
+    <t>https://www.youtube.com/watch?v=IfwGaIW_Bmo</t>
+  </si>
+  <si>
+    <t>Pn06BLdU67E</t>
+  </si>
+  <si>
+    <t>https://www.youtube.com/watch?v=Pn06BLdU67E</t>
+  </si>
+  <si>
+    <t>iNl48sdciKc</t>
+  </si>
+  <si>
+    <t>Divine Gypsy</t>
+  </si>
+  <si>
+    <t>https://www.youtube.com/watch?v=iNl48sdciKc</t>
+  </si>
+  <si>
+    <t>KLJuiG8glFA</t>
+  </si>
+  <si>
+    <t>https://www.youtube.com/watch?v=KLJuiG8glFA</t>
+  </si>
+  <si>
+    <t>WhGVZppb64M</t>
+  </si>
+  <si>
+    <t>https://www.youtube.com/watch?v=WhGVZppb64M</t>
+  </si>
+  <si>
+    <t>vQbXGiVN7LU</t>
+  </si>
+  <si>
+    <t>O God Beautiful</t>
+  </si>
+  <si>
+    <t>https://www.youtube.com/watch?v=vQbXGiVN7LU</t>
+  </si>
+  <si>
+    <t>ehZVfqD3WQs</t>
+  </si>
+  <si>
+    <t>https://www.youtube.com/watch?v=ehZVfqD3WQs</t>
+  </si>
+  <si>
+    <t>oys07DpHR30</t>
+  </si>
+  <si>
+    <t>https://www.youtube.com/watch?v=oys07DpHR30</t>
+  </si>
+  <si>
+    <t>kITE3vbsgT4</t>
+  </si>
+  <si>
+    <t>https://www.youtube.com/watch?v=kITE3vbsgT4</t>
+  </si>
+  <si>
+    <t>2GAQoi2OeDM</t>
+  </si>
+  <si>
+    <t>Door of My Heart</t>
+  </si>
+  <si>
+    <t>https://www.youtube.com/watch?v=2GAQoi2OeDM</t>
+  </si>
+  <si>
+    <t>aUa3A8Yvt8U</t>
+  </si>
+  <si>
+    <t>https://www.youtube.com/watch?v=aUa3A8Yvt8U</t>
+  </si>
+  <si>
+    <t>cu0mJ5fzLoY</t>
+  </si>
+  <si>
+    <t>https://www.youtube.com/watch?v=cu0mJ5fzLoY</t>
+  </si>
+  <si>
+    <t>9dr3gY_lf34</t>
+  </si>
+  <si>
+    <t>https://www.youtube.com/watch?v=9dr3gY_lf34</t>
+  </si>
+  <si>
+    <t>1R4_LzeiXK4</t>
+  </si>
+  <si>
+    <t>Light the Lamp of Thy Love</t>
+  </si>
+  <si>
+    <t>https://www.youtube.com/watch?v=1R4_LzeiXK4</t>
+  </si>
+  <si>
+    <t>6yQKEHq4HAA</t>
+  </si>
+  <si>
+    <t>https://www.youtube.com/watch?v=6yQKEHq4HAA</t>
+  </si>
+  <si>
+    <t>a0nOLb54y9s</t>
+  </si>
+  <si>
+    <t>Who Is in My Temple?</t>
+  </si>
+  <si>
+    <t>https://www.youtube.com/watch?v=a0nOLb54y9s</t>
+  </si>
+  <si>
+    <t>NyAbtk4864c</t>
+  </si>
+  <si>
+    <t>Murali Krishna</t>
+  </si>
+  <si>
+    <t>https://www.youtube.com/watch?v=NyAbtk4864c</t>
+  </si>
+  <si>
+    <t>yxF3_6JRsjo</t>
+  </si>
+  <si>
+    <t>https://www.youtube.com/watch?v=yxF3_6JRsjo</t>
+  </si>
+  <si>
+    <t>PBMyZt_yURw</t>
+  </si>
+  <si>
+    <t>https://www.youtube.com/watch?v=PBMyZt_yURw</t>
+  </si>
+  <si>
+    <t>KqkQgkU2t6M</t>
+  </si>
+  <si>
+    <t>https://www.youtube.com/watch?v=KqkQgkU2t6M</t>
+  </si>
+  <si>
+    <t>q0BIshw_F10</t>
+  </si>
+  <si>
+    <t>https://www.youtube.com/watch?v=q0BIshw_F10</t>
+  </si>
+  <si>
+    <t>62cSBt9bb4Q</t>
+  </si>
+  <si>
+    <t>Jaya Jaya Ma</t>
+  </si>
+  <si>
+    <t>https://www.youtube.com/watch?v=62cSBt9bb4Q</t>
+  </si>
+  <si>
+    <t>H7Li5Yo2s9Q</t>
+  </si>
+  <si>
+    <t>Jai Guru</t>
+  </si>
+  <si>
+    <t>https://www.youtube.com/watch?v=H7Li5Yo2s9Q</t>
+  </si>
+  <si>
+    <t>-AFByO1YL74</t>
+  </si>
+  <si>
+    <t>https://www.youtube.com/watch?v=-AFByO1YL74</t>
+  </si>
+  <si>
+    <t>HDxFwX6kPbI</t>
+  </si>
+  <si>
+    <t>Radha Krishna Govinda</t>
+  </si>
+  <si>
+    <t>https://www.youtube.com/watch?v=HDxFwX6kPbI</t>
+  </si>
+  <si>
+    <t>wbChJuu7CPM</t>
+  </si>
+  <si>
+    <t>https://www.youtube.com/watch?v=wbChJuu7CPM</t>
+  </si>
+  <si>
+    <t>fdqB5J32pX8</t>
+  </si>
+  <si>
+    <t>Guru Hamare</t>
+  </si>
+  <si>
+    <t>https://www.youtube.com/watch?v=fdqB5J32pX8</t>
+  </si>
+  <si>
+    <t>VdugSeqC6Oo</t>
+  </si>
+  <si>
+    <t>Help Me Come Back</t>
+  </si>
+  <si>
+    <t>https://www.youtube.com/watch?v=VdugSeqC6Oo</t>
+  </si>
+  <si>
+    <t>SCCBfCeIvpI</t>
+  </si>
+  <si>
+    <t>Tero Naam</t>
+  </si>
+  <si>
+    <t>https://www.youtube.com/watch?v=SCCBfCeIvpI</t>
+  </si>
+  <si>
+    <t>ZX2CbJvm2MQ</t>
+  </si>
+  <si>
+    <t>God, Krishna, Christ, Gurus</t>
+  </si>
+  <si>
+    <t>https://www.youtube.com/watch?v=ZX2CbJvm2MQ</t>
+  </si>
+  <si>
+    <t>urFqRZTIYmU</t>
+  </si>
+  <si>
+    <t>Om, Tat, Sat</t>
+  </si>
+  <si>
+    <t>https://www.youtube.com/watch?v=urFqRZTIYmU</t>
+  </si>
+  <si>
+    <t>S312XGYA4t8</t>
+  </si>
+  <si>
+    <t>Namo, Namo</t>
+  </si>
+  <si>
+    <t>https://www.youtube.com/watch?v=S312XGYA4t8</t>
+  </si>
+  <si>
+    <t>aGT1iAkJMdA</t>
+  </si>
+  <si>
+    <t>https://www.youtube.com/watch?v=aGT1iAkJMdA</t>
+  </si>
+  <si>
+    <t>LCpTZHPKBPw</t>
+  </si>
+  <si>
+    <t>https://www.youtube.com/watch?v=LCpTZHPKBPw</t>
+  </si>
+  <si>
+    <t>C65OWJ48RgU</t>
+  </si>
+  <si>
+    <t>Divine Mother’s Song to the Devotee</t>
+  </si>
+  <si>
+    <t>https://www.youtube.com/watch?v=C65OWJ48RgU</t>
+  </si>
+  <si>
+    <t>d-j_6bDKlzI</t>
+  </si>
+  <si>
+    <t>https://www.youtube.com/watch?v=d-j_6bDKlzI</t>
+  </si>
+  <si>
+    <t>LbscWSheiNA</t>
+  </si>
+  <si>
+    <t>https://www.youtube.com/watch?v=LbscWSheiNA</t>
+  </si>
+  <si>
+    <t>2YF9W94JB3U</t>
+  </si>
+  <si>
+    <t>https://www.youtube.com/watch?v=2YF9W94JB3U</t>
+  </si>
+  <si>
+    <t>pncNctjTm1M</t>
+  </si>
+  <si>
+    <t>https://www.youtube.com/watch?v=pncNctjTm1M</t>
+  </si>
+  <si>
+    <t>uT1dNRLmtu8</t>
+  </si>
+  <si>
+    <t>Polestar of My Life</t>
+  </si>
+  <si>
+    <t>https://www.youtube.com/watch?v=uT1dNRLmtu8</t>
+  </si>
+  <si>
+    <t>JxO0Iml-fHk</t>
+  </si>
+  <si>
+    <t>https://www.youtube.com/watch?v=JxO0Iml-fHk</t>
+  </si>
+  <si>
+    <t>vfbI83oAZ8o</t>
+  </si>
+  <si>
+    <t>https://www.youtube.com/watch?v=vfbI83oAZ8o</t>
+  </si>
+  <si>
+    <t>EHyxtdZvlY0</t>
+  </si>
+  <si>
+    <t>When Thy Song Flows Though Me</t>
+  </si>
+  <si>
+    <t>https://www.youtube.com/watch?v=EHyxtdZvlY0</t>
+  </si>
+  <si>
+    <t>0AMd2PVkmAk</t>
+  </si>
+  <si>
+    <t>https://www.youtube.com/watch?v=0AMd2PVkmAk</t>
+  </si>
+  <si>
+    <t>BPybvY2lDEw</t>
+  </si>
+  <si>
+    <t>Suno Mere Atma-Gan (At Thy Feet)</t>
+  </si>
+  <si>
+    <t>https://www.youtube.com/watch?v=BPybvY2lDEw</t>
+  </si>
+  <si>
+    <t>9D1rd8hFj9s</t>
+  </si>
+  <si>
+    <t>Is Nind Se, Prabhu (From This Sleep, Lord)</t>
+  </si>
+  <si>
+    <t>https://www.youtube.com/watch?v=9D1rd8hFj9s</t>
+  </si>
+  <si>
+    <t>_A94KMJDl7o</t>
+  </si>
+  <si>
+    <t>Dukh Ki Vadi Me (In the Valley of Sorrow)</t>
+  </si>
+  <si>
+    <t>https://www.youtube.com/watch?v=_A94KMJDl7o</t>
+  </si>
+  <si>
+    <t>8RBBs6jeu_M</t>
+  </si>
+  <si>
+    <t>Nitya Navin Anand (Ever New Joy)</t>
+  </si>
+  <si>
+    <t>https://www.youtube.com/watch?v=8RBBs6jeu_M</t>
+  </si>
+  <si>
+    <t>DfcNZfmdEDY</t>
+  </si>
+  <si>
+    <t>Shanti Mandir Me (In the Temple of Silence)</t>
+  </si>
+  <si>
+    <t>https://www.youtube.com/watch?v=DfcNZfmdEDY</t>
+  </si>
+  <si>
+    <t>G2wJnRwWoZc</t>
+  </si>
+  <si>
+    <t>Shyamal Krishna (Cloud-Colored Christ)</t>
+  </si>
+  <si>
+    <t>https://www.youtube.com/watch?v=G2wJnRwWoZc</t>
+  </si>
+  <si>
+    <t>ZUTbWsHy62o</t>
+  </si>
+  <si>
+    <t>Niras Na Karo Mere Prem Sagar Ko (Do Not Dry the Ocean of My Love)</t>
+  </si>
+  <si>
+    <t>https://www.youtube.com/watch?v=ZUTbWsHy62o</t>
+  </si>
+  <si>
+    <t>fVOWVugDSxw</t>
+  </si>
+  <si>
+    <t>Ma, Tujhe Di Atma Ki Pukar (I Give You My Soul Call)</t>
+  </si>
+  <si>
+    <t>https://www.youtube.com/watch?v=fVOWVugDSxw</t>
+  </si>
+  <si>
+    <t>4bUcwYLB8kA</t>
+  </si>
+  <si>
+    <t>Kaun Hai Mere Mandir Me (Who is in My Temple)</t>
+  </si>
+  <si>
+    <t>https://www.youtube.com/watch?v=4bUcwYLB8kA</t>
+  </si>
+  <si>
+    <t>7nZM9mXjxfU</t>
+  </si>
+  <si>
+    <t>Nil Kamal Charan (Blue Lotus Feet)</t>
+  </si>
+  <si>
+    <t>https://www.youtube.com/watch?v=7nZM9mXjxfU</t>
+  </si>
+  <si>
+    <t>N2aYWB1z2-k</t>
+  </si>
+  <si>
+    <t>Guru Stuti (Slokas) - He Bhagavan (Praise of the Guru - O Lord)</t>
+  </si>
+  <si>
+    <t>https://www.youtube.com/watch?v=N2aYWB1z2-k</t>
+  </si>
+  <si>
+    <t>2u1zIMyVxLw</t>
+  </si>
+  <si>
+    <t>Dhyan Karo (Meditate)</t>
+  </si>
+  <si>
+    <t>https://www.youtube.com/watch?v=2u1zIMyVxLw</t>
+  </si>
+  <si>
+    <t>BkCgGbqruiw</t>
+  </si>
+  <si>
+    <t>Bhaja Mana (Pray Night and Day)</t>
+  </si>
+  <si>
+    <t>https://www.youtube.com/watch?v=BkCgGbqruiw</t>
+  </si>
+  <si>
+    <t>edlqMm-8OXk</t>
+  </si>
+  <si>
+    <t>Sri Guru Sharanam (I Surrender to the Guru)</t>
+  </si>
+  <si>
+    <t>https://www.youtube.com/watch?v=edlqMm-8OXk</t>
+  </si>
+  <si>
+    <t>krSz8ApD_KE</t>
+  </si>
+  <si>
+    <t>Krishna Stuti (Sloka) - Krishna Gopal Giridhari (Praise Lord Krishna - Victory to Krishna in...</t>
+  </si>
+  <si>
+    <t>https://www.youtube.com/watch?v=krSz8ApD_KE</t>
+  </si>
+  <si>
+    <t>aBnUPM_sG2Y</t>
+  </si>
+  <si>
+    <t>Bhajan Karungi Tumhara (Lord, I Will Sing to Thee)</t>
+  </si>
+  <si>
+    <t>https://www.youtube.com/watch?v=aBnUPM_sG2Y</t>
+  </si>
+  <si>
+    <t>XHgUOm4I5Po</t>
+  </si>
+  <si>
+    <t>https://www.youtube.com/watch?v=XHgUOm4I5Po</t>
+  </si>
+  <si>
+    <t>VDqKwucZLDY</t>
+  </si>
+  <si>
+    <t>Om Jai Jagadish Hare (Arati)</t>
+  </si>
+  <si>
+    <t>https://www.youtube.com/watch?v=VDqKwucZLDY</t>
+  </si>
+  <si>
+    <t>jCEf3uDSreo</t>
+  </si>
+  <si>
+    <t>https://www.youtube.com/watch?v=jCEf3uDSreo</t>
+  </si>
+  <si>
+    <t>FmT8LxBhm7c</t>
+  </si>
+  <si>
+    <t>https://www.youtube.com/watch?v=FmT8LxBhm7c</t>
+  </si>
+  <si>
+    <t>gENNZJit6Fc</t>
+  </si>
+  <si>
+    <t>https://www.youtube.com/watch?v=gENNZJit6Fc</t>
+  </si>
+  <si>
+    <t>hH-J-Ms1_lA</t>
+  </si>
+  <si>
+    <t>https://www.youtube.com/watch?v=hH-J-Ms1_lA</t>
+  </si>
+  <si>
+    <t>27SW7QNn0pg</t>
+  </si>
+  <si>
+    <t>https://www.youtube.com/watch?v=27SW7QNn0pg</t>
+  </si>
+  <si>
+    <t>XERunXHC-1Y</t>
+  </si>
+  <si>
+    <t>https://www.youtube.com/watch?v=XERunXHC-1Y</t>
+  </si>
+  <si>
+    <t>ucwxSN14GkY</t>
+  </si>
+  <si>
+    <t>https://www.youtube.com/watch?v=ucwxSN14GkY</t>
+  </si>
+  <si>
+    <t>lLRwJlbokyM</t>
+  </si>
+  <si>
+    <t>https://www.youtube.com/watch?v=lLRwJlbokyM</t>
+  </si>
+  <si>
+    <t>aYCXRprMhc8</t>
+  </si>
+  <si>
+    <t>https://www.youtube.com/watch?v=aYCXRprMhc8</t>
+  </si>
+  <si>
+    <t>e2PsAellOiI</t>
+  </si>
+  <si>
+    <t>They Have Heard Thy Name</t>
+  </si>
+  <si>
+    <t>https://www.youtube.com/watch?v=e2PsAellOiI</t>
+  </si>
+  <si>
+    <t>yD6eVsvBf5Y</t>
+  </si>
+  <si>
+    <t>https://www.youtube.com/watch?v=yD6eVsvBf5Y</t>
+  </si>
+  <si>
+    <t>k5wXErvuWZU</t>
+  </si>
+  <si>
+    <t>When My Dream's Dream is Done</t>
+  </si>
+  <si>
+    <t>https://www.youtube.com/watch?v=k5wXErvuWZU</t>
+  </si>
+  <si>
+    <t>b1iXTbsaK60</t>
+  </si>
+  <si>
+    <t>https://www.youtube.com/watch?v=b1iXTbsaK60</t>
+  </si>
+  <si>
+    <t>Au5yOzLvxnI</t>
+  </si>
+  <si>
+    <t>https://www.youtube.com/watch?v=Au5yOzLvxnI</t>
+  </si>
+  <si>
+    <t>XO-VoGLqqSE</t>
+  </si>
+  <si>
+    <t>https://www.youtube.com/watch?v=XO-VoGLqqSE</t>
+  </si>
+  <si>
+    <t>L2fNKupQTSQ</t>
+  </si>
+  <si>
+    <t>https://www.youtube.com/watch?v=L2fNKupQTSQ</t>
+  </si>
+  <si>
+    <t>3-5XODAmWbA</t>
+  </si>
+  <si>
+    <t>https://www.youtube.com/watch?v=3-5XODAmWbA</t>
+  </si>
+  <si>
+    <t>sey0eWyRj94</t>
+  </si>
+  <si>
+    <t>https://www.youtube.com/watch?v=sey0eWyRj94</t>
+  </si>
+  <si>
+    <t>KtV9EdJv9B0</t>
+  </si>
+  <si>
+    <t>https://www.youtube.com/watch?v=KtV9EdJv9B0</t>
+  </si>
+  <si>
+    <t>Eiw1-Tgw6Uw</t>
+  </si>
+  <si>
+    <t>https://www.youtube.com/watch?v=Eiw1-Tgw6Uw</t>
+  </si>
+  <si>
+    <t>hZb8jkVwDcc</t>
+  </si>
+  <si>
+    <t>Will That Day Come to Me, Mother</t>
+  </si>
+  <si>
+    <t>https://www.youtube.com/watch?v=hZb8jkVwDcc</t>
+  </si>
+  <si>
+    <t>w4t5Rp7ksh0</t>
+  </si>
+  <si>
+    <t>https://www.youtube.com/watch?v=w4t5Rp7ksh0</t>
+  </si>
+  <si>
+    <t>9mZuIDNwLG8</t>
+  </si>
+  <si>
+    <t>https://www.youtube.com/watch?v=9mZuIDNwLG8</t>
+  </si>
+  <si>
+    <t>R3oN5u57Sdg</t>
+  </si>
+  <si>
+    <t>https://www.youtube.com/watch?v=R3oN5u57Sdg</t>
+  </si>
+  <si>
+    <t>nicK6v5xVkU</t>
+  </si>
+  <si>
+    <t>https://www.youtube.com/watch?v=nicK6v5xVkU</t>
+  </si>
+  <si>
+    <t>3GJSJPBwAS8</t>
+  </si>
+  <si>
+    <t>https://www.youtube.com/watch?v=3GJSJPBwAS8</t>
+  </si>
+  <si>
+    <t>ESKVdyY4ZYY</t>
+  </si>
+  <si>
+    <t>https://www.youtube.com/watch?v=ESKVdyY4ZYY</t>
+  </si>
+  <si>
+    <t>_yx6ZK6EqOU</t>
+  </si>
+  <si>
+    <t>Ever-New Joy</t>
+  </si>
+  <si>
+    <t>https://www.youtube.com/watch?v=_yx6ZK6EqOU</t>
+  </si>
+  <si>
+    <t>rRmCDUAG6Ek</t>
+  </si>
+  <si>
+    <t>https://www.youtube.com/watch?v=rRmCDUAG6Ek</t>
+  </si>
+  <si>
+    <t>42frmqga5m0</t>
+  </si>
+  <si>
+    <t>https://www.youtube.com/watch?v=42frmqga5m0</t>
+  </si>
+  <si>
+    <t>KEvp3toAZeQ</t>
+  </si>
+  <si>
+    <t>Wake, Yet Wake, O My Saint</t>
+  </si>
+  <si>
+    <t>https://www.youtube.com/watch?v=KEvp3toAZeQ</t>
+  </si>
+  <si>
+    <t>5XiAaGgGklQ</t>
+  </si>
+  <si>
+    <t>https://www.youtube.com/watch?v=5XiAaGgGklQ</t>
+  </si>
+  <si>
+    <t>Jdoz-xxcHKA</t>
+  </si>
+  <si>
+    <t>https://www.youtube.com/watch?v=Jdoz-xxcHKA</t>
+  </si>
+  <si>
+    <t>7Y3W6bqoJ8k</t>
+  </si>
+  <si>
+    <t>He Who Knows</t>
+  </si>
+  <si>
+    <t>https://www.youtube.com/watch?v=7Y3W6bqoJ8k</t>
+  </si>
+  <si>
+    <t>zgxviHCoyPs</t>
+  </si>
+  <si>
+    <t>Desire, My Great Enemy</t>
+  </si>
+  <si>
+    <t>https://www.youtube.com/watch?v=zgxviHCoyPs</t>
+  </si>
+  <si>
+    <t>a4ZxVychm90</t>
+  </si>
+  <si>
+    <t>https://www.youtube.com/watch?v=a4ZxVychm90</t>
+  </si>
+  <si>
+    <t>Qn4Wmndg3vQ</t>
+  </si>
+  <si>
+    <t>https://www.youtube.com/watch?v=Qn4Wmndg3vQ</t>
+  </si>
+  <si>
+    <t>bYz_XyHsJKI</t>
+  </si>
+  <si>
+    <t>Polestar of My Life - O God Beautiful</t>
+  </si>
+  <si>
+    <t>https://www.youtube.com/watch?v=bYz_XyHsJKI</t>
+  </si>
+  <si>
+    <t>jijHOc0R-4g</t>
+  </si>
+  <si>
+    <t>https://www.youtube.com/watch?v=jijHOc0R-4g</t>
+  </si>
+  <si>
+    <t>jNqrEAWVLNE</t>
+  </si>
+  <si>
+    <t>https://www.youtube.com/watch?v=jNqrEAWVLNE</t>
+  </si>
+  <si>
+    <t>Nt3urPc2tkw</t>
+  </si>
+  <si>
+    <t>Satchidananda Guru</t>
+  </si>
+  <si>
+    <t>https://www.youtube.com/watch?v=Nt3urPc2tkw</t>
+  </si>
+  <si>
+    <t>zm2TRrZbLqI</t>
+  </si>
+  <si>
+    <t>https://www.youtube.com/watch?v=zm2TRrZbLqI</t>
+  </si>
+  <si>
+    <t>BdEtD_AN_Sc</t>
+  </si>
+  <si>
+    <t>Radhe Shyam</t>
+  </si>
+  <si>
+    <t>https://www.youtube.com/watch?v=BdEtD_AN_Sc</t>
+  </si>
+  <si>
+    <t>XmQasAzmxCU</t>
+  </si>
+  <si>
+    <t>Blue Lotus Feet - Om Chant</t>
+  </si>
+  <si>
+    <t>https://www.youtube.com/watch?v=XmQasAzmxCU</t>
+  </si>
+  <si>
+    <t>jI5iAnceXZ4</t>
+  </si>
+  <si>
+    <t>https://www.youtube.com/watch?v=jI5iAnceXZ4</t>
+  </si>
+  <si>
+    <t>6BDZL9e4zDg</t>
+  </si>
+  <si>
+    <t>https://www.youtube.com/watch?v=6BDZL9e4zDg</t>
+  </si>
+  <si>
+    <t>c5OBhhEf5FA</t>
+  </si>
+  <si>
+    <t>https://www.youtube.com/watch?v=c5OBhhEf5FA</t>
+  </si>
+  <si>
+    <t>gx_VaV_mScU</t>
+  </si>
+  <si>
+    <t>Who Is in My Temple</t>
+  </si>
+  <si>
+    <t>https://www.youtube.com/watch?v=gx_VaV_mScU</t>
+  </si>
+  <si>
+    <t>COhHyD2U-r8</t>
+  </si>
+  <si>
+    <t>https://www.youtube.com/watch?v=COhHyD2U-r8</t>
+  </si>
+  <si>
+    <t>z5xNm-VYLfM</t>
+  </si>
+  <si>
+    <t>Hare Krishna, Hare Ram</t>
+  </si>
+  <si>
+    <t>https://www.youtube.com/watch?v=z5xNm-VYLfM</t>
+  </si>
+  <si>
+    <t>raQEPqlHzTQ</t>
+  </si>
+  <si>
+    <t>https://www.youtube.com/watch?v=raQEPqlHzTQ</t>
+  </si>
+  <si>
+    <t>C--HVQLIxe0</t>
+  </si>
+  <si>
+    <t>He Bhagavan</t>
+  </si>
+  <si>
+    <t>https://www.youtube.com/watch?v=C--HVQLIxe0</t>
+  </si>
+  <si>
+    <t>gj-dth2Crl0</t>
+  </si>
+  <si>
+    <t>https://www.youtube.com/watch?v=gj-dth2Crl0</t>
+  </si>
+  <si>
+    <t>LbdlrkDveZM</t>
+  </si>
+  <si>
+    <t>Swami Ram Tirtha's Song</t>
+  </si>
+  <si>
+    <t>https://www.youtube.com/watch?v=LbdlrkDveZM</t>
+  </si>
+  <si>
+    <t>UegOUQ97PWs</t>
+  </si>
+  <si>
+    <t>https://www.youtube.com/watch?v=UegOUQ97PWs</t>
+  </si>
+  <si>
+    <t>hrLrdTdTsr4</t>
+  </si>
+  <si>
+    <t>https://www.youtube.com/watch?v=hrLrdTdTsr4</t>
+  </si>
+  <si>
+    <t>c5C_4NTjiZs</t>
+  </si>
+  <si>
+    <t>Jai Guru - Radha Govinda Jai</t>
+  </si>
+  <si>
+    <t>https://www.youtube.com/watch?v=c5C_4NTjiZs</t>
+  </si>
+  <si>
+    <t>kzncvlw781g</t>
+  </si>
+  <si>
+    <t>Aum Chant</t>
+  </si>
+  <si>
+    <t>https://www.youtube.com/watch?v=kzncvlw781g</t>
+  </si>
+  <si>
+    <t>Fa0Q3XfS3Cc</t>
+  </si>
+  <si>
+    <t>https://www.youtube.com/watch?v=Fa0Q3XfS3Cc</t>
+  </si>
+  <si>
+    <t>5uK-ri-mMEE</t>
+  </si>
+  <si>
+    <t>https://www.youtube.com/watch?v=5uK-ri-mMEE</t>
+  </si>
+  <si>
+    <t>km2XWg7aHGs</t>
+  </si>
+  <si>
+    <t>Divine Mother's Song to the Devotee</t>
+  </si>
+  <si>
+    <t>https://www.youtube.com/watch?v=km2XWg7aHGs</t>
+  </si>
+  <si>
+    <t>eqwc5nqtqbo</t>
+  </si>
+  <si>
+    <t>https://www.youtube.com/watch?v=eqwc5nqtqbo</t>
+  </si>
+  <si>
+    <t>MHjKi1oFeIY</t>
+  </si>
+  <si>
+    <t>https://www.youtube.com/watch?v=MHjKi1oFeIY</t>
+  </si>
+  <si>
+    <t>AqFNf8QiRG4</t>
+  </si>
+  <si>
+    <t>https://www.youtube.com/watch?v=AqFNf8QiRG4</t>
+  </si>
+  <si>
+    <t>8OXYnWbPSMo</t>
+  </si>
+  <si>
+    <t>https://www.youtube.com/watch?v=8OXYnWbPSMo</t>
+  </si>
+  <si>
+    <t>UIq6YRA7HGE</t>
+  </si>
+  <si>
+    <t>https://www.youtube.com/watch?v=UIq6YRA7HGE</t>
+  </si>
+  <si>
+    <t>SsIi9Ba4h2Y</t>
+  </si>
+  <si>
+    <t>https://www.youtube.com/watch?v=SsIi9Ba4h2Y</t>
+  </si>
+  <si>
+    <t>P_QZSGjaK9Y</t>
+  </si>
+  <si>
+    <t>https://www.youtube.com/watch?v=P_QZSGjaK9Y</t>
+  </si>
+  <si>
+    <t>mXZazhOSN84</t>
+  </si>
+  <si>
+    <t>https://www.youtube.com/watch?v=mXZazhOSN84</t>
+  </si>
+  <si>
+    <t>Mj2w2WB9WwI</t>
+  </si>
+  <si>
+    <t>https://www.youtube.com/watch?v=Mj2w2WB9WwI</t>
+  </si>
+  <si>
+    <t>s7redy0-Law</t>
+  </si>
+  <si>
+    <t>https://www.youtube.com/watch?v=s7redy0-Law</t>
+  </si>
+  <si>
+    <t>6px3yz6gA-Y</t>
+  </si>
+  <si>
+    <t>https://www.youtube.com/watch?v=6px3yz6gA-Y</t>
+  </si>
+  <si>
+    <t>6bWOCm9OeTI</t>
+  </si>
+  <si>
+    <t>O God Beautiful - Aum Chant</t>
+  </si>
+  <si>
+    <t>https://www.youtube.com/watch?v=6bWOCm9OeTI</t>
+  </si>
+  <si>
+    <t>Prayer, Dawn|Mejda | Songs of My Heart|Kirtan</t>
+  </si>
+  <si>
+    <t>God, Beautiful, Paramhansa, Yogananda|Mejda | Songs of My Heart|Kirtan</t>
+  </si>
+  <si>
+    <t>Hari, Sundara|Mejda | Songs of My Heart|Kirtan</t>
+  </si>
+  <si>
+    <t>What, Lightning, Flash|Mejda | Songs of My Heart|Kirtan</t>
+  </si>
+  <si>
+    <t>God, Christ, Gurus|Mejda | Songs of My Heart|Kirtan</t>
+  </si>
+  <si>
+    <t>Prayer, Noon|Mejda | Songs of My Heart|Kirtan</t>
+  </si>
+  <si>
+    <t>Hound, Heaven|Mejda | Songs of My Heart|Kirtan</t>
+  </si>
+  <si>
+    <t>CloudColored, Christ|Mejda | Songs of My Heart|Kirtan</t>
+  </si>
+  <si>
+    <t>Divine, Mothers, Song, Devotee|Mejda | Songs of My Heart|Kirtan</t>
+  </si>
+  <si>
+    <t>Temple, Silence|Mejda | Songs of My Heart|Kirtan</t>
+  </si>
+  <si>
+    <t>Song, India|Mejda | Songs of My Heart|Kirtan</t>
+  </si>
+  <si>
+    <t>Shanti, Mundiray|Mejda | Songs of My Heart|Kirtan</t>
+  </si>
+  <si>
+    <t>Prayer, Eventide|Mejda | Songs of My Heart|Kirtan</t>
+  </si>
+  <si>
+    <t>Will, Thine, Always|Mejda | Songs of My Heart|Kirtan</t>
+  </si>
+  <si>
+    <t>Main, Tera, Hamesha|Mejda | Songs of My Heart|Kirtan</t>
+  </si>
+  <si>
+    <t>Not, Dry, Ocean, Love, Paramhansa|Mejda | Songs of My Heart|Kirtan</t>
+  </si>
+  <si>
+    <t>Prayer, Night|Mejda | Songs of My Heart|Kirtan</t>
+  </si>
+  <si>
+    <t>Deliver, From, Delusion|I am the sky | Instrumental|Kirtan</t>
+  </si>
+  <si>
+    <t>Who, Temple|I am the sky | Instrumental|Kirtan</t>
+  </si>
+  <si>
+    <t>Thy, Feet|I am the sky | Instrumental|Kirtan</t>
+  </si>
+  <si>
+    <t>Bubble, Make, Sea|I am the sky | Instrumental|Kirtan</t>
+  </si>
+  <si>
+    <t>Valley, Sorrow|I am the sky | Instrumental|Kirtan</t>
+  </si>
+  <si>
+    <t>Krishna, Blue|I am the sky | Instrumental|Kirtan</t>
+  </si>
+  <si>
+    <t>Sky|I am the sky | Instrumental|Kirtan</t>
+  </si>
+  <si>
+    <t>Where, There, Love|I am the sky | Instrumental|Kirtan</t>
+  </si>
+  <si>
+    <t>From, This, Sleep, Lord|I am the sky | Instrumental|Kirtan</t>
+  </si>
+  <si>
+    <t>Land, Beyond, Dreams|I am the sky | Instrumental|Kirtan</t>
+  </si>
+  <si>
+    <t>Listen|I am the sky | Instrumental|Kirtan</t>
+  </si>
+  <si>
+    <t>When, Thy, Song, Flows, Through|I am the sky | Instrumental|Kirtan</t>
+  </si>
+  <si>
+    <t>Today, Mind, Has, Dived|I am the sky | Instrumental|Kirtan</t>
+  </si>
+  <si>
+    <t>Song|I am the sky | Instrumental|Kirtan</t>
+  </si>
+  <si>
+    <t>Thou, King, Infinite|I am the sky | Instrumental|Kirtan</t>
+  </si>
+  <si>
+    <t>Kali|I am the sky | Instrumental|Kirtan</t>
+  </si>
+  <si>
+    <t>Divine, Gypsy|I am the sky | Instrumental|Kirtan</t>
+  </si>
+  <si>
+    <t>Thousands, Suns|I am the sky | Instrumental|Kirtan</t>
+  </si>
+  <si>
+    <t>Thou, Blue, Sky|I am the sky | Instrumental|Kirtan</t>
+  </si>
+  <si>
+    <t>God, Beautiful|I am the sky | Instrumental|Kirtan</t>
+  </si>
+  <si>
+    <t>Hymn, Brahma|I am the sky | Instrumental|Kirtan</t>
+  </si>
+  <si>
+    <t>Thy, Feet|At Thy Feet | SRF Nuns|Kirtan</t>
+  </si>
+  <si>
+    <t>Bubble, Make, Sea|At Thy Feet | SRF Nuns|Kirtan</t>
+  </si>
+  <si>
+    <t>Door, Heart|At Thy Feet | SRF Nuns|Kirtan</t>
+  </si>
+  <si>
+    <t>CloudColored, Christ|At Thy Feet | SRF Nuns|Kirtan</t>
+  </si>
+  <si>
+    <t>Dawn, Chant|At Thy Feet | SRF Nuns|Kirtan</t>
+  </si>
+  <si>
+    <t>Sri, Guru, Sharanam|At Thy Feet | SRF Nuns|Kirtan</t>
+  </si>
+  <si>
+    <t>Light, Lamp, Thy, Love|At Thy Feet | SRF Nuns|Kirtan</t>
+  </si>
+  <si>
+    <t>Sky|At Thy Feet | SRF Nuns|Kirtan</t>
+  </si>
+  <si>
+    <t>Who, Temple|At Thy Feet | SRF Nuns|Kirtan</t>
+  </si>
+  <si>
+    <t>Murali, Krishna|At Thy Feet | SRF Nuns|Kirtan</t>
+  </si>
+  <si>
+    <t>Land, Beyond, Dreams|At Thy Feet | SRF Nuns|Kirtan</t>
+  </si>
+  <si>
+    <t>Give, You, Soul, Call|At Thy Feet | SRF Nuns|Kirtan</t>
+  </si>
+  <si>
+    <t>Thousands, Suns|At Thy Feet | SRF Nuns|Kirtan</t>
+  </si>
+  <si>
+    <t>Thou, Art, Life|At Thy Feet | SRF Nuns|Kirtan</t>
+  </si>
+  <si>
+    <t>Jaya|At Thy Feet | SRF Nuns|Kirtan</t>
+  </si>
+  <si>
+    <t>Jai, Guru|At Thy Feet | SRF Nuns|Kirtan</t>
+  </si>
+  <si>
+    <t>Thou, Blue, Sky|At Thy Feet | SRF Nuns|Kirtan</t>
+  </si>
+  <si>
+    <t>Radha, Krishna, Govinda|At Thy Feet | SRF Nuns|Kirtan</t>
+  </si>
+  <si>
+    <t>Will, Sing, Thy, Name|At Thy Feet | SRF Nuns|Kirtan</t>
+  </si>
+  <si>
+    <t>Guru, Hamare|Guru Sharanam|Kirtan</t>
+  </si>
+  <si>
+    <t>Help, Come, Back|Guru Sharanam|Kirtan</t>
+  </si>
+  <si>
+    <t>Tero, Naam|Guru Sharanam|Kirtan</t>
+  </si>
+  <si>
+    <t>God, Krishna, Christ, Gurus|Guru Sharanam|Kirtan</t>
+  </si>
+  <si>
+    <t>Tat, Sat|Guru Sharanam|Kirtan</t>
+  </si>
+  <si>
+    <t>Namo|Guru Sharanam|Kirtan</t>
+  </si>
+  <si>
+    <t>Thou, Art, Life|Thou Art My Life | Instrumental|Kirtan</t>
+  </si>
+  <si>
+    <t>Deliver, From, Delusion|Thou Art My Life | Instrumental|Kirtan</t>
+  </si>
+  <si>
+    <t>Divine, Mothers, Song, Devotee|Thou Art My Life | Instrumental|Kirtan</t>
+  </si>
+  <si>
+    <t>Krishna, Blue|Thou Art My Life | Instrumental|Kirtan</t>
+  </si>
+  <si>
+    <t>Where, There, Love|Thou Art My Life | Instrumental|Kirtan</t>
+  </si>
+  <si>
+    <t>From, This, Sleep, Lord|Thou Art My Life | Instrumental|Kirtan</t>
+  </si>
+  <si>
+    <t>CloudColored, Christ|Thou Art My Life | Instrumental|Kirtan</t>
+  </si>
+  <si>
+    <t>Polestar, Life|Thou Art My Life | Instrumental|Kirtan</t>
+  </si>
+  <si>
+    <t>Valley, Sorrow|Thou Art My Life | Instrumental|Kirtan</t>
+  </si>
+  <si>
+    <t>Blue, Lotus, Feet|Thou Art My Life | Instrumental|Kirtan</t>
+  </si>
+  <si>
+    <t>When, Thy, Song, Flows, Though|Thou Art My Life | Instrumental|Kirtan</t>
+  </si>
+  <si>
+    <t>Hymn, Brahma|Thou Art My Life | Instrumental|Kirtan</t>
+  </si>
+  <si>
+    <t>Suno, Mere, AtmaGan, Thy, Feet|Shanti Mandir |Brahmacharini Mirabai|Kirtan</t>
+  </si>
+  <si>
+    <t>Nind, Prabhu, From, This, Sleep|Shanti Mandir |Brahmacharini Mirabai|Kirtan</t>
+  </si>
+  <si>
+    <t>Dukh, Vadi, Valley, Sorrow|Shanti Mandir |Brahmacharini Mirabai|Kirtan</t>
+  </si>
+  <si>
+    <t>Nitya, Navin, Anand, Ever, New|Shanti Mandir |Brahmacharini Mirabai|Kirtan</t>
+  </si>
+  <si>
+    <t>Shanti, Mandir, Temple, Silence|Shanti Mandir |Brahmacharini Mirabai|Kirtan</t>
+  </si>
+  <si>
+    <t>Shyamal, Krishna, CloudColored, Christ|Shanti Mandir |Brahmacharini Mirabai|Kirtan</t>
+  </si>
+  <si>
+    <t>Niras, Karo, Mere, Prem, Sagar|Shanti Mandir |Brahmacharini Mirabai|Kirtan</t>
+  </si>
+  <si>
+    <t>Tujhe, Atma, Pukar, Give, You|Shanti Mandir |Brahmacharini Mirabai|Kirtan</t>
+  </si>
+  <si>
+    <t>Kaun, Hai, Mere, Mandir, Who|Shanti Mandir |Brahmacharini Mirabai|Kirtan</t>
+  </si>
+  <si>
+    <t>Nil, Kamal, Charan, Blue, Lotus|Shanti Mandir |Brahmacharini Mirabai|Kirtan</t>
+  </si>
+  <si>
+    <t>Guru, Stuti, Slokas, Bhagavan, Praise|Shanti Mandir |Brahmacharini Mirabai|Kirtan</t>
+  </si>
+  <si>
+    <t>Dhyan, Karo, Meditate|Shanti Mandir |Brahmacharini Mirabai|Kirtan</t>
+  </si>
+  <si>
+    <t>Bhaja, Mana, Pray, Night, Day|Shanti Mandir |Brahmacharini Mirabai|Kirtan</t>
+  </si>
+  <si>
+    <t>Sri, Guru, Sharanam, Surrender|Shanti Mandir |Brahmacharini Mirabai|Kirtan</t>
+  </si>
+  <si>
+    <t>Krishna, Stuti, Sloka, Gopal, Giridhari|Shanti Mandir |Brahmacharini Mirabai|Kirtan</t>
+  </si>
+  <si>
+    <t>Bhajan, Karungi, Tumhara, Lord, Will|Shanti Mandir |Brahmacharini Mirabai|Kirtan</t>
+  </si>
+  <si>
+    <t>Hare, Krishna|Shanti Mandir |Brahmacharini Mirabai|Kirtan</t>
+  </si>
+  <si>
+    <t>Jai, Jagadish, Hare, Arati|Shanti Mandir |Brahmacharini Mirabai|Kirtan</t>
+  </si>
+  <si>
+    <t>Land, Beyond, Dreams|In the Land Beyond My Dreams | Instrumental|Kirtan</t>
+  </si>
+  <si>
+    <t>Blue, Lotus, Feet|In the Land Beyond My Dreams | Instrumental|Kirtan</t>
+  </si>
+  <si>
+    <t>From, This, Sleep, Lord|In the Land Beyond My Dreams | Instrumental|Kirtan</t>
+  </si>
+  <si>
+    <t>Not, Dry, Ocean, Love|In the Land Beyond My Dreams | Instrumental|Kirtan</t>
+  </si>
+  <si>
+    <t>Light, Lamp, Thy, Love|In the Land Beyond My Dreams | Instrumental|Kirtan</t>
+  </si>
+  <si>
+    <t>Thou, Art, Life|In the Land Beyond My Dreams | Instrumental|Kirtan</t>
+  </si>
+  <si>
+    <t>Valley, Sorrow|In the Land Beyond My Dreams | Instrumental|Kirtan</t>
+  </si>
+  <si>
+    <t>Receive, Thy, Lap|In the Land Beyond My Dreams | Instrumental|Kirtan</t>
+  </si>
+  <si>
+    <t>Deliver, From, Delusion|In the Land Beyond My Dreams | Instrumental|Kirtan</t>
+  </si>
+  <si>
+    <t>They, Have, Heard, Thy, Name|In the Land Beyond My Dreams | Instrumental|Kirtan</t>
+  </si>
+  <si>
+    <t>When, Thy, Song, Flows, Through|In the Land Beyond My Dreams | Instrumental|Kirtan</t>
+  </si>
+  <si>
+    <t>When, Dreams, Dream, Done|In the Land Beyond My Dreams | Instrumental|Kirtan</t>
+  </si>
+  <si>
+    <t>Come, Listen, Soul, Song|In the Land Beyond My Dreams | Instrumental|Kirtan</t>
+  </si>
+  <si>
+    <t>Give, You, Soul, Call|In the Land Beyond My Dreams | Instrumental|Kirtan</t>
+  </si>
+  <si>
+    <t>Will, Thine, Always|In the Land Beyond My Dreams | Instrumental|Kirtan</t>
+  </si>
+  <si>
+    <t>Where, There, Love|In the Land Beyond My Dreams | Instrumental|Kirtan</t>
+  </si>
+  <si>
+    <t>Temple, Silence|In the Land Beyond My Dreams | Instrumental|Kirtan</t>
+  </si>
+  <si>
+    <t>Wink, Has, Not, Touched, Eyes|In the Land Beyond My Dreams | Instrumental|Kirtan</t>
+  </si>
+  <si>
+    <t>I Am the Sky|In the Land Beyond My Dreams | Instrumental|Kirtan</t>
+  </si>
+  <si>
+    <t>Thou, King, Infinite|In the Land Beyond My Dreams | Instrumental|Kirtan</t>
+  </si>
+  <si>
+    <t>Will, That, Day, Come, Mother|In the Land Beyond My Dreams | Instrumental|Kirtan</t>
+  </si>
+  <si>
+    <t>Bubble, Make, Sea|In the Land Beyond My Dreams | Instrumental|Kirtan</t>
+  </si>
+  <si>
+    <t>Hymn, Brahma|In the Land Beyond My Dreams | Instrumental|Kirtan</t>
+  </si>
+  <si>
+    <t>From, This, Sleep, Lord|Where Golden Dreams Dwell | Instrumental|Kirtan</t>
+  </si>
+  <si>
+    <t>Land, Beyond, Dreams|Where Golden Dreams Dwell | Instrumental|Kirtan</t>
+  </si>
+  <si>
+    <t>Come, Listen, Soul, Song|Where Golden Dreams Dwell | Instrumental|Kirtan</t>
+  </si>
+  <si>
+    <t>Search, Him, Out, Secret|Where Golden Dreams Dwell | Instrumental|Kirtan</t>
+  </si>
+  <si>
+    <t>EverNew, Joy|Where Golden Dreams Dwell | Instrumental|Kirtan</t>
+  </si>
+  <si>
+    <t>Dawn, Chant|Where Golden Dreams Dwell | Instrumental|Kirtan</t>
+  </si>
+  <si>
+    <t>What, Lightning, Flash|Where Golden Dreams Dwell | Instrumental|Kirtan</t>
+  </si>
+  <si>
+    <t>Wake, Yet, Saint|Where Golden Dreams Dwell | Instrumental|Kirtan</t>
+  </si>
+  <si>
+    <t>Will, That, Day, Come, Mother|Where Golden Dreams Dwell | Instrumental|Kirtan</t>
+  </si>
+  <si>
+    <t>Thou, Blue, Sky|Where Golden Dreams Dwell | Instrumental|Kirtan</t>
+  </si>
+  <si>
+    <t>Who, Knows|Where Golden Dreams Dwell | Instrumental|Kirtan</t>
+  </si>
+  <si>
+    <t>Desire, Great, Enemy|Where Golden Dreams Dwell | Instrumental|Kirtan</t>
+  </si>
+  <si>
+    <t>When, Dreams, Dream, Done|Where Golden Dreams Dwell | Instrumental|Kirtan</t>
+  </si>
+  <si>
+    <t>Hymn, Brahma|When My Dream's Dream is Done | SRF Nuns|Kirtan</t>
+  </si>
+  <si>
+    <t>Polestar, Life, God, Beautiful|When My Dream's Dream is Done | SRF Nuns|Kirtan</t>
+  </si>
+  <si>
+    <t>Spirit, Nature|When My Dream's Dream is Done | SRF Nuns|Kirtan</t>
+  </si>
+  <si>
+    <t>When, Dreams, Dream, Done|When My Dream's Dream is Done | SRF Nuns|Kirtan</t>
+  </si>
+  <si>
+    <t>Satchidananda, Guru|When My Dream's Dream is Done | SRF Nuns|Kirtan</t>
+  </si>
+  <si>
+    <t>Listen|When My Dream's Dream is Done | SRF Nuns|Kirtan</t>
+  </si>
+  <si>
+    <t>Radhe, Shyam|When My Dream's Dream is Done | SRF Nuns|Kirtan</t>
+  </si>
+  <si>
+    <t>Blue, Lotus, Feet, Chant|When My Dream's Dream is Done | SRF Nuns|Kirtan</t>
+  </si>
+  <si>
+    <t>Will, Sing, Thy, Name|I Will Sing Thy Name|Kirtan</t>
+  </si>
+  <si>
+    <t>Search, Him, Out, Secret|I Will Sing Thy Name|Kirtan</t>
+  </si>
+  <si>
+    <t>Deliver, From, Delusion|I Will Sing Thy Name|Kirtan</t>
+  </si>
+  <si>
+    <t>Who, Temple|I Will Sing Thy Name|Kirtan</t>
+  </si>
+  <si>
+    <t>Spirit, Nature|I Will Sing Thy Name|Kirtan</t>
+  </si>
+  <si>
+    <t>Hare, Krishna, Ram|I Will Sing Thy Name|Kirtan</t>
+  </si>
+  <si>
+    <t>Valley, Sorrow|I Will Sing Thy Name|Kirtan</t>
+  </si>
+  <si>
+    <t>Bhagavan|I Will Sing Thy Name|Kirtan</t>
+  </si>
+  <si>
+    <t>Light, Lamp, Thy, Love|I Will Sing Thy Name|Kirtan</t>
+  </si>
+  <si>
+    <t>Swami, Ram, Tirthas, Song|I Will Sing Thy Name|Kirtan</t>
+  </si>
+  <si>
+    <t>Divine, Gypsy|I Will Sing Thy Name|Kirtan</t>
+  </si>
+  <si>
+    <t>Wink, Has, Not, Touched, Eyes|The Divine Gypsy | Instrunmental|Kirtan</t>
+  </si>
+  <si>
+    <t>Jai, Guru, Radha, Govinda|The Divine Gypsy | Instrunmental|Kirtan</t>
+  </si>
+  <si>
+    <t>Aum, Chant|The Divine Gypsy | Instrunmental|Kirtan</t>
+  </si>
+  <si>
+    <t>Divine, Gypsy|The Divine Gypsy | Instrunmental|Kirtan</t>
+  </si>
+  <si>
+    <t>Will, Thine, Always|The Divine Gypsy | Instrunmental|Kirtan</t>
+  </si>
+  <si>
+    <t>Divine, Mothers, Song, Devotee|The Divine Gypsy | Instrunmental|Kirtan</t>
+  </si>
+  <si>
+    <t>Thousands, Suns|The Divine Gypsy | Instrunmental|Kirtan</t>
+  </si>
+  <si>
+    <t>They, Have, Heard, Thy, Name|The Divine Gypsy | Instrunmental|Kirtan</t>
+  </si>
+  <si>
+    <t>Sky|The Divine Gypsy | Instrunmental|Kirtan</t>
+  </si>
+  <si>
+    <t>God, Beautiful|The Divine Gypsy | Instrunmental|Kirtan</t>
+  </si>
+  <si>
+    <t>Jai, Guru|When Thy Song Flows Through Me |SRF Monks|Kirtan</t>
+  </si>
+  <si>
+    <t>Thou, Art, Life|When Thy Song Flows Through Me |SRF Monks|Kirtan</t>
+  </si>
+  <si>
+    <t>Door, Heart|When Thy Song Flows Through Me |SRF Monks|Kirtan</t>
+  </si>
+  <si>
+    <t>When, Thy, Song, Flows, Through|When Thy Song Flows Through Me |SRF Monks|Kirtan</t>
+  </si>
+  <si>
+    <t>Sky|When Thy Song Flows Through Me |SRF Monks|Kirtan</t>
+  </si>
+  <si>
+    <t>Polestar, Life|When Thy Song Flows Through Me |SRF Monks|Kirtan</t>
+  </si>
+  <si>
+    <t>Blue, Lotus, Feet|When Thy Song Flows Through Me |SRF Monks|Kirtan</t>
+  </si>
+  <si>
+    <t>God, Beautiful, Aum, Chant|When Thy Song Flows Through Me |SRF Monks|Kirtan</t>
   </si>
 </sst>
 </file>
@@ -11387,13 +13115,14 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{EE52D9B7-0D33-6C4B-ABD2-124A93043E14}">
-  <dimension ref="A1:D1159"/>
+  <dimension ref="A1:D1325"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="44" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="126" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="34" customWidth="1"/>
     <col min="3" max="3" width="45.33203125" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="62.83203125" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="62.83203125" customWidth="1"/>
+    <col min="6" max="6" width="12.1640625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:4" x14ac:dyDescent="0.2">
@@ -27619,8 +29348,2332 @@
         <v>3657</v>
       </c>
     </row>
+    <row r="1160" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A1160" t="s">
+        <v>3658</v>
+      </c>
+      <c r="B1160" t="s">
+        <v>3659</v>
+      </c>
+      <c r="C1160" t="s">
+        <v>3660</v>
+      </c>
+      <c r="D1160" t="s">
+        <v>4068</v>
+      </c>
+    </row>
+    <row r="1161" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A1161" t="s">
+        <v>3661</v>
+      </c>
+      <c r="B1161" t="s">
+        <v>3662</v>
+      </c>
+      <c r="C1161" t="s">
+        <v>3663</v>
+      </c>
+      <c r="D1161" t="s">
+        <v>4069</v>
+      </c>
+    </row>
+    <row r="1162" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A1162" t="s">
+        <v>3664</v>
+      </c>
+      <c r="B1162" t="s">
+        <v>3665</v>
+      </c>
+      <c r="C1162" t="s">
+        <v>3666</v>
+      </c>
+      <c r="D1162" t="s">
+        <v>4070</v>
+      </c>
+    </row>
+    <row r="1163" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A1163" t="s">
+        <v>3667</v>
+      </c>
+      <c r="B1163" t="s">
+        <v>3086</v>
+      </c>
+      <c r="C1163" t="s">
+        <v>3668</v>
+      </c>
+      <c r="D1163" t="s">
+        <v>4071</v>
+      </c>
+    </row>
+    <row r="1164" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A1164" t="s">
+        <v>3669</v>
+      </c>
+      <c r="B1164" t="s">
+        <v>3670</v>
+      </c>
+      <c r="C1164" t="s">
+        <v>3671</v>
+      </c>
+      <c r="D1164" t="s">
+        <v>4072</v>
+      </c>
+    </row>
+    <row r="1165" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A1165" t="s">
+        <v>3672</v>
+      </c>
+      <c r="B1165" t="s">
+        <v>3673</v>
+      </c>
+      <c r="C1165" t="s">
+        <v>3674</v>
+      </c>
+      <c r="D1165" t="s">
+        <v>4073</v>
+      </c>
+    </row>
+    <row r="1166" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A1166" t="s">
+        <v>3675</v>
+      </c>
+      <c r="B1166" t="s">
+        <v>3676</v>
+      </c>
+      <c r="C1166" t="s">
+        <v>3677</v>
+      </c>
+      <c r="D1166" t="s">
+        <v>4074</v>
+      </c>
+    </row>
+    <row r="1167" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A1167" t="s">
+        <v>3678</v>
+      </c>
+      <c r="B1167" t="s">
+        <v>3135</v>
+      </c>
+      <c r="C1167" t="s">
+        <v>3679</v>
+      </c>
+      <c r="D1167" t="s">
+        <v>4075</v>
+      </c>
+    </row>
+    <row r="1168" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A1168" t="s">
+        <v>3680</v>
+      </c>
+      <c r="B1168" t="s">
+        <v>3681</v>
+      </c>
+      <c r="C1168" t="s">
+        <v>3682</v>
+      </c>
+      <c r="D1168" t="s">
+        <v>4076</v>
+      </c>
+    </row>
+    <row r="1169" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A1169" t="s">
+        <v>3683</v>
+      </c>
+      <c r="B1169" t="s">
+        <v>3684</v>
+      </c>
+      <c r="C1169" t="s">
+        <v>3685</v>
+      </c>
+      <c r="D1169" t="s">
+        <v>4077</v>
+      </c>
+    </row>
+    <row r="1170" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A1170" t="s">
+        <v>3686</v>
+      </c>
+      <c r="B1170" t="s">
+        <v>3687</v>
+      </c>
+      <c r="C1170" t="s">
+        <v>3688</v>
+      </c>
+      <c r="D1170" t="s">
+        <v>4078</v>
+      </c>
+    </row>
+    <row r="1171" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A1171" t="s">
+        <v>3689</v>
+      </c>
+      <c r="B1171" t="s">
+        <v>3690</v>
+      </c>
+      <c r="C1171" t="s">
+        <v>3691</v>
+      </c>
+      <c r="D1171" t="s">
+        <v>4079</v>
+      </c>
+    </row>
+    <row r="1172" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A1172" t="s">
+        <v>3692</v>
+      </c>
+      <c r="B1172" t="s">
+        <v>3693</v>
+      </c>
+      <c r="C1172" t="s">
+        <v>3694</v>
+      </c>
+      <c r="D1172" t="s">
+        <v>4080</v>
+      </c>
+    </row>
+    <row r="1173" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A1173" t="s">
+        <v>3695</v>
+      </c>
+      <c r="B1173" t="s">
+        <v>3696</v>
+      </c>
+      <c r="C1173" t="s">
+        <v>3697</v>
+      </c>
+      <c r="D1173" t="s">
+        <v>4081</v>
+      </c>
+    </row>
+    <row r="1174" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A1174" t="s">
+        <v>3698</v>
+      </c>
+      <c r="B1174" t="s">
+        <v>3699</v>
+      </c>
+      <c r="C1174" t="s">
+        <v>3700</v>
+      </c>
+      <c r="D1174" t="s">
+        <v>4082</v>
+      </c>
+    </row>
+    <row r="1175" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A1175" t="s">
+        <v>3701</v>
+      </c>
+      <c r="B1175" t="s">
+        <v>3702</v>
+      </c>
+      <c r="C1175" t="s">
+        <v>3703</v>
+      </c>
+      <c r="D1175" t="s">
+        <v>4083</v>
+      </c>
+    </row>
+    <row r="1176" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A1176" t="s">
+        <v>3704</v>
+      </c>
+      <c r="B1176" t="s">
+        <v>3705</v>
+      </c>
+      <c r="C1176" t="s">
+        <v>3706</v>
+      </c>
+      <c r="D1176" t="s">
+        <v>4084</v>
+      </c>
+    </row>
+    <row r="1177" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A1177" t="s">
+        <v>3707</v>
+      </c>
+      <c r="B1177" t="s">
+        <v>3175</v>
+      </c>
+      <c r="C1177" t="s">
+        <v>3708</v>
+      </c>
+      <c r="D1177" t="s">
+        <v>4085</v>
+      </c>
+    </row>
+    <row r="1178" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A1178" t="s">
+        <v>3709</v>
+      </c>
+      <c r="B1178" t="s">
+        <v>3710</v>
+      </c>
+      <c r="C1178" t="s">
+        <v>3711</v>
+      </c>
+      <c r="D1178" t="s">
+        <v>4086</v>
+      </c>
+    </row>
+    <row r="1179" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A1179" t="s">
+        <v>3712</v>
+      </c>
+      <c r="B1179" t="s">
+        <v>3052</v>
+      </c>
+      <c r="C1179" t="s">
+        <v>3713</v>
+      </c>
+      <c r="D1179" t="s">
+        <v>4087</v>
+      </c>
+    </row>
+    <row r="1180" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A1180" t="s">
+        <v>3714</v>
+      </c>
+      <c r="B1180" t="s">
+        <v>3038</v>
+      </c>
+      <c r="C1180" t="s">
+        <v>3715</v>
+      </c>
+      <c r="D1180" t="s">
+        <v>4088</v>
+      </c>
+    </row>
+    <row r="1181" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A1181" t="s">
+        <v>3716</v>
+      </c>
+      <c r="B1181" t="s">
+        <v>3717</v>
+      </c>
+      <c r="C1181" t="s">
+        <v>3718</v>
+      </c>
+      <c r="D1181" t="s">
+        <v>4089</v>
+      </c>
+    </row>
+    <row r="1182" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A1182" t="s">
+        <v>3719</v>
+      </c>
+      <c r="B1182" t="s">
+        <v>3720</v>
+      </c>
+      <c r="C1182" t="s">
+        <v>3721</v>
+      </c>
+      <c r="D1182" t="s">
+        <v>4090</v>
+      </c>
+    </row>
+    <row r="1183" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A1183" t="s">
+        <v>3722</v>
+      </c>
+      <c r="B1183" t="s">
+        <v>3723</v>
+      </c>
+      <c r="C1183" t="s">
+        <v>3724</v>
+      </c>
+      <c r="D1183" t="s">
+        <v>4091</v>
+      </c>
+    </row>
+    <row r="1184" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A1184" t="s">
+        <v>3725</v>
+      </c>
+      <c r="B1184" t="s">
+        <v>3726</v>
+      </c>
+      <c r="C1184" t="s">
+        <v>3727</v>
+      </c>
+      <c r="D1184" t="s">
+        <v>4092</v>
+      </c>
+    </row>
+    <row r="1185" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A1185" t="s">
+        <v>3728</v>
+      </c>
+      <c r="B1185" t="s">
+        <v>3141</v>
+      </c>
+      <c r="C1185" t="s">
+        <v>3729</v>
+      </c>
+      <c r="D1185" t="s">
+        <v>4093</v>
+      </c>
+    </row>
+    <row r="1186" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A1186" t="s">
+        <v>3730</v>
+      </c>
+      <c r="B1186" t="s">
+        <v>3129</v>
+      </c>
+      <c r="C1186" t="s">
+        <v>3731</v>
+      </c>
+      <c r="D1186" t="s">
+        <v>4094</v>
+      </c>
+    </row>
+    <row r="1187" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A1187" t="s">
+        <v>3732</v>
+      </c>
+      <c r="B1187" t="s">
+        <v>3733</v>
+      </c>
+      <c r="C1187" t="s">
+        <v>3734</v>
+      </c>
+      <c r="D1187" t="s">
+        <v>4095</v>
+      </c>
+    </row>
+    <row r="1188" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A1188" t="s">
+        <v>3735</v>
+      </c>
+      <c r="B1188" t="s">
+        <v>3047</v>
+      </c>
+      <c r="C1188" t="s">
+        <v>3736</v>
+      </c>
+      <c r="D1188" t="s">
+        <v>4096</v>
+      </c>
+    </row>
+    <row r="1189" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A1189" t="s">
+        <v>3737</v>
+      </c>
+      <c r="B1189" t="s">
+        <v>3738</v>
+      </c>
+      <c r="C1189" t="s">
+        <v>3739</v>
+      </c>
+      <c r="D1189" t="s">
+        <v>4097</v>
+      </c>
+    </row>
+    <row r="1190" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A1190" t="s">
+        <v>3740</v>
+      </c>
+      <c r="B1190" t="s">
+        <v>3741</v>
+      </c>
+      <c r="C1190" t="s">
+        <v>3742</v>
+      </c>
+      <c r="D1190" t="s">
+        <v>4098</v>
+      </c>
+    </row>
+    <row r="1191" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A1191" t="s">
+        <v>3743</v>
+      </c>
+      <c r="B1191" t="s">
+        <v>3744</v>
+      </c>
+      <c r="C1191" t="s">
+        <v>3745</v>
+      </c>
+      <c r="D1191" t="s">
+        <v>4099</v>
+      </c>
+    </row>
+    <row r="1192" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A1192" t="s">
+        <v>3746</v>
+      </c>
+      <c r="B1192" t="s">
+        <v>3023</v>
+      </c>
+      <c r="C1192" t="s">
+        <v>3747</v>
+      </c>
+      <c r="D1192" t="s">
+        <v>4100</v>
+      </c>
+    </row>
+    <row r="1193" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A1193" t="s">
+        <v>3748</v>
+      </c>
+      <c r="B1193" t="s">
+        <v>3749</v>
+      </c>
+      <c r="C1193" t="s">
+        <v>3750</v>
+      </c>
+      <c r="D1193" t="s">
+        <v>4101</v>
+      </c>
+    </row>
+    <row r="1194" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A1194" t="s">
+        <v>3751</v>
+      </c>
+      <c r="B1194" t="s">
+        <v>3132</v>
+      </c>
+      <c r="C1194" t="s">
+        <v>3752</v>
+      </c>
+      <c r="D1194" t="s">
+        <v>4102</v>
+      </c>
+    </row>
+    <row r="1195" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A1195" t="s">
+        <v>3753</v>
+      </c>
+      <c r="B1195" t="s">
+        <v>3124</v>
+      </c>
+      <c r="C1195" t="s">
+        <v>3754</v>
+      </c>
+      <c r="D1195" t="s">
+        <v>4103</v>
+      </c>
+    </row>
+    <row r="1196" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A1196" t="s">
+        <v>3755</v>
+      </c>
+      <c r="B1196" t="s">
+        <v>3756</v>
+      </c>
+      <c r="C1196" t="s">
+        <v>3757</v>
+      </c>
+      <c r="D1196" t="s">
+        <v>4104</v>
+      </c>
+    </row>
+    <row r="1197" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A1197" t="s">
+        <v>3758</v>
+      </c>
+      <c r="B1197" t="s">
+        <v>3014</v>
+      </c>
+      <c r="C1197" t="s">
+        <v>3759</v>
+      </c>
+      <c r="D1197" t="s">
+        <v>4105</v>
+      </c>
+    </row>
+    <row r="1198" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A1198" t="s">
+        <v>3760</v>
+      </c>
+      <c r="B1198" t="s">
+        <v>3052</v>
+      </c>
+      <c r="C1198" t="s">
+        <v>3761</v>
+      </c>
+      <c r="D1198" t="s">
+        <v>4106</v>
+      </c>
+    </row>
+    <row r="1199" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A1199" t="s">
+        <v>3762</v>
+      </c>
+      <c r="B1199" t="s">
+        <v>3038</v>
+      </c>
+      <c r="C1199" t="s">
+        <v>3763</v>
+      </c>
+      <c r="D1199" t="s">
+        <v>4107</v>
+      </c>
+    </row>
+    <row r="1200" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A1200" t="s">
+        <v>3764</v>
+      </c>
+      <c r="B1200" t="s">
+        <v>3765</v>
+      </c>
+      <c r="C1200" t="s">
+        <v>3766</v>
+      </c>
+      <c r="D1200" t="s">
+        <v>4108</v>
+      </c>
+    </row>
+    <row r="1201" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A1201" t="s">
+        <v>3767</v>
+      </c>
+      <c r="B1201" t="s">
+        <v>3135</v>
+      </c>
+      <c r="C1201" t="s">
+        <v>3768</v>
+      </c>
+      <c r="D1201" t="s">
+        <v>4109</v>
+      </c>
+    </row>
+    <row r="1202" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A1202" t="s">
+        <v>3769</v>
+      </c>
+      <c r="B1202" t="s">
+        <v>3017</v>
+      </c>
+      <c r="C1202" t="s">
+        <v>3770</v>
+      </c>
+      <c r="D1202" t="s">
+        <v>4110</v>
+      </c>
+    </row>
+    <row r="1203" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A1203" t="s">
+        <v>3771</v>
+      </c>
+      <c r="B1203" t="s">
+        <v>3055</v>
+      </c>
+      <c r="C1203" t="s">
+        <v>3772</v>
+      </c>
+      <c r="D1203" t="s">
+        <v>4111</v>
+      </c>
+    </row>
+    <row r="1204" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A1204" t="s">
+        <v>3773</v>
+      </c>
+      <c r="B1204" t="s">
+        <v>3774</v>
+      </c>
+      <c r="C1204" t="s">
+        <v>3775</v>
+      </c>
+      <c r="D1204" t="s">
+        <v>4112</v>
+      </c>
+    </row>
+    <row r="1205" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A1205" t="s">
+        <v>3776</v>
+      </c>
+      <c r="B1205" t="s">
+        <v>3723</v>
+      </c>
+      <c r="C1205" t="s">
+        <v>3777</v>
+      </c>
+      <c r="D1205" t="s">
+        <v>4113</v>
+      </c>
+    </row>
+    <row r="1206" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A1206" t="s">
+        <v>3778</v>
+      </c>
+      <c r="B1206" t="s">
+        <v>3779</v>
+      </c>
+      <c r="C1206" t="s">
+        <v>3780</v>
+      </c>
+      <c r="D1206" t="s">
+        <v>4114</v>
+      </c>
+    </row>
+    <row r="1207" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A1207" t="s">
+        <v>3781</v>
+      </c>
+      <c r="B1207" t="s">
+        <v>3782</v>
+      </c>
+      <c r="C1207" t="s">
+        <v>3783</v>
+      </c>
+      <c r="D1207" t="s">
+        <v>4115</v>
+      </c>
+    </row>
+    <row r="1208" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A1208" t="s">
+        <v>3784</v>
+      </c>
+      <c r="B1208" t="s">
+        <v>3129</v>
+      </c>
+      <c r="C1208" t="s">
+        <v>3785</v>
+      </c>
+      <c r="D1208" t="s">
+        <v>4116</v>
+      </c>
+    </row>
+    <row r="1209" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A1209" t="s">
+        <v>3786</v>
+      </c>
+      <c r="B1209" t="s">
+        <v>3080</v>
+      </c>
+      <c r="C1209" t="s">
+        <v>3787</v>
+      </c>
+      <c r="D1209" t="s">
+        <v>4117</v>
+      </c>
+    </row>
+    <row r="1210" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A1210" t="s">
+        <v>3788</v>
+      </c>
+      <c r="B1210" t="s">
+        <v>3132</v>
+      </c>
+      <c r="C1210" t="s">
+        <v>3789</v>
+      </c>
+      <c r="D1210" t="s">
+        <v>4118</v>
+      </c>
+    </row>
+    <row r="1211" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A1211" t="s">
+        <v>3790</v>
+      </c>
+      <c r="B1211" t="s">
+        <v>3035</v>
+      </c>
+      <c r="C1211" t="s">
+        <v>3791</v>
+      </c>
+      <c r="D1211" t="s">
+        <v>4119</v>
+      </c>
+    </row>
+    <row r="1212" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A1212" t="s">
+        <v>3792</v>
+      </c>
+      <c r="B1212" t="s">
+        <v>3793</v>
+      </c>
+      <c r="C1212" t="s">
+        <v>3794</v>
+      </c>
+      <c r="D1212" t="s">
+        <v>4120</v>
+      </c>
+    </row>
+    <row r="1213" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A1213" t="s">
+        <v>3795</v>
+      </c>
+      <c r="B1213" t="s">
+        <v>3796</v>
+      </c>
+      <c r="C1213" t="s">
+        <v>3797</v>
+      </c>
+      <c r="D1213" t="s">
+        <v>4121</v>
+      </c>
+    </row>
+    <row r="1214" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A1214" t="s">
+        <v>3798</v>
+      </c>
+      <c r="B1214" t="s">
+        <v>3124</v>
+      </c>
+      <c r="C1214" t="s">
+        <v>3799</v>
+      </c>
+      <c r="D1214" t="s">
+        <v>4122</v>
+      </c>
+    </row>
+    <row r="1215" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A1215" t="s">
+        <v>3800</v>
+      </c>
+      <c r="B1215" t="s">
+        <v>3801</v>
+      </c>
+      <c r="C1215" t="s">
+        <v>3802</v>
+      </c>
+      <c r="D1215" t="s">
+        <v>4123</v>
+      </c>
+    </row>
+    <row r="1216" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A1216" t="s">
+        <v>3803</v>
+      </c>
+      <c r="B1216" t="s">
+        <v>3169</v>
+      </c>
+      <c r="C1216" t="s">
+        <v>3804</v>
+      </c>
+      <c r="D1216" t="s">
+        <v>4124</v>
+      </c>
+    </row>
+    <row r="1217" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A1217" t="s">
+        <v>3805</v>
+      </c>
+      <c r="B1217" t="s">
+        <v>3806</v>
+      </c>
+      <c r="C1217" t="s">
+        <v>3807</v>
+      </c>
+      <c r="D1217" t="s">
+        <v>4125</v>
+      </c>
+    </row>
+    <row r="1218" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A1218" t="s">
+        <v>3808</v>
+      </c>
+      <c r="B1218" t="s">
+        <v>3809</v>
+      </c>
+      <c r="C1218" t="s">
+        <v>3810</v>
+      </c>
+      <c r="D1218" t="s">
+        <v>4126</v>
+      </c>
+    </row>
+    <row r="1219" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A1219" t="s">
+        <v>3811</v>
+      </c>
+      <c r="B1219" t="s">
+        <v>3812</v>
+      </c>
+      <c r="C1219" t="s">
+        <v>3813</v>
+      </c>
+      <c r="D1219" t="s">
+        <v>4127</v>
+      </c>
+    </row>
+    <row r="1220" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A1220" t="s">
+        <v>3814</v>
+      </c>
+      <c r="B1220" t="s">
+        <v>3815</v>
+      </c>
+      <c r="C1220" t="s">
+        <v>3816</v>
+      </c>
+      <c r="D1220" t="s">
+        <v>4128</v>
+      </c>
+    </row>
+    <row r="1221" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A1221" t="s">
+        <v>3817</v>
+      </c>
+      <c r="B1221" t="s">
+        <v>3818</v>
+      </c>
+      <c r="C1221" t="s">
+        <v>3819</v>
+      </c>
+      <c r="D1221" t="s">
+        <v>4129</v>
+      </c>
+    </row>
+    <row r="1222" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A1222" t="s">
+        <v>3820</v>
+      </c>
+      <c r="B1222" t="s">
+        <v>3821</v>
+      </c>
+      <c r="C1222" t="s">
+        <v>3822</v>
+      </c>
+      <c r="D1222" t="s">
+        <v>4130</v>
+      </c>
+    </row>
+    <row r="1223" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A1223" t="s">
+        <v>3823</v>
+      </c>
+      <c r="B1223" t="s">
+        <v>3035</v>
+      </c>
+      <c r="C1223" t="s">
+        <v>3824</v>
+      </c>
+      <c r="D1223" t="s">
+        <v>4131</v>
+      </c>
+    </row>
+    <row r="1224" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A1224" t="s">
+        <v>3825</v>
+      </c>
+      <c r="B1224" t="s">
+        <v>3175</v>
+      </c>
+      <c r="C1224" t="s">
+        <v>3826</v>
+      </c>
+      <c r="D1224" t="s">
+        <v>4132</v>
+      </c>
+    </row>
+    <row r="1225" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A1225" t="s">
+        <v>3827</v>
+      </c>
+      <c r="B1225" t="s">
+        <v>3828</v>
+      </c>
+      <c r="C1225" t="s">
+        <v>3829</v>
+      </c>
+      <c r="D1225" t="s">
+        <v>4133</v>
+      </c>
+    </row>
+    <row r="1226" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A1226" t="s">
+        <v>3830</v>
+      </c>
+      <c r="B1226" t="s">
+        <v>3032</v>
+      </c>
+      <c r="C1226" t="s">
+        <v>3831</v>
+      </c>
+      <c r="D1226" t="s">
+        <v>4134</v>
+      </c>
+    </row>
+    <row r="1227" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A1227" t="s">
+        <v>3832</v>
+      </c>
+      <c r="B1227" t="s">
+        <v>3147</v>
+      </c>
+      <c r="C1227" t="s">
+        <v>3833</v>
+      </c>
+      <c r="D1227" t="s">
+        <v>4135</v>
+      </c>
+    </row>
+    <row r="1228" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A1228" t="s">
+        <v>3834</v>
+      </c>
+      <c r="B1228" t="s">
+        <v>3141</v>
+      </c>
+      <c r="C1228" t="s">
+        <v>3835</v>
+      </c>
+      <c r="D1228" t="s">
+        <v>4136</v>
+      </c>
+    </row>
+    <row r="1229" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A1229" t="s">
+        <v>3836</v>
+      </c>
+      <c r="B1229" t="s">
+        <v>3135</v>
+      </c>
+      <c r="C1229" t="s">
+        <v>3837</v>
+      </c>
+      <c r="D1229" t="s">
+        <v>4137</v>
+      </c>
+    </row>
+    <row r="1230" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A1230" t="s">
+        <v>3838</v>
+      </c>
+      <c r="B1230" t="s">
+        <v>3839</v>
+      </c>
+      <c r="C1230" t="s">
+        <v>3840</v>
+      </c>
+      <c r="D1230" t="s">
+        <v>4138</v>
+      </c>
+    </row>
+    <row r="1231" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A1231" t="s">
+        <v>3841</v>
+      </c>
+      <c r="B1231" t="s">
+        <v>3717</v>
+      </c>
+      <c r="C1231" t="s">
+        <v>3842</v>
+      </c>
+      <c r="D1231" t="s">
+        <v>4139</v>
+      </c>
+    </row>
+    <row r="1232" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A1232" t="s">
+        <v>3843</v>
+      </c>
+      <c r="B1232" t="s">
+        <v>3061</v>
+      </c>
+      <c r="C1232" t="s">
+        <v>3844</v>
+      </c>
+      <c r="D1232" t="s">
+        <v>4140</v>
+      </c>
+    </row>
+    <row r="1233" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A1233" t="s">
+        <v>3845</v>
+      </c>
+      <c r="B1233" t="s">
+        <v>3846</v>
+      </c>
+      <c r="C1233" t="s">
+        <v>3847</v>
+      </c>
+      <c r="D1233" t="s">
+        <v>4141</v>
+      </c>
+    </row>
+    <row r="1234" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A1234" t="s">
+        <v>3848</v>
+      </c>
+      <c r="B1234" t="s">
+        <v>3014</v>
+      </c>
+      <c r="C1234" t="s">
+        <v>3849</v>
+      </c>
+      <c r="D1234" t="s">
+        <v>4142</v>
+      </c>
+    </row>
+    <row r="1235" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A1235" t="s">
+        <v>3850</v>
+      </c>
+      <c r="B1235" t="s">
+        <v>3851</v>
+      </c>
+      <c r="C1235" t="s">
+        <v>3852</v>
+      </c>
+      <c r="D1235" t="s">
+        <v>4143</v>
+      </c>
+    </row>
+    <row r="1236" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A1236" t="s">
+        <v>3853</v>
+      </c>
+      <c r="B1236" t="s">
+        <v>3854</v>
+      </c>
+      <c r="C1236" t="s">
+        <v>3855</v>
+      </c>
+      <c r="D1236" t="s">
+        <v>4144</v>
+      </c>
+    </row>
+    <row r="1237" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A1237" t="s">
+        <v>3856</v>
+      </c>
+      <c r="B1237" t="s">
+        <v>3857</v>
+      </c>
+      <c r="C1237" t="s">
+        <v>3858</v>
+      </c>
+      <c r="D1237" t="s">
+        <v>4145</v>
+      </c>
+    </row>
+    <row r="1238" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A1238" t="s">
+        <v>3859</v>
+      </c>
+      <c r="B1238" t="s">
+        <v>3860</v>
+      </c>
+      <c r="C1238" t="s">
+        <v>3861</v>
+      </c>
+      <c r="D1238" t="s">
+        <v>4146</v>
+      </c>
+    </row>
+    <row r="1239" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A1239" t="s">
+        <v>3862</v>
+      </c>
+      <c r="B1239" t="s">
+        <v>3863</v>
+      </c>
+      <c r="C1239" t="s">
+        <v>3864</v>
+      </c>
+      <c r="D1239" t="s">
+        <v>4147</v>
+      </c>
+    </row>
+    <row r="1240" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A1240" t="s">
+        <v>3865</v>
+      </c>
+      <c r="B1240" t="s">
+        <v>3866</v>
+      </c>
+      <c r="C1240" t="s">
+        <v>3867</v>
+      </c>
+      <c r="D1240" t="s">
+        <v>4148</v>
+      </c>
+    </row>
+    <row r="1241" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A1241" t="s">
+        <v>3868</v>
+      </c>
+      <c r="B1241" t="s">
+        <v>3869</v>
+      </c>
+      <c r="C1241" t="s">
+        <v>3870</v>
+      </c>
+      <c r="D1241" t="s">
+        <v>4149</v>
+      </c>
+    </row>
+    <row r="1242" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A1242" t="s">
+        <v>3871</v>
+      </c>
+      <c r="B1242" t="s">
+        <v>3872</v>
+      </c>
+      <c r="C1242" t="s">
+        <v>3873</v>
+      </c>
+      <c r="D1242" t="s">
+        <v>4150</v>
+      </c>
+    </row>
+    <row r="1243" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A1243" t="s">
+        <v>3874</v>
+      </c>
+      <c r="B1243" t="s">
+        <v>3875</v>
+      </c>
+      <c r="C1243" t="s">
+        <v>3876</v>
+      </c>
+      <c r="D1243" t="s">
+        <v>4151</v>
+      </c>
+    </row>
+    <row r="1244" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A1244" t="s">
+        <v>3877</v>
+      </c>
+      <c r="B1244" t="s">
+        <v>3878</v>
+      </c>
+      <c r="C1244" t="s">
+        <v>3879</v>
+      </c>
+      <c r="D1244" t="s">
+        <v>4152</v>
+      </c>
+    </row>
+    <row r="1245" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A1245" t="s">
+        <v>3880</v>
+      </c>
+      <c r="B1245" t="s">
+        <v>3881</v>
+      </c>
+      <c r="C1245" t="s">
+        <v>3882</v>
+      </c>
+      <c r="D1245" t="s">
+        <v>4153</v>
+      </c>
+    </row>
+    <row r="1246" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A1246" t="s">
+        <v>3883</v>
+      </c>
+      <c r="B1246" t="s">
+        <v>3884</v>
+      </c>
+      <c r="C1246" t="s">
+        <v>3885</v>
+      </c>
+      <c r="D1246" t="s">
+        <v>4154</v>
+      </c>
+    </row>
+    <row r="1247" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A1247" t="s">
+        <v>3886</v>
+      </c>
+      <c r="B1247" t="s">
+        <v>3887</v>
+      </c>
+      <c r="C1247" t="s">
+        <v>3888</v>
+      </c>
+      <c r="D1247" t="s">
+        <v>4155</v>
+      </c>
+    </row>
+    <row r="1248" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A1248" t="s">
+        <v>3889</v>
+      </c>
+      <c r="B1248" t="s">
+        <v>3890</v>
+      </c>
+      <c r="C1248" t="s">
+        <v>3891</v>
+      </c>
+      <c r="D1248" t="s">
+        <v>4156</v>
+      </c>
+    </row>
+    <row r="1249" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A1249" t="s">
+        <v>3892</v>
+      </c>
+      <c r="B1249" t="s">
+        <v>3893</v>
+      </c>
+      <c r="C1249" t="s">
+        <v>3894</v>
+      </c>
+      <c r="D1249" t="s">
+        <v>4157</v>
+      </c>
+    </row>
+    <row r="1250" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A1250" t="s">
+        <v>3895</v>
+      </c>
+      <c r="B1250" t="s">
+        <v>3896</v>
+      </c>
+      <c r="C1250" t="s">
+        <v>3897</v>
+      </c>
+      <c r="D1250" t="s">
+        <v>4158</v>
+      </c>
+    </row>
+    <row r="1251" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A1251" t="s">
+        <v>3898</v>
+      </c>
+      <c r="B1251" t="s">
+        <v>3144</v>
+      </c>
+      <c r="C1251" t="s">
+        <v>3899</v>
+      </c>
+      <c r="D1251" t="s">
+        <v>4159</v>
+      </c>
+    </row>
+    <row r="1252" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A1252" t="s">
+        <v>3900</v>
+      </c>
+      <c r="B1252" t="s">
+        <v>3901</v>
+      </c>
+      <c r="C1252" t="s">
+        <v>3902</v>
+      </c>
+      <c r="D1252" t="s">
+        <v>4160</v>
+      </c>
+    </row>
+    <row r="1253" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A1253" t="s">
+        <v>3903</v>
+      </c>
+      <c r="B1253" t="s">
+        <v>3129</v>
+      </c>
+      <c r="C1253" t="s">
+        <v>3904</v>
+      </c>
+      <c r="D1253" t="s">
+        <v>4161</v>
+      </c>
+    </row>
+    <row r="1254" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A1254" t="s">
+        <v>3905</v>
+      </c>
+      <c r="B1254" t="s">
+        <v>3061</v>
+      </c>
+      <c r="C1254" t="s">
+        <v>3906</v>
+      </c>
+      <c r="D1254" t="s">
+        <v>4162</v>
+      </c>
+    </row>
+    <row r="1255" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A1255" t="s">
+        <v>3907</v>
+      </c>
+      <c r="B1255" t="s">
+        <v>3141</v>
+      </c>
+      <c r="C1255" t="s">
+        <v>3908</v>
+      </c>
+      <c r="D1255" t="s">
+        <v>4163</v>
+      </c>
+    </row>
+    <row r="1256" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A1256" t="s">
+        <v>3909</v>
+      </c>
+      <c r="B1256" t="s">
+        <v>3026</v>
+      </c>
+      <c r="C1256" t="s">
+        <v>3910</v>
+      </c>
+      <c r="D1256" t="s">
+        <v>4164</v>
+      </c>
+    </row>
+    <row r="1257" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A1257" t="s">
+        <v>3911</v>
+      </c>
+      <c r="B1257" t="s">
+        <v>3774</v>
+      </c>
+      <c r="C1257" t="s">
+        <v>3912</v>
+      </c>
+      <c r="D1257" t="s">
+        <v>4165</v>
+      </c>
+    </row>
+    <row r="1258" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A1258" t="s">
+        <v>3913</v>
+      </c>
+      <c r="B1258" t="s">
+        <v>3035</v>
+      </c>
+      <c r="C1258" t="s">
+        <v>3914</v>
+      </c>
+      <c r="D1258" t="s">
+        <v>4166</v>
+      </c>
+    </row>
+    <row r="1259" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A1259" t="s">
+        <v>3915</v>
+      </c>
+      <c r="B1259" t="s">
+        <v>3717</v>
+      </c>
+      <c r="C1259" t="s">
+        <v>3916</v>
+      </c>
+      <c r="D1259" t="s">
+        <v>4167</v>
+      </c>
+    </row>
+    <row r="1260" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A1260" t="s">
+        <v>3917</v>
+      </c>
+      <c r="B1260" t="s">
+        <v>3138</v>
+      </c>
+      <c r="C1260" t="s">
+        <v>3918</v>
+      </c>
+      <c r="D1260" t="s">
+        <v>4168</v>
+      </c>
+    </row>
+    <row r="1261" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A1261" t="s">
+        <v>3919</v>
+      </c>
+      <c r="B1261" t="s">
+        <v>3175</v>
+      </c>
+      <c r="C1261" t="s">
+        <v>3920</v>
+      </c>
+      <c r="D1261" t="s">
+        <v>4169</v>
+      </c>
+    </row>
+    <row r="1262" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A1262" t="s">
+        <v>3921</v>
+      </c>
+      <c r="B1262" t="s">
+        <v>3922</v>
+      </c>
+      <c r="C1262" t="s">
+        <v>3923</v>
+      </c>
+      <c r="D1262" t="s">
+        <v>4170</v>
+      </c>
+    </row>
+    <row r="1263" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A1263" t="s">
+        <v>3924</v>
+      </c>
+      <c r="B1263" t="s">
+        <v>3047</v>
+      </c>
+      <c r="C1263" t="s">
+        <v>3925</v>
+      </c>
+      <c r="D1263" t="s">
+        <v>4171</v>
+      </c>
+    </row>
+    <row r="1264" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A1264" t="s">
+        <v>3926</v>
+      </c>
+      <c r="B1264" t="s">
+        <v>3927</v>
+      </c>
+      <c r="C1264" t="s">
+        <v>3928</v>
+      </c>
+      <c r="D1264" t="s">
+        <v>4172</v>
+      </c>
+    </row>
+    <row r="1265" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A1265" t="s">
+        <v>3929</v>
+      </c>
+      <c r="B1265" t="s">
+        <v>3117</v>
+      </c>
+      <c r="C1265" t="s">
+        <v>3930</v>
+      </c>
+      <c r="D1265" t="s">
+        <v>4173</v>
+      </c>
+    </row>
+    <row r="1266" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A1266" t="s">
+        <v>3931</v>
+      </c>
+      <c r="B1266" t="s">
+        <v>3080</v>
+      </c>
+      <c r="C1266" t="s">
+        <v>3932</v>
+      </c>
+      <c r="D1266" t="s">
+        <v>4174</v>
+      </c>
+    </row>
+    <row r="1267" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A1267" t="s">
+        <v>3933</v>
+      </c>
+      <c r="B1267" t="s">
+        <v>3696</v>
+      </c>
+      <c r="C1267" t="s">
+        <v>3934</v>
+      </c>
+      <c r="D1267" t="s">
+        <v>4175</v>
+      </c>
+    </row>
+    <row r="1268" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A1268" t="s">
+        <v>3935</v>
+      </c>
+      <c r="B1268" t="s">
+        <v>3726</v>
+      </c>
+      <c r="C1268" t="s">
+        <v>3936</v>
+      </c>
+      <c r="D1268" t="s">
+        <v>4176</v>
+      </c>
+    </row>
+    <row r="1269" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A1269" t="s">
+        <v>3937</v>
+      </c>
+      <c r="B1269" t="s">
+        <v>3684</v>
+      </c>
+      <c r="C1269" t="s">
+        <v>3938</v>
+      </c>
+      <c r="D1269" t="s">
+        <v>4177</v>
+      </c>
+    </row>
+    <row r="1270" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A1270" t="s">
+        <v>3939</v>
+      </c>
+      <c r="B1270" t="s">
+        <v>3089</v>
+      </c>
+      <c r="C1270" t="s">
+        <v>3940</v>
+      </c>
+      <c r="D1270" t="s">
+        <v>4178</v>
+      </c>
+    </row>
+    <row r="1271" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A1271" t="s">
+        <v>3941</v>
+      </c>
+      <c r="B1271" t="s">
+        <v>3723</v>
+      </c>
+      <c r="C1271" t="s">
+        <v>3942</v>
+      </c>
+      <c r="D1271" t="s">
+        <v>4179</v>
+      </c>
+    </row>
+    <row r="1272" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A1272" t="s">
+        <v>3943</v>
+      </c>
+      <c r="B1272" t="s">
+        <v>3744</v>
+      </c>
+      <c r="C1272" t="s">
+        <v>3944</v>
+      </c>
+      <c r="D1272" t="s">
+        <v>4180</v>
+      </c>
+    </row>
+    <row r="1273" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A1273" t="s">
+        <v>3945</v>
+      </c>
+      <c r="B1273" t="s">
+        <v>3946</v>
+      </c>
+      <c r="C1273" t="s">
+        <v>3947</v>
+      </c>
+      <c r="D1273" t="s">
+        <v>4181</v>
+      </c>
+    </row>
+    <row r="1274" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A1274" t="s">
+        <v>3948</v>
+      </c>
+      <c r="B1274" t="s">
+        <v>3038</v>
+      </c>
+      <c r="C1274" t="s">
+        <v>3949</v>
+      </c>
+      <c r="D1274" t="s">
+        <v>4182</v>
+      </c>
+    </row>
+    <row r="1275" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A1275" t="s">
+        <v>3950</v>
+      </c>
+      <c r="B1275" t="s">
+        <v>3014</v>
+      </c>
+      <c r="C1275" t="s">
+        <v>3951</v>
+      </c>
+      <c r="D1275" t="s">
+        <v>4183</v>
+      </c>
+    </row>
+    <row r="1276" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A1276" t="s">
+        <v>3952</v>
+      </c>
+      <c r="B1276" t="s">
+        <v>3141</v>
+      </c>
+      <c r="C1276" t="s">
+        <v>3953</v>
+      </c>
+      <c r="D1276" t="s">
+        <v>4184</v>
+      </c>
+    </row>
+    <row r="1277" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A1277" t="s">
+        <v>3954</v>
+      </c>
+      <c r="B1277" t="s">
+        <v>3129</v>
+      </c>
+      <c r="C1277" t="s">
+        <v>3955</v>
+      </c>
+      <c r="D1277" t="s">
+        <v>4185</v>
+      </c>
+    </row>
+    <row r="1278" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A1278" t="s">
+        <v>3956</v>
+      </c>
+      <c r="B1278" t="s">
+        <v>3117</v>
+      </c>
+      <c r="C1278" t="s">
+        <v>3957</v>
+      </c>
+      <c r="D1278" t="s">
+        <v>4186</v>
+      </c>
+    </row>
+    <row r="1279" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A1279" t="s">
+        <v>3958</v>
+      </c>
+      <c r="B1279" t="s">
+        <v>3157</v>
+      </c>
+      <c r="C1279" t="s">
+        <v>3959</v>
+      </c>
+      <c r="D1279" t="s">
+        <v>4187</v>
+      </c>
+    </row>
+    <row r="1280" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A1280" t="s">
+        <v>3960</v>
+      </c>
+      <c r="B1280" t="s">
+        <v>3961</v>
+      </c>
+      <c r="C1280" t="s">
+        <v>3962</v>
+      </c>
+      <c r="D1280" t="s">
+        <v>4188</v>
+      </c>
+    </row>
+    <row r="1281" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A1281" t="s">
+        <v>3963</v>
+      </c>
+      <c r="B1281" t="s">
+        <v>3017</v>
+      </c>
+      <c r="C1281" t="s">
+        <v>3964</v>
+      </c>
+      <c r="D1281" t="s">
+        <v>4189</v>
+      </c>
+    </row>
+    <row r="1282" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A1282" t="s">
+        <v>3965</v>
+      </c>
+      <c r="B1282" t="s">
+        <v>3086</v>
+      </c>
+      <c r="C1282" t="s">
+        <v>3966</v>
+      </c>
+      <c r="D1282" t="s">
+        <v>4190</v>
+      </c>
+    </row>
+    <row r="1283" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A1283" t="s">
+        <v>3967</v>
+      </c>
+      <c r="B1283" t="s">
+        <v>3968</v>
+      </c>
+      <c r="C1283" t="s">
+        <v>3969</v>
+      </c>
+      <c r="D1283" t="s">
+        <v>4191</v>
+      </c>
+    </row>
+    <row r="1284" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A1284" t="s">
+        <v>3970</v>
+      </c>
+      <c r="B1284" t="s">
+        <v>3946</v>
+      </c>
+      <c r="C1284" t="s">
+        <v>3971</v>
+      </c>
+      <c r="D1284" t="s">
+        <v>4192</v>
+      </c>
+    </row>
+    <row r="1285" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A1285" t="s">
+        <v>3972</v>
+      </c>
+      <c r="B1285" t="s">
+        <v>3124</v>
+      </c>
+      <c r="C1285" t="s">
+        <v>3973</v>
+      </c>
+      <c r="D1285" t="s">
+        <v>4193</v>
+      </c>
+    </row>
+    <row r="1286" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A1286" t="s">
+        <v>3974</v>
+      </c>
+      <c r="B1286" t="s">
+        <v>3975</v>
+      </c>
+      <c r="C1286" t="s">
+        <v>3976</v>
+      </c>
+      <c r="D1286" t="s">
+        <v>4194</v>
+      </c>
+    </row>
+    <row r="1287" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A1287" t="s">
+        <v>3977</v>
+      </c>
+      <c r="B1287" t="s">
+        <v>3978</v>
+      </c>
+      <c r="C1287" t="s">
+        <v>3979</v>
+      </c>
+      <c r="D1287" t="s">
+        <v>4195</v>
+      </c>
+    </row>
+    <row r="1288" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A1288" t="s">
+        <v>3980</v>
+      </c>
+      <c r="B1288" t="s">
+        <v>3927</v>
+      </c>
+      <c r="C1288" t="s">
+        <v>3981</v>
+      </c>
+      <c r="D1288" t="s">
+        <v>4196</v>
+      </c>
+    </row>
+    <row r="1289" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A1289" t="s">
+        <v>3982</v>
+      </c>
+      <c r="B1289" t="s">
+        <v>3014</v>
+      </c>
+      <c r="C1289" t="s">
+        <v>3983</v>
+      </c>
+      <c r="D1289" t="s">
+        <v>4197</v>
+      </c>
+    </row>
+    <row r="1290" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A1290" t="s">
+        <v>3984</v>
+      </c>
+      <c r="B1290" t="s">
+        <v>3985</v>
+      </c>
+      <c r="C1290" t="s">
+        <v>3986</v>
+      </c>
+      <c r="D1290" t="s">
+        <v>4198</v>
+      </c>
+    </row>
+    <row r="1291" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A1291" t="s">
+        <v>3987</v>
+      </c>
+      <c r="B1291" t="s">
+        <v>3172</v>
+      </c>
+      <c r="C1291" t="s">
+        <v>3988</v>
+      </c>
+      <c r="D1291" t="s">
+        <v>4199</v>
+      </c>
+    </row>
+    <row r="1292" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A1292" t="s">
+        <v>3989</v>
+      </c>
+      <c r="B1292" t="s">
+        <v>3927</v>
+      </c>
+      <c r="C1292" t="s">
+        <v>3990</v>
+      </c>
+      <c r="D1292" t="s">
+        <v>4200</v>
+      </c>
+    </row>
+    <row r="1293" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A1293" t="s">
+        <v>3991</v>
+      </c>
+      <c r="B1293" t="s">
+        <v>3992</v>
+      </c>
+      <c r="C1293" t="s">
+        <v>3993</v>
+      </c>
+      <c r="D1293" t="s">
+        <v>4201</v>
+      </c>
+    </row>
+    <row r="1294" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A1294" t="s">
+        <v>3994</v>
+      </c>
+      <c r="B1294" t="s">
+        <v>3733</v>
+      </c>
+      <c r="C1294" t="s">
+        <v>3995</v>
+      </c>
+      <c r="D1294" t="s">
+        <v>4202</v>
+      </c>
+    </row>
+    <row r="1295" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A1295" t="s">
+        <v>3996</v>
+      </c>
+      <c r="B1295" t="s">
+        <v>3997</v>
+      </c>
+      <c r="C1295" t="s">
+        <v>3998</v>
+      </c>
+      <c r="D1295" t="s">
+        <v>4203</v>
+      </c>
+    </row>
+    <row r="1296" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A1296" t="s">
+        <v>3999</v>
+      </c>
+      <c r="B1296" t="s">
+        <v>4000</v>
+      </c>
+      <c r="C1296" t="s">
+        <v>4001</v>
+      </c>
+      <c r="D1296" t="s">
+        <v>4204</v>
+      </c>
+    </row>
+    <row r="1297" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A1297" t="s">
+        <v>4002</v>
+      </c>
+      <c r="B1297" t="s">
+        <v>3169</v>
+      </c>
+      <c r="C1297" t="s">
+        <v>4003</v>
+      </c>
+      <c r="D1297" t="s">
+        <v>4205</v>
+      </c>
+    </row>
+    <row r="1298" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A1298" t="s">
+        <v>4004</v>
+      </c>
+      <c r="B1298" t="s">
+        <v>3157</v>
+      </c>
+      <c r="C1298" t="s">
+        <v>4005</v>
+      </c>
+      <c r="D1298" t="s">
+        <v>4206</v>
+      </c>
+    </row>
+    <row r="1299" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A1299" t="s">
+        <v>4006</v>
+      </c>
+      <c r="B1299" t="s">
+        <v>3175</v>
+      </c>
+      <c r="C1299" t="s">
+        <v>4007</v>
+      </c>
+      <c r="D1299" t="s">
+        <v>4207</v>
+      </c>
+    </row>
+    <row r="1300" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A1300" t="s">
+        <v>4008</v>
+      </c>
+      <c r="B1300" t="s">
+        <v>4009</v>
+      </c>
+      <c r="C1300" t="s">
+        <v>4010</v>
+      </c>
+      <c r="D1300" t="s">
+        <v>4208</v>
+      </c>
+    </row>
+    <row r="1301" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A1301" t="s">
+        <v>4011</v>
+      </c>
+      <c r="B1301" t="s">
+        <v>3172</v>
+      </c>
+      <c r="C1301" t="s">
+        <v>4012</v>
+      </c>
+      <c r="D1301" t="s">
+        <v>4209</v>
+      </c>
+    </row>
+    <row r="1302" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A1302" t="s">
+        <v>4013</v>
+      </c>
+      <c r="B1302" t="s">
+        <v>4014</v>
+      </c>
+      <c r="C1302" t="s">
+        <v>4015</v>
+      </c>
+      <c r="D1302" t="s">
+        <v>4210</v>
+      </c>
+    </row>
+    <row r="1303" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A1303" t="s">
+        <v>4016</v>
+      </c>
+      <c r="B1303" t="s">
+        <v>3717</v>
+      </c>
+      <c r="C1303" t="s">
+        <v>4017</v>
+      </c>
+      <c r="D1303" t="s">
+        <v>4211</v>
+      </c>
+    </row>
+    <row r="1304" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A1304" t="s">
+        <v>4018</v>
+      </c>
+      <c r="B1304" t="s">
+        <v>4019</v>
+      </c>
+      <c r="C1304" t="s">
+        <v>4020</v>
+      </c>
+      <c r="D1304" t="s">
+        <v>4212</v>
+      </c>
+    </row>
+    <row r="1305" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A1305" t="s">
+        <v>4021</v>
+      </c>
+      <c r="B1305" t="s">
+        <v>3774</v>
+      </c>
+      <c r="C1305" t="s">
+        <v>4022</v>
+      </c>
+      <c r="D1305" t="s">
+        <v>4213</v>
+      </c>
+    </row>
+    <row r="1306" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A1306" t="s">
+        <v>4023</v>
+      </c>
+      <c r="B1306" t="s">
+        <v>4024</v>
+      </c>
+      <c r="C1306" t="s">
+        <v>4025</v>
+      </c>
+      <c r="D1306" t="s">
+        <v>4214</v>
+      </c>
+    </row>
+    <row r="1307" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A1307" t="s">
+        <v>4026</v>
+      </c>
+      <c r="B1307" t="s">
+        <v>3749</v>
+      </c>
+      <c r="C1307" t="s">
+        <v>4027</v>
+      </c>
+      <c r="D1307" t="s">
+        <v>4215</v>
+      </c>
+    </row>
+    <row r="1308" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A1308" t="s">
+        <v>4028</v>
+      </c>
+      <c r="B1308" t="s">
+        <v>3089</v>
+      </c>
+      <c r="C1308" t="s">
+        <v>4029</v>
+      </c>
+      <c r="D1308" t="s">
+        <v>4216</v>
+      </c>
+    </row>
+    <row r="1309" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A1309" t="s">
+        <v>4030</v>
+      </c>
+      <c r="B1309" t="s">
+        <v>4031</v>
+      </c>
+      <c r="C1309" t="s">
+        <v>4032</v>
+      </c>
+      <c r="D1309" t="s">
+        <v>4217</v>
+      </c>
+    </row>
+    <row r="1310" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A1310" t="s">
+        <v>4033</v>
+      </c>
+      <c r="B1310" t="s">
+        <v>4034</v>
+      </c>
+      <c r="C1310" t="s">
+        <v>4035</v>
+      </c>
+      <c r="D1310" t="s">
+        <v>4218</v>
+      </c>
+    </row>
+    <row r="1311" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A1311" t="s">
+        <v>4036</v>
+      </c>
+      <c r="B1311" t="s">
+        <v>3749</v>
+      </c>
+      <c r="C1311" t="s">
+        <v>4037</v>
+      </c>
+      <c r="D1311" t="s">
+        <v>4219</v>
+      </c>
+    </row>
+    <row r="1312" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A1312" t="s">
+        <v>4038</v>
+      </c>
+      <c r="B1312" t="s">
+        <v>3696</v>
+      </c>
+      <c r="C1312" t="s">
+        <v>4039</v>
+      </c>
+      <c r="D1312" t="s">
+        <v>4220</v>
+      </c>
+    </row>
+    <row r="1313" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A1313" t="s">
+        <v>4040</v>
+      </c>
+      <c r="B1313" t="s">
+        <v>4041</v>
+      </c>
+      <c r="C1313" t="s">
+        <v>4042</v>
+      </c>
+      <c r="D1313" t="s">
+        <v>4221</v>
+      </c>
+    </row>
+    <row r="1314" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A1314" t="s">
+        <v>4043</v>
+      </c>
+      <c r="B1314" t="s">
+        <v>3132</v>
+      </c>
+      <c r="C1314" t="s">
+        <v>4044</v>
+      </c>
+      <c r="D1314" t="s">
+        <v>4222</v>
+      </c>
+    </row>
+    <row r="1315" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A1315" t="s">
+        <v>4045</v>
+      </c>
+      <c r="B1315" t="s">
+        <v>3922</v>
+      </c>
+      <c r="C1315" t="s">
+        <v>4046</v>
+      </c>
+      <c r="D1315" t="s">
+        <v>4223</v>
+      </c>
+    </row>
+    <row r="1316" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A1316" t="s">
+        <v>4047</v>
+      </c>
+      <c r="B1316" t="s">
+        <v>3723</v>
+      </c>
+      <c r="C1316" t="s">
+        <v>4048</v>
+      </c>
+      <c r="D1316" t="s">
+        <v>4224</v>
+      </c>
+    </row>
+    <row r="1317" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A1317" t="s">
+        <v>4049</v>
+      </c>
+      <c r="B1317" t="s">
+        <v>3756</v>
+      </c>
+      <c r="C1317" t="s">
+        <v>4050</v>
+      </c>
+      <c r="D1317" t="s">
+        <v>4225</v>
+      </c>
+    </row>
+    <row r="1318" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A1318" t="s">
+        <v>4051</v>
+      </c>
+      <c r="B1318" t="s">
+        <v>3796</v>
+      </c>
+      <c r="C1318" t="s">
+        <v>4052</v>
+      </c>
+      <c r="D1318" t="s">
+        <v>4226</v>
+      </c>
+    </row>
+    <row r="1319" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A1319" t="s">
+        <v>4053</v>
+      </c>
+      <c r="B1319" t="s">
+        <v>3035</v>
+      </c>
+      <c r="C1319" t="s">
+        <v>4054</v>
+      </c>
+      <c r="D1319" t="s">
+        <v>4227</v>
+      </c>
+    </row>
+    <row r="1320" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A1320" t="s">
+        <v>4055</v>
+      </c>
+      <c r="B1320" t="s">
+        <v>3765</v>
+      </c>
+      <c r="C1320" t="s">
+        <v>4056</v>
+      </c>
+      <c r="D1320" t="s">
+        <v>4228</v>
+      </c>
+    </row>
+    <row r="1321" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A1321" t="s">
+        <v>4057</v>
+      </c>
+      <c r="B1321" t="s">
+        <v>3047</v>
+      </c>
+      <c r="C1321" t="s">
+        <v>4058</v>
+      </c>
+      <c r="D1321" t="s">
+        <v>4229</v>
+      </c>
+    </row>
+    <row r="1322" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A1322" t="s">
+        <v>4059</v>
+      </c>
+      <c r="B1322" t="s">
+        <v>3723</v>
+      </c>
+      <c r="C1322" t="s">
+        <v>4060</v>
+      </c>
+      <c r="D1322" t="s">
+        <v>4230</v>
+      </c>
+    </row>
+    <row r="1323" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A1323" t="s">
+        <v>4061</v>
+      </c>
+      <c r="B1323" t="s">
+        <v>3839</v>
+      </c>
+      <c r="C1323" t="s">
+        <v>4062</v>
+      </c>
+      <c r="D1323" t="s">
+        <v>4231</v>
+      </c>
+    </row>
+    <row r="1324" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A1324" t="s">
+        <v>4063</v>
+      </c>
+      <c r="B1324" t="s">
+        <v>3061</v>
+      </c>
+      <c r="C1324" t="s">
+        <v>4064</v>
+      </c>
+      <c r="D1324" t="s">
+        <v>4232</v>
+      </c>
+    </row>
+    <row r="1325" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A1325" t="s">
+        <v>4065</v>
+      </c>
+      <c r="B1325" t="s">
+        <v>4066</v>
+      </c>
+      <c r="C1325" t="s">
+        <v>4067</v>
+      </c>
+      <c r="D1325" t="s">
+        <v>4233</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:D956" xr:uid="{EE52D9B7-0D33-6C4B-ABD2-124A93043E14}"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" horizontalDpi="0" verticalDpi="0"/>
 </worksheet>
 </file>